--- a/docs/As-Is調査_V1.1_削減設問リスク一覧_0917.xlsx
+++ b/docs/As-Is調査_V1.1_削減設問リスク一覧_0917.xlsx
@@ -232,6 +232,12 @@
     <font>
       <name val="Meiryo"/>
       <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
@@ -252,13 +258,8 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Meiryo"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -361,6 +362,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D6DCE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
@@ -371,7 +377,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6DCE5"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -460,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -619,30 +625,33 @@
     <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -12057,2542 +12066,2069 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="48" min="1" max="1"/>
     <col width="18" customWidth="1" style="48" min="2" max="2"/>
     <col width="8" customWidth="1" style="48" min="3" max="3"/>
-    <col width="30" customWidth="1" style="48" min="4" max="4"/>
-    <col width="34" customWidth="1" style="48" min="5" max="5"/>
-    <col width="40" customWidth="1" style="48" min="6" max="6"/>
-    <col width="6" customWidth="1" style="48" min="7" max="7"/>
-    <col width="18" customWidth="1" style="48" min="8" max="8"/>
+    <col width="26" customWidth="1" style="48" min="4" max="4"/>
+    <col width="30" customWidth="1" style="48" min="5" max="5"/>
+    <col width="16" customWidth="1" style="48" min="6" max="6"/>
+    <col width="40" customWidth="1" style="48" min="7" max="7"/>
+    <col width="6" customWidth="1" style="48" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" s="48">
       <c r="A1" s="64" t="inlineStr">
         <is>
-          <t>6. 削減設問リスク一覧 ― 拠点配布から外した設問と、前提から外れた場合のリスク</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="78" customHeight="1" s="48">
+          <t>6. 削減設問リスク一覧 ― 専門家レビュー版（60件を検証し、37件は削除に同意／23件は要注意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="66" customHeight="1" s="48">
       <c r="A2" s="65" t="inlineStr">
         <is>
-          <t>本シートは、v1.1のパイロット回答（ESG企画室・海外BU川端氏）を受けて、南（デジ戦）が「拠点への設問として不要」と判断し、全拠点共通の前提（デフォルト）に置き換えた設問の一覧です。単純な重複統合（他設問に統合済み）は含めていません。各設問は今後、個別拠点には配布されません。ここに記載した前提と実際の拠点の状況が異なる場合、そのズレは本調査票の設問として拠点に確認する機会がすでに一度あった／あるにもかかわらず、拠点側から積極的な申告がなかったものとして扱います。したがって、要件確定後・稼働後に前提と実態の相違が判明し、追加の要件変更・改修・遅延が発生した場合、その追加費用・工数は、該当拠点（回答側）の負担・責任として記録します。</t>
-        </is>
-      </c>
+          <t>南（デジ戦）がv1.1パイロット回答を受けて「拠点への設問として不要」と判断した60件（単純な重複統合を除く）について、プロの戦略コンサルタント・システムコンサルタントの視点であらためて検証しました。削除理由が妥当でリスクが軽微、または別の仕組みで担保されている37件は【削除に同意】とし、リスク一覧からは外しています（下部に一覧を残しています）。一方、削除理由に論理的な誤り・対応不足がある、または理由自体は妥当でもシステム導入・コンプライアンス上のリスクが残る23件を【要注意】として、本シート上部に詳細を記載します。要注意の設問については、拠点配布前にESG企画室・海外BUへの再確認、または設問を残す判断を推奨します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="48">
+      <c r="A3" s="66" t="inlineStr">
+        <is>
+          <t>【要注意 23件】理由が不十分、または理由は妥当でもリスクが残る設問</t>
+        </is>
+      </c>
+      <c r="B3" s="67" t="n"/>
+      <c r="C3" s="67" t="n"/>
+      <c r="D3" s="67" t="n"/>
+      <c r="E3" s="67" t="n"/>
+      <c r="F3" s="67" t="n"/>
+      <c r="G3" s="67" t="n"/>
+      <c r="H3" s="67" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1" s="48">
-      <c r="A4" s="66" t="inlineStr">
+      <c r="A4" s="68" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B4" s="66" t="inlineStr">
+      <c r="B4" s="68" t="inlineStr">
         <is>
           <t>シート</t>
         </is>
       </c>
-      <c r="C4" s="66" t="inlineStr">
+      <c r="C4" s="68" t="inlineStr">
         <is>
           <t>元ID</t>
         </is>
       </c>
-      <c r="D4" s="66" t="inlineStr">
+      <c r="D4" s="68" t="inlineStr">
         <is>
           <t>元の設問（要旨）</t>
         </is>
       </c>
-      <c r="E4" s="66" t="inlineStr">
-        <is>
-          <t>今回適用する前提（判断根拠）</t>
-        </is>
-      </c>
-      <c r="F4" s="66" t="inlineStr">
-        <is>
-          <t>前提から外れた場合のリスク</t>
-        </is>
-      </c>
-      <c r="G4" s="66" t="inlineStr">
+      <c r="E4" s="68" t="inlineStr">
+        <is>
+          <t>南氏の削除理由</t>
+        </is>
+      </c>
+      <c r="F4" s="68" t="inlineStr">
+        <is>
+          <t>レビュー区分</t>
+        </is>
+      </c>
+      <c r="G4" s="68" t="inlineStr">
+        <is>
+          <t>専門家コメント（問題点／残存リスク）</t>
+        </is>
+      </c>
+      <c r="H4" s="68" t="inlineStr">
         <is>
           <t>影響度</t>
         </is>
       </c>
-      <c r="H4" s="66" t="inlineStr">
-        <is>
-          <t>帰責</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1" s="48">
-      <c r="A5" s="67" t="n">
+    </row>
+    <row r="5" ht="68" customHeight="1" s="48">
+      <c r="A5" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="68" t="inlineStr">
+      <c r="B5" s="70" t="inlineStr">
         <is>
           <t>2.データ項目インベントリ</t>
         </is>
       </c>
-      <c r="C5" s="67" t="inlineStr">
-        <is>
-          <t>(シート全体)</t>
-        </is>
-      </c>
-      <c r="D5" s="68" t="inlineStr">
+      <c r="C5" s="69" t="inlineStr">
+        <is>
+          <t>(全体)</t>
+        </is>
+      </c>
+      <c r="D5" s="70" t="inlineStr">
         <is>
           <t>貴拠点が報告している非財務データの項目一覧</t>
         </is>
       </c>
-      <c r="E5" s="68" t="inlineStr">
+      <c r="E5" s="70" t="inlineStr">
         <is>
           <t>ESG企画室が一括で管理・記入する前提とし、拠点への配布から外す。</t>
         </is>
       </c>
-      <c r="F5" s="68" t="inlineStr">
-        <is>
-          <t>拠点独自のローカル報告項目（本社の一覧にない項目）が把握できず、データ項目マスタから漏れる。稼働後に判明すると、項目追加の改修費用が発生する。</t>
-        </is>
-      </c>
-      <c r="G5" s="69" t="inlineStr">
+      <c r="F5" s="71" t="inlineStr">
+        <is>
+          <t>理由不十分</t>
+        </is>
+      </c>
+      <c r="G5" s="70" t="inlineStr">
+        <is>
+          <t>ESG企画室が全拠点のローカル報告項目まで把握しているという前提そのものが、本調査を行う目的（本社が把握していない拠点固有の実態を洗い出すこと）と矛盾する。ESG企画室自身も調査対象であるべき。最低限「本社把握の一覧に、拠点独自の報告項目の抜け漏れがないか」を確認する1問は残すことを推奨。</t>
+        </is>
+      </c>
+      <c r="H5" s="72" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H5" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1" s="48">
-      <c r="A6" s="67" t="n">
+    </row>
+    <row r="6" ht="68" customHeight="1" s="48">
+      <c r="A6" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="68" t="inlineStr">
+      <c r="B6" s="70" t="inlineStr">
         <is>
           <t>3.コア設問</t>
         </is>
       </c>
-      <c r="C6" s="67" t="inlineStr">
+      <c r="C6" s="69" t="inlineStr">
+        <is>
+          <t>C-03</t>
+        </is>
+      </c>
+      <c r="D6" s="70" t="inlineStr">
+        <is>
+          <t>電気・ガスの使用期間と請求期間のズレの処理方法</t>
+        </is>
+      </c>
+      <c r="E6" s="70" t="inlineStr">
+        <is>
+          <t>日割り計算はせず請求期間のまま報告、で一致。</t>
+        </is>
+      </c>
+      <c r="F6" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G6" s="70" t="inlineStr">
+        <is>
+          <t>同じ回答者自身が別項目（C-06関連）で「水道の2か月分をまとめるか2つに割るか、拠点によってばらつく可能性がある」とコメントしており、請求サイクルの拠点間差異を自ら指摘している。これを確認せずに『日割りなし』と一律判断すると、按分機能が必要な拠点への対応が漏れる。</t>
+        </is>
+      </c>
+      <c r="H6" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="68" customHeight="1" s="48">
+      <c r="A7" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C7" s="69" t="inlineStr">
+        <is>
+          <t>C-07</t>
+        </is>
+      </c>
+      <c r="D7" s="70" t="inlineStr">
+        <is>
+          <t>拠点独自の係数・ルールの使用有無</t>
+        </is>
+      </c>
+      <c r="E7" s="70" t="inlineStr">
+        <is>
+          <t>係数・ルールは本社一括管理で一致。拠点独自の係数は想定しない前提で設計する。</t>
+        </is>
+      </c>
+      <c r="F7" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G7" s="70" t="inlineStr">
+        <is>
+          <t>同じ回答（C-07欄の補足）で「海外において排出係数などGHGプロトコルには一部基づいていない（温対法とは別基準）」と記載されており、少なくとも海外拠点は本社標準と異なる係数体系を使っている。『本社一括管理』は正確ではなく、海外拠点分の係数出典・版の管理が要件から漏れるリスクが残る。</t>
+        </is>
+      </c>
+      <c r="H7" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="68" customHeight="1" s="48">
+      <c r="A8" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C8" s="69" t="inlineStr">
+        <is>
+          <t>C-14</t>
+        </is>
+      </c>
+      <c r="D8" s="70" t="inlineStr">
+        <is>
+          <t>業務システムからデータを取り出せるか（CSV/API等）</t>
+        </is>
+      </c>
+      <c r="E8" s="70" t="inlineStr">
+        <is>
+          <t>主要システムは出力可で一致。</t>
+        </is>
+      </c>
+      <c r="F8" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G8" s="70" t="inlineStr">
+        <is>
+          <t>回答者はESG企画室・海外BUという本社側の立場であり、34拠点それぞれのシステム連携可否を代表する調査ではない。特に古い設備を使う拠点・海外拠点では出力できないシステムが存在する可能性があり、パイロット2件のみでの一般化は根拠として弱い。</t>
+        </is>
+      </c>
+      <c r="H8" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="68" customHeight="1" s="48">
+      <c r="A9" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C9" s="69" t="inlineStr">
+        <is>
+          <t>C-22</t>
+        </is>
+      </c>
+      <c r="D9" s="70" t="inlineStr">
+        <is>
+          <t>年間で最も負荷が高い月</t>
+        </is>
+      </c>
+      <c r="E9" s="70" t="inlineStr">
+        <is>
+          <t>1〜3月がピークで一致。1月依頼・2月締切を締切設計の前提とする。</t>
+        </is>
+      </c>
+      <c r="F9" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G9" s="70" t="inlineStr">
+        <is>
+          <t>国内の決算スケジュールを前提とした回答である可能性が高く、現地の会計年度が異なる海外拠点（カレンダーイヤー決算の国等）には当てはまらないおそれがある。海外拠点分のピーク月は別途確認が必要。</t>
+        </is>
+      </c>
+      <c r="H9" s="74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="68" customHeight="1" s="48">
+      <c r="A10" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C10" s="69" t="inlineStr">
+        <is>
+          <t>C-26</t>
+        </is>
+      </c>
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>推計・概算で報告しているデータの割合</t>
+        </is>
+      </c>
+      <c r="E10" s="70" t="inlineStr">
+        <is>
+          <t>按分は小田原研究所の外部テナントに限られると把握。</t>
+        </is>
+      </c>
+      <c r="F10" s="71" t="inlineStr">
+        <is>
+          <t>理由不十分</t>
+        </is>
+      </c>
+      <c r="G10" s="70" t="inlineStr">
+        <is>
+          <t>この回答は「按分」（C-25が問う内容）について述べたものであり、C-26が問う『推計・概算報告の割合』には答えていない。設問と回答の対応がずれており、推計データの割合は実質的に未確認のまま残っている。</t>
+        </is>
+      </c>
+      <c r="H10" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="68" customHeight="1" s="48">
+      <c r="A11" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C11" s="69" t="inlineStr">
+        <is>
+          <t>C-28</t>
+        </is>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>証憑が個人PC・個人メールにしかないか</t>
+        </is>
+      </c>
+      <c r="E11" s="70" t="inlineStr">
+        <is>
+          <t>実態を把握できたため削除。メールで入手している排出係数（鹿島北共同発電、タイSAHAグループ等）や都市ガス会社への問い合わせメールも保存対象の証憑に含める。</t>
+        </is>
+      </c>
+      <c r="F11" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G11" s="70" t="inlineStr">
+        <is>
+          <t>把握できたのは具体的な2つの事例のみで、他の拠点における同様の個人管理記録の有無は未確認。判明した事例をシステム要件に反映する対応自体は適切だが、『これで全体を把握できた』とは言えない。</t>
+        </is>
+      </c>
+      <c r="H11" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="68" customHeight="1" s="48">
+      <c r="A12" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C12" s="69" t="inlineStr">
+        <is>
+          <t>C-35</t>
+        </is>
+      </c>
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>工場・現場のPC・ネットワーク環境</t>
+        </is>
+      </c>
+      <c r="E12" s="70" t="inlineStr">
+        <is>
+          <t>全拠点でPCが使え、システム入力可能で一致。</t>
+        </is>
+      </c>
+      <c r="F12" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G12" s="70" t="inlineStr">
+        <is>
+          <t>回答者（ESG企画室・海外BU）が工場現場のネットワーク環境を直接把握している立場か不明。海外工場のネットワーク制限は当初の難所チェック（H7系）でも想定していた既知の懸念点であり、現場担当者への確認なしに『全拠点で問題なし』と判断するのはリスクが残る。</t>
+        </is>
+      </c>
+      <c r="H12" s="74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="68" customHeight="1" s="48">
+      <c r="A13" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>4.難所チェック</t>
+        </is>
+      </c>
+      <c r="C13" s="69" t="inlineStr">
+        <is>
+          <t>10-01</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>開示範囲・報告範囲の解釈に迷うことがあるか</t>
+        </is>
+      </c>
+      <c r="E13" s="70" t="inlineStr">
+        <is>
+          <t>ESG企画室の回答で代替できるため、拠点への設問は不要。</t>
+        </is>
+      </c>
+      <c r="F13" s="71" t="inlineStr">
+        <is>
+          <t>理由不十分</t>
+        </is>
+      </c>
+      <c r="G13" s="70" t="inlineStr">
+        <is>
+          <t>本設問は『現場が本社ルールの解釈に迷っているか』を問うものであり、本社（ESG企画室）自身の回答で代替できる内容ではない。現場と本社の認識のズレの有無こそがこの設問の主旨であり、論理が成立していない。</t>
+        </is>
+      </c>
+      <c r="H13" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="68" customHeight="1" s="48">
+      <c r="A14" s="69" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="70" t="inlineStr">
+        <is>
+          <t>4.難所チェック</t>
+        </is>
+      </c>
+      <c r="C14" s="69" t="inlineStr">
+        <is>
+          <t>10-02</t>
+        </is>
+      </c>
+      <c r="D14" s="70" t="inlineStr">
+        <is>
+          <t>本社ルールの変更が現場まで正確に伝わらない・時差があるか</t>
+        </is>
+      </c>
+      <c r="E14" s="70" t="inlineStr">
+        <is>
+          <t>ESG企画室の回答で代替できるため、拠点への設問は不要。</t>
+        </is>
+      </c>
+      <c r="F14" s="71" t="inlineStr">
+        <is>
+          <t>理由不十分</t>
+        </is>
+      </c>
+      <c r="G14" s="70" t="inlineStr">
+        <is>
+          <t>10-01と同様の理由不備。伝達の送り手（ESG企画室）が、受け手（拠点）側の理解度・時差の実態を自己評価で代替することはできない。</t>
+        </is>
+      </c>
+      <c r="H14" s="74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="68" customHeight="1" s="48">
+      <c r="A15" s="69" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="70" t="inlineStr">
+        <is>
+          <t>4.難所チェック</t>
+        </is>
+      </c>
+      <c r="C15" s="69" t="inlineStr">
+        <is>
+          <t>10-05</t>
+        </is>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>サプライヤー・委託先・ビル管理会社からのデータ入手の遅れ</t>
+        </is>
+      </c>
+      <c r="E15" s="70" t="inlineStr">
+        <is>
+          <t>請求に直結するデータが多く遅れは稀、という評価（頻度：稀／影響度：大）を前提に設計する。</t>
+        </is>
+      </c>
+      <c r="F15" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G15" s="70" t="inlineStr">
+        <is>
+          <t>この評価は電気・ガス等の請求データを想定したものと考えられる。Scope3関連の委託先データ（輸送・廃棄物処理等、請求に基づかない情報）には同じ評価が当てはまらない可能性があり、対象範囲を明確にした上での再確認が望ましい。</t>
+        </is>
+      </c>
+      <c r="H15" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="68" customHeight="1" s="48">
+      <c r="A16" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C16" s="69" t="inlineStr">
+        <is>
+          <t>H3-04</t>
+        </is>
+      </c>
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>入力タイミング（月初何営業日目か）</t>
+        </is>
+      </c>
+      <c r="E16" s="70" t="inlineStr">
+        <is>
+          <t>リマインドのタイミングはESG企画室と調整する方針とし、月次のリマインドは不要という前提で設計する。</t>
+        </is>
+      </c>
+      <c r="F16" s="71" t="inlineStr">
+        <is>
+          <t>理由不十分</t>
+        </is>
+      </c>
+      <c r="G16" s="70" t="inlineStr">
+        <is>
+          <t>南氏自身が別項目（C-02関連）で「本設問はリマインドの要否ではなく、頻度・タイミングの強度を決めるためのもの」と説明している。今回の削除理由は要否判断（不要）にとどまっており、リマインドを実装する前提であれば必要な『いつ・どの強さで』という設計情報が確保されていない。</t>
+        </is>
+      </c>
+      <c r="H16" s="74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="68" customHeight="1" s="48">
+      <c r="A17" s="69" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C17" s="69" t="inlineStr">
+        <is>
+          <t>H3-05</t>
+        </is>
+      </c>
+      <c r="D17" s="70" t="inlineStr">
+        <is>
+          <t>締切に間に合わない月の有無</t>
+        </is>
+      </c>
+      <c r="E17" s="70" t="inlineStr">
+        <is>
+          <t>水道は2か月に1回で、12-1月請求分が1月中下旬着になり得る点を締切設計の前提に反映する。</t>
+        </is>
+      </c>
+      <c r="F17" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G17" s="70" t="inlineStr">
+        <is>
+          <t>把握できたのは特定拠点の請求サイクルの一例。他拠点（特に海外拠点や異なる契約形態の拠点）で同様に締切に間に合わない月がないかは未確認。締切設計は全拠点に影響するため、他の請求パターンの有無を確認すべき。</t>
+        </is>
+      </c>
+      <c r="H17" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="68" customHeight="1" s="48">
+      <c r="A18" s="69" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C18" s="69" t="inlineStr">
+        <is>
+          <t>H3-08</t>
+        </is>
+      </c>
+      <c r="D18" s="70" t="inlineStr">
+        <is>
+          <t>組織変更・拠点統廃合時のデータ連続性の担保方法</t>
+        </is>
+      </c>
+      <c r="E18" s="70" t="inlineStr">
+        <is>
+          <t>拠点単位での連続性は求められないとのことなので、不要。</t>
+        </is>
+      </c>
+      <c r="F18" s="71" t="inlineStr">
+        <is>
+          <t>理由が誤りの可能性</t>
+        </is>
+      </c>
+      <c r="G18" s="70" t="inlineStr">
+        <is>
+          <t>本設問は『SSBJの過年度比較の根幹』に関わるものとして影響度「高」に設定されていた。SSBJ・ISSB系の開示基準は、組織再編後もベースイヤーとの比較可能性の確保（再計算・遡及）を求めるのが一般的であり、これは拠点の意向とは独立した規制要件である。拠点担当者が『不要』と答えたとしても、開示基準側の要求が優先されるべきで、この削除判断はコンプライアンス上のリスクを残す。</t>
+        </is>
+      </c>
+      <c r="H18" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="68" customHeight="1" s="48">
+      <c r="A19" s="69" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C19" s="69" t="inlineStr">
+        <is>
+          <t>H4-01</t>
+        </is>
+      </c>
+      <c r="D19" s="70" t="inlineStr">
+        <is>
+          <t>使用係数の名称・出典・年度版</t>
+        </is>
+      </c>
+      <c r="E19" s="70" t="inlineStr">
+        <is>
+          <t>係数は本社一括管理のため不要と判断。</t>
+        </is>
+      </c>
+      <c r="F19" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G19" s="70" t="inlineStr">
+        <is>
+          <t>C-07と同じ根拠の誤り。海外拠点はGHGプロトコル準拠の係数を独自に使用しており、必ずしも本社一括管理ではない。係数の出典・版の全量把握を省略すると、監査で説明できない係数が残るリスクがある。</t>
+        </is>
+      </c>
+      <c r="H19" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="68" customHeight="1" s="48">
+      <c r="A20" s="69" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C20" s="69" t="inlineStr">
+        <is>
+          <t>H4-07</t>
+        </is>
+      </c>
+      <c r="D20" s="70" t="inlineStr">
+        <is>
+          <t>小さな排出源の集計の網羅性</t>
+        </is>
+      </c>
+      <c r="E20" s="70" t="inlineStr">
+        <is>
+          <t>回答の妥当性確認が現実的に困難という前提に立ち、小規模な排出源は本社側でチェックリスト化して補う方針とする。</t>
+        </is>
+      </c>
+      <c r="F20" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G20" s="70" t="inlineStr">
+        <is>
+          <t>対応の方向性自体は妥当だが、本社（ESG企画室）が34拠点すべての小口設備（社有車・非常用発電機・LPGボンダ等）を正確に把握できるかは未検証。特に海外拠点の小口設備は本社の把握が手薄になりがちで、バウンダリの完全性リスクが残る。</t>
+        </is>
+      </c>
+      <c r="H20" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="68" customHeight="1" s="48">
+      <c r="A21" s="69" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C21" s="69" t="inlineStr">
+        <is>
+          <t>H4-08</t>
+        </is>
+      </c>
+      <c r="D21" s="70" t="inlineStr">
+        <is>
+          <t>冷媒（フロン類）の充填・漏えい量の把握方法</t>
+        </is>
+      </c>
+      <c r="E21" s="70" t="inlineStr">
+        <is>
+          <t>充填作業記録（紙をPDF化）を証憑として扱う前提で要件化する。海外は報告対象外とする。</t>
+        </is>
+      </c>
+      <c r="F21" s="71" t="inlineStr">
+        <is>
+          <t>根拠不明確</t>
+        </is>
+      </c>
+      <c r="G21" s="70" t="inlineStr">
+        <is>
+          <t>『海外は報告対象外』とする根拠が示されていない。海外の製造拠点も空調・冷却設備で冷媒を使用している可能性が高く、Scope1漏えい排出の完全性の観点で、対象外とする判断が妥当か確認が必要。</t>
+        </is>
+      </c>
+      <c r="H21" s="74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="68" customHeight="1" s="48">
+      <c r="A22" s="69" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C22" s="69" t="inlineStr">
+        <is>
+          <t>H4-09</t>
+        </is>
+      </c>
+      <c r="D22" s="70" t="inlineStr">
+        <is>
+          <t>水（取水源別計測・排水量把握）の実態</t>
+        </is>
+      </c>
+      <c r="E22" s="70" t="inlineStr">
+        <is>
+          <t>原則すべてメーター記録。地下水は料金が発生しない場合があるため、計測の有無だけ確認できる形にする。</t>
+        </is>
+      </c>
+      <c r="F22" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存（軽微）</t>
+        </is>
+      </c>
+      <c r="G22" s="70" t="inlineStr">
+        <is>
+          <t>実務上の妥当な簡略化ではあるが、地下水を多く使用する拠点があれば、料金データがなく使用量を過小評価したまま開示数値に反映されるおそれがある。水リスクの開示重要性が高まる中、軽微だが留意点として残す。</t>
+        </is>
+      </c>
+      <c r="H22" s="74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="68" customHeight="1" s="48">
+      <c r="A23" s="69" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C23" s="69" t="inlineStr">
+        <is>
+          <t>H5-01</t>
+        </is>
+      </c>
+      <c r="D23" s="70" t="inlineStr">
+        <is>
+          <t>証憑の種類・保管場所の全量</t>
+        </is>
+      </c>
+      <c r="E23" s="70" t="inlineStr">
+        <is>
+          <t>証憑の種類・保管場所は把握できたため、保管先の集約範囲を要件に反映する。</t>
+        </is>
+      </c>
+      <c r="F23" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G23" s="70" t="inlineStr">
+        <is>
+          <t>シート2・C-28と同様の問題。パイロット2拠点の実態把握のみでは、他拠点の個人管理・ローカル保管の実態を捉えきれない。移行計画の完全性（個人PC等にしかない証憑の消失リスク）に関わる影響度「高」の項目であり、全拠点的な把握なしに設問を外すのはリスクが残る。</t>
+        </is>
+      </c>
+      <c r="H23" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="68" customHeight="1" s="48">
+      <c r="A24" s="69" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C24" s="69" t="inlineStr">
+        <is>
+          <t>H6-02</t>
+        </is>
+      </c>
+      <c r="D24" s="70" t="inlineStr">
+        <is>
+          <t>異常値の定義・閾値と発見時の対応者</t>
+        </is>
+      </c>
+      <c r="E24" s="70" t="inlineStr">
+        <is>
+          <t>閾値はESG企画室の机上設定で進める。</t>
+        </is>
+      </c>
+      <c r="F24" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存（理由自体は妥当だがリスク未解消）</t>
+        </is>
+      </c>
+      <c r="G24" s="70" t="inlineStr">
+        <is>
+          <t>この判断は、当初の設問が指摘していたリスク（閾値が机上設定になり拠点の実態を反映しない）を解消するものではなく、そのリスクを受け入れる内容になっている。少なくとも初期閾値は保守的に設定し、運用開始後に拠点別の実態に応じて調整する仕組みを残すことを推奨する。</t>
+        </is>
+      </c>
+      <c r="H24" s="74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="68" customHeight="1" s="48">
+      <c r="A25" s="69" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C25" s="69" t="inlineStr">
+        <is>
+          <t>H9-02</t>
+        </is>
+      </c>
+      <c r="D25" s="70" t="inlineStr">
+        <is>
+          <t>現地排出係数の種類と入手元</t>
+        </is>
+      </c>
+      <c r="E25" s="70" t="inlineStr">
+        <is>
+          <t>既に検証を受けている係数を正とする前提で進める。</t>
+        </is>
+      </c>
+      <c r="F25" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G25" s="70" t="inlineStr">
+        <is>
+          <t>H4-01・C-07と同根の問題。『既に検証済み』の対象が具体的にどの拠点・年度までを指すか不明確。第三者保証（SGS等）は歴史的に国内拠点を中心に進んできた可能性があり、全海外拠点の係数が検証済みとは限らない。</t>
+        </is>
+      </c>
+      <c r="H25" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="68" customHeight="1" s="48">
+      <c r="A26" s="69" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C26" s="69" t="inlineStr">
+        <is>
+          <t>H9-05</t>
+        </is>
+      </c>
+      <c r="D26" s="70" t="inlineStr">
+        <is>
+          <t>現地事情（停電・通信障害等）による欠測・遅延の頻度</t>
+        </is>
+      </c>
+      <c r="E26" s="70" t="inlineStr">
+        <is>
+          <t>バングラデシュでも致命的な遅延はない想定とのことなので、オフライン前提の機能は見送る。</t>
+        </is>
+      </c>
+      <c r="F26" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G26" s="70" t="inlineStr">
+        <is>
+          <t>バングラデシュは一般的に電力・通信インフラの課題が指摘されやすい国であり、この回答が現場の実態を正確に反映しているか、他の新興国拠点も含め再確認の余地がある。回答者（海外BU）が現地の日常的な運用実態まで把握しているかは不明。</t>
+        </is>
+      </c>
+      <c r="H26" s="74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="68" customHeight="1" s="48">
+      <c r="A27" s="69" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C27" s="69" t="inlineStr">
+        <is>
+          <t>H9-07</t>
+        </is>
+      </c>
+      <c r="D27" s="70" t="inlineStr">
+        <is>
+          <t>現地経営層（社長・工場長）の関与度・承認追加の実現性</t>
+        </is>
+      </c>
+      <c r="E27" s="70" t="inlineStr">
+        <is>
+          <t>承認のフローとして不要であるという回答と判断。</t>
+        </is>
+      </c>
+      <c r="F27" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G27" s="70" t="inlineStr">
+        <is>
+          <t>一部の国・地域ではESGデータに対する現地の法定代表者の承認・確認が法制度上求められる可能性がある（EUのCSRD等、域内規制の広がり）。『承認フローとして不要』と一律に判断すると、現地の法制度によってはコンプライアンス上の問題になり得る。</t>
+        </is>
+      </c>
+      <c r="H27" s="74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" s="48">
+      <c r="A29" s="75" t="inlineStr">
+        <is>
+          <t>【削除に同意 37件】理由が妥当と判断し、リスク一覧からは除外した設問（参考記録）</t>
+        </is>
+      </c>
+      <c r="B29" s="76" t="n"/>
+      <c r="C29" s="76" t="n"/>
+      <c r="D29" s="76" t="n"/>
+      <c r="E29" s="76" t="n"/>
+      <c r="F29" s="76" t="n"/>
+      <c r="G29" s="76" t="n"/>
+      <c r="H29" s="76" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" s="48">
+      <c r="B30" s="68" t="inlineStr">
+        <is>
+          <t>シート</t>
+        </is>
+      </c>
+      <c r="C30" s="68" t="inlineStr">
+        <is>
+          <t>元ID</t>
+        </is>
+      </c>
+      <c r="D30" s="68" t="inlineStr">
+        <is>
+          <t>元の設問（要旨）</t>
+        </is>
+      </c>
+      <c r="E30" s="68" t="inlineStr">
+        <is>
+          <t>削除理由の要旨</t>
+        </is>
+      </c>
+      <c r="G30" s="68" t="inlineStr">
+        <is>
+          <t>同意コメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1" s="48">
+      <c r="B31" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C31" s="69" t="inlineStr">
         <is>
           <t>C-01</t>
         </is>
       </c>
-      <c r="D6" s="68" t="inlineStr">
-        <is>
-          <t>データ入力・報告の手順書はあるか</t>
-        </is>
-      </c>
-      <c r="E6" s="68" t="inlineStr">
-        <is>
-          <t>ESG企画室・海外BUとも「報告手順書はない」と回答したため一致とみなし、全拠点「手順書なし・属人」を前提に設計を進める。</t>
-        </is>
-      </c>
-      <c r="F6" s="68" t="inlineStr">
-        <is>
-          <t>実際に手順書を持つ拠点があった場合、その業務フローの文書化根拠を活かせず、稼働後に個別のヒアリングをやり直す手間が生じる。</t>
-        </is>
-      </c>
-      <c r="G6" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H6" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1" s="48">
-      <c r="A7" s="67" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="68" t="inlineStr">
+      <c r="D31" s="70" t="inlineStr">
+        <is>
+          <t>手順書の有無</t>
+        </is>
+      </c>
+      <c r="E31" s="70" t="inlineStr">
+        <is>
+          <t>両拠点とも手順書なしで一致</t>
+        </is>
+      </c>
+      <c r="G31" s="70" t="inlineStr">
+        <is>
+          <t>仮に手順書がある拠点があっても、被る不利益は個別ヒアリングの手間程度で小さい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1" s="48">
+      <c r="B32" s="70" t="inlineStr">
         <is>
           <t>3.コア設問</t>
         </is>
       </c>
-      <c r="C7" s="67" t="inlineStr">
-        <is>
-          <t>C-03</t>
-        </is>
-      </c>
-      <c r="D7" s="68" t="inlineStr">
-        <is>
-          <t>使用期間と請求期間のズレの処理方法</t>
-        </is>
-      </c>
-      <c r="E7" s="68" t="inlineStr">
-        <is>
-          <t>両拠点とも「日割り計算はせず請求期間のまま報告」で一致。全拠点にこの前提を適用する。</t>
-        </is>
-      </c>
-      <c r="F7" s="68" t="inlineStr">
-        <is>
-          <t>実際に日割り処理をしている拠点があった場合、計算ロジックに単一方式しか実装されていないと、その拠点のデータを正しく扱えず、按分機能を追加開発する費用が発生する。</t>
-        </is>
-      </c>
-      <c r="G7" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H7" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1" s="48">
-      <c r="A8" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="68" t="inlineStr">
+      <c r="C32" s="69" t="inlineStr">
+        <is>
+          <t>C-09</t>
+        </is>
+      </c>
+      <c r="D32" s="70" t="inlineStr">
+        <is>
+          <t>証憑の保管形式</t>
+        </is>
+      </c>
+      <c r="E32" s="70" t="inlineStr">
+        <is>
+          <t>PDF・Excelが中心と把握</t>
+        </is>
+      </c>
+      <c r="G32" s="70" t="inlineStr">
+        <is>
+          <t>低リスク。仮に紙中心の拠点があっても保管容量を多めに見ておけば対応可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1" s="48">
+      <c r="B33" s="70" t="inlineStr">
         <is>
           <t>3.コア設問</t>
         </is>
       </c>
-      <c r="C8" s="67" t="inlineStr">
-        <is>
-          <t>C-07</t>
-        </is>
-      </c>
-      <c r="D8" s="68" t="inlineStr">
-        <is>
-          <t>拠点独自の係数・ルールの使用有無</t>
-        </is>
-      </c>
-      <c r="E8" s="68" t="inlineStr">
-        <is>
-          <t>「係数・ルールは本社一括管理」で一致。拠点独自の係数は想定しない前提で設計する。</t>
-        </is>
-      </c>
-      <c r="F8" s="68" t="inlineStr">
-        <is>
-          <t>独自係数を使っている拠点が実際に存在した場合、システムにその係数の設定機能がなく、数値の不整合が生じ、監査で説明できなくなる。</t>
-        </is>
-      </c>
-      <c r="G8" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H8" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1" s="48">
-      <c r="A9" s="67" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="68" t="inlineStr">
+      <c r="C33" s="69" t="inlineStr">
+        <is>
+          <t>C-13</t>
+        </is>
+      </c>
+      <c r="D33" s="70" t="inlineStr">
+        <is>
+          <t>変更履歴の有無</t>
+        </is>
+      </c>
+      <c r="E33" s="70" t="inlineStr">
+        <is>
+          <t>変更履歴を必須要件として確定</t>
+        </is>
+      </c>
+      <c r="G33" s="70" t="inlineStr">
+        <is>
+          <t>履歴機能を全拠点前提で実装するため、実態が違っても上位互換で吸収できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1" s="48">
+      <c r="B34" s="70" t="inlineStr">
         <is>
           <t>3.コア設問</t>
         </is>
       </c>
-      <c r="C9" s="67" t="inlineStr">
-        <is>
-          <t>C-09</t>
-        </is>
-      </c>
-      <c r="D9" s="68" t="inlineStr">
-        <is>
-          <t>数値の根拠となる証憑の保管形式</t>
-        </is>
-      </c>
-      <c r="E9" s="68" t="inlineStr">
-        <is>
-          <t>「PDFとExcelが中心（まれにpng/jpeg）」と把握。この前提で保管の仕組みを設計する。</t>
-        </is>
-      </c>
-      <c r="F9" s="68" t="inlineStr">
-        <is>
-          <t>紙が中心の拠点があった場合、スキャン運用・保存容量の設計が不足し、稼働後に追加のスキャン作業・ストレージ増設が必要になる。</t>
-        </is>
-      </c>
-      <c r="G9" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H9" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1" s="48">
-      <c r="A10" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="68" t="inlineStr">
+      <c r="C34" s="69" t="inlineStr">
+        <is>
+          <t>C-23</t>
+        </is>
+      </c>
+      <c r="D34" s="70" t="inlineStr">
+        <is>
+          <t>抜け漏れ・遅延の主な原因</t>
+        </is>
+      </c>
+      <c r="E34" s="70" t="inlineStr">
+        <is>
+          <t>5つの原因を要件に反映</t>
+        </is>
+      </c>
+      <c r="G34" s="70" t="inlineStr">
+        <is>
+          <t>汎用的な原因（アラート視認性、単位換算、年始重なり等）で妥当性が高い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1" s="48">
+      <c r="B35" s="70" t="inlineStr">
         <is>
           <t>3.コア設問</t>
         </is>
       </c>
-      <c r="C10" s="67" t="inlineStr">
-        <is>
-          <t>C-13</t>
-        </is>
-      </c>
-      <c r="D10" s="68" t="inlineStr">
-        <is>
-          <t>データの変更履歴は残るか</t>
-        </is>
-      </c>
-      <c r="E10" s="68" t="inlineStr">
-        <is>
-          <t>履歴は残らない仕様と把握、かつ履歴機能の必要性にも同意が得られたため、変更履歴を必須要件として確定する。</t>
-        </is>
-      </c>
-      <c r="F10" s="68" t="inlineStr">
-        <is>
-          <t>この決定自体は保守的（機能を厚めに持つ）ため大きな漏れは小さいが、拠点固有の監査対応ルール等、履歴以外の個別要件が見過ごされる可能性がある。</t>
-        </is>
-      </c>
-      <c r="G10" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H10" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1" s="48">
-      <c r="A11" s="67" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="68" t="inlineStr">
+      <c r="C35" s="69" t="inlineStr">
+        <is>
+          <t>C-27</t>
+        </is>
+      </c>
+      <c r="D35" s="70" t="inlineStr">
+        <is>
+          <t>妥当性チェック方法</t>
+        </is>
+      </c>
+      <c r="E35" s="70" t="inlineStr">
+        <is>
+          <t>標準閾値はESG企画室が設定</t>
+        </is>
+      </c>
+      <c r="G35" s="70" t="inlineStr">
+        <is>
+          <t>現状の拠点実態に関わらず、今後の方針として妥当な決定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1" s="48">
+      <c r="B36" s="70" t="inlineStr">
         <is>
           <t>3.コア設問</t>
         </is>
       </c>
-      <c r="C11" s="67" t="inlineStr">
-        <is>
-          <t>C-14</t>
-        </is>
-      </c>
-      <c r="D11" s="68" t="inlineStr">
-        <is>
-          <t>業務システムからデータを取り出せるか</t>
-        </is>
-      </c>
-      <c r="E11" s="68" t="inlineStr">
-        <is>
-          <t>「主要システムは出力可」で一致。この前提で連携設計を進める。</t>
-        </is>
-      </c>
-      <c r="F11" s="68" t="inlineStr">
-        <is>
-          <t>出力できない拠点があった場合、連携設計から漏れて手入力前提のまま稼働し、後日判明すると連携方式全体の見直しが必要になる。</t>
-        </is>
-      </c>
-      <c r="G11" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H11" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1" s="48">
-      <c r="A12" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="68" t="inlineStr">
+      <c r="C36" s="69" t="inlineStr">
+        <is>
+          <t>C-29</t>
+        </is>
+      </c>
+      <c r="D36" s="70" t="inlineStr">
+        <is>
+          <t>証憑を探す時間</t>
+        </is>
+      </c>
+      <c r="E36" s="70" t="inlineStr">
+        <is>
+          <t>BOX運用を前提に保存・検索機能を必須化</t>
+        </is>
+      </c>
+      <c r="G36" s="70" t="inlineStr">
+        <is>
+          <t>機能を厚めに実装する対応であり、実態が違っても問題は生じにくい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1" s="48">
+      <c r="B37" s="70" t="inlineStr">
         <is>
           <t>3.コア設問</t>
         </is>
       </c>
-      <c r="C12" s="67" t="inlineStr">
-        <is>
-          <t>C-22</t>
-        </is>
-      </c>
-      <c r="D12" s="68" t="inlineStr">
-        <is>
-          <t>年間で最も負荷が高い月</t>
-        </is>
-      </c>
-      <c r="E12" s="68" t="inlineStr">
-        <is>
-          <t>「1〜3月がピーク」で一致。1月依頼・2月締切を締切設計の前提とする。</t>
-        </is>
-      </c>
-      <c r="F12" s="68" t="inlineStr">
-        <is>
-          <t>決算月がずれる拠点（一部海外拠点等）があった場合、締切カレンダーが実態と合わず、その拠点だけ常に遅延が発生する。</t>
-        </is>
-      </c>
-      <c r="G12" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H12" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1" s="48">
-      <c r="A13" s="67" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="68" t="inlineStr">
+      <c r="C37" s="69" t="inlineStr">
+        <is>
+          <t>C-31</t>
+        </is>
+      </c>
+      <c r="D37" s="70" t="inlineStr">
+        <is>
+          <t>確定・ロックの概念</t>
+        </is>
+      </c>
+      <c r="E37" s="70" t="inlineStr">
+        <is>
+          <t>本社が確定・ロックを行っている</t>
+        </is>
+      </c>
+      <c r="G37" s="70" t="inlineStr">
+        <is>
+          <t>本社主導の統制であり、拠点側の実態に依存しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1" s="48">
+      <c r="B38" s="70" t="inlineStr">
         <is>
           <t>3.コア設問</t>
         </is>
       </c>
-      <c r="C13" s="67" t="inlineStr">
-        <is>
-          <t>C-23</t>
-        </is>
-      </c>
-      <c r="D13" s="68" t="inlineStr">
-        <is>
-          <t>抜け漏れ・遅延が起きる主な原因</t>
-        </is>
-      </c>
-      <c r="E13" s="68" t="inlineStr">
-        <is>
-          <t>両拠点の回答から5つの原因（作業手順の想起コスト、アラートの視認性、単位換算・複数書類の集計、年1回ゆえの予定化されにくさ、依頼時期と年始・旧正月の重なり）を要件に反映する。</t>
-        </is>
-      </c>
-      <c r="F13" s="68" t="inlineStr">
-        <is>
-          <t>挙げられていない別の原因（拠点特有のシステム障害等）を持つ拠点があった場合、その拠点の遅延は改善されないまま残る。</t>
-        </is>
-      </c>
-      <c r="G13" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H13" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1" s="48">
-      <c r="A14" s="67" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="68" t="inlineStr">
+      <c r="C38" s="69" t="inlineStr">
+        <is>
+          <t>C-34</t>
+        </is>
+      </c>
+      <c r="D38" s="70" t="inlineStr">
+        <is>
+          <t>スマートメーター等の有無</t>
+        </is>
+      </c>
+      <c r="E38" s="70" t="inlineStr">
+        <is>
+          <t>自動計測は対象外、OCR検討に振替</t>
+        </is>
+      </c>
+      <c r="G38" s="70" t="inlineStr">
+        <is>
+          <t>意図的なスコープ決定であり、機会損失は自覚的に受容されている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1" s="48">
+      <c r="B39" s="70" t="inlineStr">
         <is>
           <t>3.コア設問</t>
         </is>
       </c>
-      <c r="C14" s="67" t="inlineStr">
-        <is>
-          <t>C-26</t>
-        </is>
-      </c>
-      <c r="D14" s="68" t="inlineStr">
-        <is>
-          <t>推計・概算で報告している割合</t>
-        </is>
-      </c>
-      <c r="E14" s="68" t="inlineStr">
-        <is>
-          <t>「按分は小田原研究所の外部テナントに限られる」と把握。</t>
-        </is>
-      </c>
-      <c r="F14" s="68" t="inlineStr">
-        <is>
-          <t>他拠点にも推計・按分が必要な項目があった場合、推計値の管理機能（実測/推計フラグ）がないため、精度の低いデータがそのまま開示数値に使われる。</t>
-        </is>
-      </c>
-      <c r="G14" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H14" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1" s="48">
-      <c r="A15" s="67" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="68" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C15" s="67" t="inlineStr">
-        <is>
-          <t>C-27</t>
-        </is>
-      </c>
-      <c r="D15" s="68" t="inlineStr">
-        <is>
-          <t>計算結果の妥当性チェック方法</t>
-        </is>
-      </c>
-      <c r="E15" s="68" t="inlineStr">
-        <is>
-          <t>「標準閾値はESG企画室が設定」する前提とし、拠点への設問は削除する。</t>
-        </is>
-      </c>
-      <c r="F15" s="68" t="inlineStr">
-        <is>
-          <t>拠点ごとの特殊な変動要因（季節性の強い拠点等）を考慮しない一律の閾値になり、異常値の誤検知・見逃しが増える拠点が出る。</t>
-        </is>
-      </c>
-      <c r="G15" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H15" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1" s="48">
-      <c r="A16" s="67" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="68" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C16" s="67" t="inlineStr">
-        <is>
-          <t>C-28</t>
-        </is>
-      </c>
-      <c r="D16" s="68" t="inlineStr">
-        <is>
-          <t>証憑が個人PC・個人メールにしかないか</t>
-        </is>
-      </c>
-      <c r="E16" s="68" t="inlineStr">
-        <is>
-          <t>把握できた証憑（電力共同発電・海外グループ・都市ガス問い合わせメール等）のみ保存対象に含める。</t>
-        </is>
-      </c>
-      <c r="F16" s="68" t="inlineStr">
-        <is>
-          <t>把握できていない個人PC上の証憑（他拠点の担当者が個人管理しているもの）が移行前に退避されず、あとで検証時に証憑を提示できなくなる。</t>
-        </is>
-      </c>
-      <c r="G16" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H16" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="46" customHeight="1" s="48">
-      <c r="A17" s="67" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="68" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C17" s="67" t="inlineStr">
-        <is>
-          <t>C-29</t>
-        </is>
-      </c>
-      <c r="D17" s="68" t="inlineStr">
-        <is>
-          <t>証憑を探すのにかかった時間</t>
-        </is>
-      </c>
-      <c r="E17" s="68" t="inlineStr">
-        <is>
-          <t>「現行システムの証憑保存機能が使えずBOX運用で対応」と把握。証憑の保存・検索機能を必須要件として確定する。</t>
-        </is>
-      </c>
-      <c r="F17" s="68" t="inlineStr">
-        <is>
-          <t>BOX以外の運用をしている拠点があった場合、そのデータの移行方法が計画から漏れる。</t>
-        </is>
-      </c>
-      <c r="G17" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H17" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="46" customHeight="1" s="48">
-      <c r="A18" s="67" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="68" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C18" s="67" t="inlineStr">
-        <is>
-          <t>C-31</t>
-        </is>
-      </c>
-      <c r="D18" s="68" t="inlineStr">
-        <is>
-          <t>データの確定・ロックの概念</t>
-        </is>
-      </c>
-      <c r="E18" s="68" t="inlineStr">
-        <is>
-          <t>「本社が確定・ロックを行っている」で一致。</t>
-        </is>
-      </c>
-      <c r="F18" s="68" t="inlineStr">
-        <is>
-          <t>拠点側で独自にロック・確定運用をしている（または全くしていない）場合、本社機能だけでは統制が効かず、書き換えリスクが残る拠点が見過ごされる。</t>
-        </is>
-      </c>
-      <c r="G18" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H18" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="46" customHeight="1" s="48">
-      <c r="A19" s="67" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="68" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C19" s="67" t="inlineStr">
-        <is>
-          <t>C-34</t>
-        </is>
-      </c>
-      <c r="D19" s="68" t="inlineStr">
-        <is>
-          <t>スマートメーター・BEMS等の有無</t>
-        </is>
-      </c>
-      <c r="E19" s="68" t="inlineStr">
-        <is>
-          <t>自動計測は投資規模と取得範囲の面で対象外とし、請求書のOCR検討に振り替える。</t>
-        </is>
-      </c>
-      <c r="F19" s="68" t="inlineStr">
-        <is>
-          <t>既にスマートメーター等を導入している拠点があった場合、自動連携できるにもかかわらず手入力運用のままとなり、自動化の効果を取り損なう。</t>
-        </is>
-      </c>
-      <c r="G19" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H19" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="46" customHeight="1" s="48">
-      <c r="A20" s="67" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="68" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C20" s="67" t="inlineStr">
-        <is>
-          <t>C-35</t>
-        </is>
-      </c>
-      <c r="D20" s="68" t="inlineStr">
-        <is>
-          <t>工場・現場のPC・ネットワーク環境</t>
-        </is>
-      </c>
-      <c r="E20" s="68" t="inlineStr">
-        <is>
-          <t>「全拠点でPCが使え、システム入力可能」で一致。</t>
-        </is>
-      </c>
-      <c r="F20" s="68" t="inlineStr">
-        <is>
-          <t>実際にネットワーク制限やPC不足がある拠点（海外の一部拠点等）があった場合、稼働後に「入力できない」という運用トラブルが発生する。</t>
-        </is>
-      </c>
-      <c r="G20" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H20" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="46" customHeight="1" s="48">
-      <c r="A21" s="67" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="68" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C21" s="67" t="inlineStr">
+      <c r="C39" s="69" t="inlineStr">
         <is>
           <t>C-37</t>
         </is>
       </c>
-      <c r="D21" s="68" t="inlineStr">
-        <is>
-          <t>「自分しかできない」業務の有無</t>
-        </is>
-      </c>
-      <c r="E21" s="68" t="inlineStr">
-        <is>
-          <t>「一部属人化している」前提で、マニュアル整備を導入時のタスクとして要件に含める。</t>
-        </is>
-      </c>
-      <c r="F21" s="68" t="inlineStr">
-        <is>
-          <t>「ほぼ全て属人化」というより深刻な拠点があった場合、マニュアル整備だけでは引き継ぎリスクが解消されない。</t>
-        </is>
-      </c>
-      <c r="G21" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H21" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="46" customHeight="1" s="48">
-      <c r="A22" s="67" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="68" t="inlineStr">
+      <c r="D39" s="70" t="inlineStr">
+        <is>
+          <t>属人化の有無</t>
+        </is>
+      </c>
+      <c r="E39" s="70" t="inlineStr">
+        <is>
+          <t>一部属人化前提でマニュアル整備を要件化</t>
+        </is>
+      </c>
+      <c r="G39" s="70" t="inlineStr">
+        <is>
+          <t>保守的な前提で対応するため、実態が多少違っても支障は小さい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1" s="48">
+      <c r="B40" s="70" t="inlineStr">
         <is>
           <t>4.難所チェック</t>
         </is>
       </c>
-      <c r="C22" s="67" t="inlineStr">
-        <is>
-          <t>10-01</t>
-        </is>
-      </c>
-      <c r="D22" s="68" t="inlineStr">
-        <is>
-          <t>開示範囲の解釈に迷うか</t>
-        </is>
-      </c>
-      <c r="E22" s="68" t="inlineStr">
-        <is>
-          <t>ESG企画室の回答で代替できるため、拠点への設問は不要と判断。</t>
-        </is>
-      </c>
-      <c r="F22" s="68" t="inlineStr">
-        <is>
-          <t>拠点側で本社ルールの解釈に迷っている実態が個別に拾えず、拠点ごとに異なる解釈で運用され続ける。</t>
-        </is>
-      </c>
-      <c r="G22" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H22" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="46" customHeight="1" s="48">
-      <c r="A23" s="67" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="68" t="inlineStr">
+      <c r="C40" s="69" t="inlineStr">
+        <is>
+          <t>10-06</t>
+        </is>
+      </c>
+      <c r="D40" s="70" t="inlineStr">
+        <is>
+          <t>抜け漏れの構造的発生</t>
+        </is>
+      </c>
+      <c r="E40" s="70" t="inlineStr">
+        <is>
+          <t>未然防止でなく事後の早期修正で担保</t>
+        </is>
+      </c>
+      <c r="G40" s="70" t="inlineStr">
+        <is>
+          <t>リスクを無視せず、別の仕組み（早期修正）で正面から対応している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1" s="48">
+      <c r="B41" s="70" t="inlineStr">
         <is>
           <t>4.難所チェック</t>
         </is>
       </c>
-      <c r="C23" s="67" t="inlineStr">
-        <is>
-          <t>10-02</t>
-        </is>
-      </c>
-      <c r="D23" s="68" t="inlineStr">
-        <is>
-          <t>本社ルール変更の伝達の時差</t>
-        </is>
-      </c>
-      <c r="E23" s="68" t="inlineStr">
-        <is>
-          <t>ESG企画室の回答で代替できるため、拠点への設問は不要と判断。</t>
-        </is>
-      </c>
-      <c r="F23" s="68" t="inlineStr">
-        <is>
-          <t>実際の伝達の遅れ・漏れの程度が拠点ごとに把握されず、周知の仕組みの設計が不十分になる。</t>
-        </is>
-      </c>
-      <c r="G23" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H23" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="46" customHeight="1" s="48">
-      <c r="A24" s="67" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="68" t="inlineStr">
+      <c r="C41" s="69" t="inlineStr">
+        <is>
+          <t>10-07</t>
+        </is>
+      </c>
+      <c r="D41" s="70" t="inlineStr">
+        <is>
+          <t>単位換算・按分の計算ミス</t>
+        </is>
+      </c>
+      <c r="E41" s="70" t="inlineStr">
+        <is>
+          <t>実績（毎年1〜2拠点で発生）を閾値設計に反映</t>
+        </is>
+      </c>
+      <c r="G41" s="70" t="inlineStr">
+        <is>
+          <t>エビデンスに基づく設計判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1" s="48">
+      <c r="B42" s="70" t="inlineStr">
         <is>
           <t>4.難所チェック</t>
         </is>
       </c>
-      <c r="C24" s="67" t="inlineStr">
-        <is>
-          <t>10-05</t>
-        </is>
-      </c>
-      <c r="D24" s="68" t="inlineStr">
-        <is>
-          <t>外部（サプライヤー等）からのデータ入手の遅れ</t>
-        </is>
-      </c>
-      <c r="E24" s="68" t="inlineStr">
-        <is>
-          <t>「頻度：稀／影響度：大」という評価を全拠点の前提とする。</t>
-        </is>
-      </c>
-      <c r="F24" s="68" t="inlineStr">
-        <is>
-          <t>委託先が多い等、特定拠点で実際には頻発している場合、外部データ連携の優先度が過小評価される。</t>
-        </is>
-      </c>
-      <c r="G24" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H24" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="46" customHeight="1" s="48">
-      <c r="A25" s="67" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="68" t="inlineStr">
+      <c r="C42" s="69" t="inlineStr">
+        <is>
+          <t>10-08</t>
+        </is>
+      </c>
+      <c r="D42" s="70" t="inlineStr">
+        <is>
+          <t>異常値照会の往復</t>
+        </is>
+      </c>
+      <c r="E42" s="70" t="inlineStr">
+        <is>
+          <t>異常値照会機能を優先度高い要件とする</t>
+        </is>
+      </c>
+      <c r="G42" s="70" t="inlineStr">
+        <is>
+          <t>リスクを認識した上で機能として正面から対応している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="34" customHeight="1" s="48">
+      <c r="B43" s="70" t="inlineStr">
         <is>
           <t>4.難所チェック</t>
         </is>
       </c>
-      <c r="C25" s="67" t="inlineStr">
-        <is>
-          <t>10-06</t>
-        </is>
-      </c>
-      <c r="D25" s="68" t="inlineStr">
-        <is>
-          <t>抜け漏れの構造的発生</t>
-        </is>
-      </c>
-      <c r="E25" s="68" t="inlineStr">
-        <is>
-          <t>「未然の発見は困難」という前提に立ち、検証で誤りが見つかった際に素早く修正できることを要件として担保する。</t>
-        </is>
-      </c>
-      <c r="F25" s="68" t="inlineStr">
-        <is>
-          <t>特定拠点で構造的な抜け漏れ（小口設備の登録漏れ等）が特に多い場合、その拠点だけ検証後の修正対応に恒常的な負荷が生じる。</t>
-        </is>
-      </c>
-      <c r="G25" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H25" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="46" customHeight="1" s="48">
-      <c r="A26" s="67" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="68" t="inlineStr">
+      <c r="C43" s="69" t="inlineStr">
+        <is>
+          <t>10-09</t>
+        </is>
+      </c>
+      <c r="D43" s="70" t="inlineStr">
+        <is>
+          <t>再計算への不安</t>
+        </is>
+      </c>
+      <c r="E43" s="70" t="inlineStr">
+        <is>
+          <t>拠点は計算していないため本社機能として設計</t>
+        </is>
+      </c>
+      <c r="G43" s="70" t="inlineStr">
+        <is>
+          <t>C-06が引き続き生きた設問として残り、実態と異なる拠点があれば別途捕捉される安全網がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1" s="48">
+      <c r="B44" s="70" t="inlineStr">
         <is>
           <t>4.難所チェック</t>
         </is>
       </c>
-      <c r="C26" s="67" t="inlineStr">
-        <is>
-          <t>10-07</t>
-        </is>
-      </c>
-      <c r="D26" s="68" t="inlineStr">
-        <is>
-          <t>単位換算・按分の計算ミス</t>
-        </is>
-      </c>
-      <c r="E26" s="68" t="inlineStr">
-        <is>
-          <t>「k／M等1000倍の換算ミスが毎年1〜2拠点で発生」という実績を、入力時チェックの閾値設計に反映する。</t>
-        </is>
-      </c>
-      <c r="F26" s="68" t="inlineStr">
-        <is>
-          <t>想定より多い拠点で発生する場合、入力チェックの閾値だけでは防げず、誤った数値が開示される。</t>
-        </is>
-      </c>
-      <c r="G26" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H26" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="46" customHeight="1" s="48">
-      <c r="A27" s="67" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="68" t="inlineStr">
+      <c r="C44" s="69" t="inlineStr">
+        <is>
+          <t>10-11</t>
+        </is>
+      </c>
+      <c r="D44" s="70" t="inlineStr">
+        <is>
+          <t>証拠探しの負荷</t>
+        </is>
+      </c>
+      <c r="E44" s="70" t="inlineStr">
+        <is>
+          <t>国内浸透・海外未浸透を移行計画の前提</t>
+        </is>
+      </c>
+      <c r="G44" s="70" t="inlineStr">
+        <is>
+          <t>結果に誤りがあっても移行期間の見積り誤差程度で、影響は軽微。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1" s="48">
+      <c r="B45" s="70" t="inlineStr">
         <is>
           <t>4.難所チェック</t>
         </is>
       </c>
-      <c r="C27" s="67" t="inlineStr">
-        <is>
-          <t>10-08</t>
-        </is>
-      </c>
-      <c r="D27" s="68" t="inlineStr">
-        <is>
-          <t>異常値の照会・確認での本社との往復</t>
-        </is>
-      </c>
-      <c r="E27" s="68" t="inlineStr">
-        <is>
-          <t>「毎年必ず発生し、1拠点の遅れが全体の確定を遅らせる」という評価を踏まえ、異常値の照会機能を優先度の高い要件とする。</t>
-        </is>
-      </c>
-      <c r="F27" s="68" t="inlineStr">
-        <is>
-          <t>特定拠点で往復頻度が特に高い場合、その拠点向けの追加サポートが計画されず、確定作業の遅延が偏って発生する。</t>
-        </is>
-      </c>
-      <c r="G27" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H27" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="46" customHeight="1" s="48">
-      <c r="A28" s="67" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="68" t="inlineStr">
-        <is>
-          <t>4.難所チェック</t>
-        </is>
-      </c>
-      <c r="C28" s="67" t="inlineStr">
-        <is>
-          <t>10-09</t>
-        </is>
-      </c>
-      <c r="D28" s="68" t="inlineStr">
-        <is>
-          <t>係数・ルール変更時の再計算への不安</t>
-        </is>
-      </c>
-      <c r="E28" s="68" t="inlineStr">
-        <is>
-          <t>「拠点で計算は行っていない」ため、再計算は本社側の機能として設計する。</t>
-        </is>
-      </c>
-      <c r="F28" s="68" t="inlineStr">
-        <is>
-          <t>実際に拠点側で計算をしている拠点（本社が把握していない拠点）があった場合、係数更新時の再計算機能から漏れ、その拠点の数値だけ古い係数で計算され続ける。</t>
-        </is>
-      </c>
-      <c r="G28" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H28" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="46" customHeight="1" s="48">
-      <c r="A29" s="67" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="68" t="inlineStr">
-        <is>
-          <t>4.難所チェック</t>
-        </is>
-      </c>
-      <c r="C29" s="67" t="inlineStr">
-        <is>
-          <t>10-11</t>
-        </is>
-      </c>
-      <c r="D29" s="68" t="inlineStr">
-        <is>
-          <t>監査・検証のたびの証拠探し</t>
-        </is>
-      </c>
-      <c r="E29" s="68" t="inlineStr">
-        <is>
-          <t>「国内はPDF事前提出の運用が浸透、海外は未浸透」という実態を移行計画の前提とする。</t>
-        </is>
-      </c>
-      <c r="F29" s="68" t="inlineStr">
-        <is>
-          <t>実際は国内にもPDF化が進んでいない拠点があった場合、その拠点の証憑移行に想定以上の時間がかかる。</t>
-        </is>
-      </c>
-      <c r="G29" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H29" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="46" customHeight="1" s="48">
-      <c r="A30" s="67" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="68" t="inlineStr">
-        <is>
-          <t>4.難所チェック</t>
-        </is>
-      </c>
-      <c r="C30" s="67" t="inlineStr">
+      <c r="C45" s="69" t="inlineStr">
         <is>
           <t>10-12</t>
         </is>
       </c>
-      <c r="D30" s="68" t="inlineStr">
-        <is>
-          <t>入力・報告のみでフィードバックがない</t>
-        </is>
-      </c>
-      <c r="E30" s="68" t="inlineStr">
-        <is>
-          <t>フィードバック機能は一定のニーズがあるものの、費用との見合いで判断する保留項目として整理する。</t>
-        </is>
-      </c>
-      <c r="F30" s="68" t="inlineStr">
-        <is>
-          <t>拠点側の定着意欲・活用ニーズの実態を把握しないまま先送りするため、後日「使ってもらえないシステム」になる兆候を早期に捉えられない。</t>
-        </is>
-      </c>
-      <c r="G30" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H30" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="46" customHeight="1" s="48">
-      <c r="A31" s="67" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="68" t="inlineStr">
+      <c r="D45" s="70" t="inlineStr">
+        <is>
+          <t>フィードバック機能の要否</t>
+        </is>
+      </c>
+      <c r="E45" s="70" t="inlineStr">
+        <is>
+          <t>費用対効果で判断する保留項目として整理</t>
+        </is>
+      </c>
+      <c r="G45" s="70" t="inlineStr">
+        <is>
+          <t>無視ではなく先送りの判断であり妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1" s="48">
+      <c r="B46" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C31" s="67" t="inlineStr">
+      <c r="C46" s="69" t="inlineStr">
         <is>
           <t>H3-01</t>
         </is>
       </c>
-      <c r="D31" s="68" t="inlineStr">
-        <is>
-          <t>手順書の形式・保管場所・最終更新時期</t>
-        </is>
-      </c>
-      <c r="E31" s="68" t="inlineStr">
-        <is>
-          <t>「システム入力マニュアル以外の手順書はない」で一致。</t>
-        </is>
-      </c>
-      <c r="F31" s="68" t="inlineStr">
-        <is>
-          <t>独自の手順書を持つ拠点があった場合、その内容が要件に反映されない。</t>
-        </is>
-      </c>
-      <c r="G31" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H31" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="46" customHeight="1" s="48">
-      <c r="A32" s="67" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="68" t="inlineStr">
+      <c r="D46" s="70" t="inlineStr">
+        <is>
+          <t>手順書の形式等</t>
+        </is>
+      </c>
+      <c r="E46" s="70" t="inlineStr">
+        <is>
+          <t>システム入力マニュアル以外の手順書はない</t>
+        </is>
+      </c>
+      <c r="G46" s="70" t="inlineStr">
+        <is>
+          <t>C-01と同様、低リスク。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1" s="48">
+      <c r="B47" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C32" s="67" t="inlineStr">
+      <c r="C47" s="69" t="inlineStr">
         <is>
           <t>H3-02</t>
         </is>
       </c>
-      <c r="D32" s="68" t="inlineStr">
-        <is>
-          <t>手順書と実運用の乖離・独自の工夫</t>
-        </is>
-      </c>
-      <c r="E32" s="68" t="inlineStr">
-        <is>
-          <t>手順書がないため、手順の明文化を新システム導入時のタスクとして計画に含める。</t>
-        </is>
-      </c>
-      <c r="F32" s="68" t="inlineStr">
-        <is>
-          <t>実際に手順書と異なる独自の工夫をしている拠点があった場合、その工夫（暗黙知）がシステム移行時に失われる。</t>
-        </is>
-      </c>
-      <c r="G32" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H32" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="46" customHeight="1" s="48">
-      <c r="A33" s="67" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="68" t="inlineStr">
+      <c r="D47" s="70" t="inlineStr">
+        <is>
+          <t>手順書と実態の乖離</t>
+        </is>
+      </c>
+      <c r="E47" s="70" t="inlineStr">
+        <is>
+          <t>手順書がないため明文化を導入時タスクに含める</t>
+        </is>
+      </c>
+      <c r="G47" s="70" t="inlineStr">
+        <is>
+          <t>対応がリスクを正面から解消している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="34" customHeight="1" s="48">
+      <c r="B48" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C33" s="67" t="inlineStr">
-        <is>
-          <t>H3-04</t>
-        </is>
-      </c>
-      <c r="D33" s="68" t="inlineStr">
-        <is>
-          <t>入力タイミング（月初何営業日目か）</t>
-        </is>
-      </c>
-      <c r="E33" s="68" t="inlineStr">
-        <is>
-          <t>リマインドのタイミングはESG企画室と調整する方針とし、月次のリマインドは不要という前提で設計する。</t>
-        </is>
-      </c>
-      <c r="F33" s="68" t="inlineStr">
-        <is>
-          <t>入力タイミングが遅く月次リマインドが必要な拠点があった場合、その拠点の入力遅延を早期に検知できない。</t>
-        </is>
-      </c>
-      <c r="G33" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H33" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="46" customHeight="1" s="48">
-      <c r="A34" s="67" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="68" t="inlineStr">
+      <c r="C48" s="69" t="inlineStr">
+        <is>
+          <t>H3-06</t>
+        </is>
+      </c>
+      <c r="D48" s="70" t="inlineStr">
+        <is>
+          <t>データ欠測の穴埋め方法</t>
+        </is>
+      </c>
+      <c r="E48" s="70" t="inlineStr">
+        <is>
+          <t>欠測は例外的としシステム外の補完を許容</t>
+        </is>
+      </c>
+      <c r="G48" s="70" t="inlineStr">
+        <is>
+          <t>例外処理を許容する設計判断で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1" s="48">
+      <c r="B49" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C34" s="67" t="inlineStr">
-        <is>
-          <t>H3-05</t>
-        </is>
-      </c>
-      <c r="D34" s="68" t="inlineStr">
-        <is>
-          <t>締切に間に合わない月の有無</t>
-        </is>
-      </c>
-      <c r="E34" s="68" t="inlineStr">
-        <is>
-          <t>「水道は2か月に1回で、12-1月請求分が1月中下旬着になり得る」点を締切設計の前提に反映する。</t>
-        </is>
-      </c>
-      <c r="F34" s="68" t="inlineStr">
-        <is>
-          <t>異なる請求サイクルの拠点（他のインフラ契約形態）があった場合、その拠点だけ締切に間に合わない状態が常態化する。</t>
-        </is>
-      </c>
-      <c r="G34" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H34" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="46" customHeight="1" s="48">
-      <c r="A35" s="67" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="68" t="inlineStr">
+      <c r="C49" s="69" t="inlineStr">
+        <is>
+          <t>H3-09</t>
+        </is>
+      </c>
+      <c r="D49" s="70" t="inlineStr">
+        <is>
+          <t>複数報告間の食い違い</t>
+        </is>
+      </c>
+      <c r="E49" s="70" t="inlineStr">
+        <is>
+          <t>多目的出力を要件化、様式変更対応は別途調整</t>
+        </is>
+      </c>
+      <c r="G49" s="70" t="inlineStr">
+        <is>
+          <t>主要リスク（数値不整合）は要件化で解消。CDP対応のみ先送り。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="34" customHeight="1" s="48">
+      <c r="B50" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C35" s="67" t="inlineStr">
-        <is>
-          <t>H3-06</t>
-        </is>
-      </c>
-      <c r="D35" s="68" t="inlineStr">
-        <is>
-          <t>データ欠測の典型パターンと穴埋め方法</t>
-        </is>
-      </c>
-      <c r="E35" s="68" t="inlineStr">
-        <is>
-          <t>欠測は例外的なため、システム外のやり取りでの補完を許容する設計とする。</t>
-        </is>
-      </c>
-      <c r="F35" s="68" t="inlineStr">
-        <is>
-          <t>欠測が頻発する拠点（老朽化した設備等）があった場合、システム外の補完運用に負荷が集中し、報告品質が拠点間で偏る。</t>
-        </is>
-      </c>
-      <c r="G35" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H35" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="46" customHeight="1" s="48">
-      <c r="A36" s="67" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="68" t="inlineStr">
+      <c r="C50" s="69" t="inlineStr">
+        <is>
+          <t>H4-02</t>
+        </is>
+      </c>
+      <c r="D50" s="70" t="inlineStr">
+        <is>
+          <t>係数更新時の再計算</t>
+        </is>
+      </c>
+      <c r="E50" s="70" t="inlineStr">
+        <is>
+          <t>更新・再計算可能性を要件に反映（保守的）</t>
+        </is>
+      </c>
+      <c r="G50" s="70" t="inlineStr">
+        <is>
+          <t>機能を厚めに実装する対応で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="34" customHeight="1" s="48">
+      <c r="B51" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C36" s="67" t="inlineStr">
-        <is>
-          <t>H3-08</t>
-        </is>
-      </c>
-      <c r="D36" s="68" t="inlineStr">
-        <is>
-          <t>組織変更時のデータ連続性の担保方法</t>
-        </is>
-      </c>
-      <c r="E36" s="68" t="inlineStr">
-        <is>
-          <t>拠点単位での連続性は求められないとの回答のため、不要と判断。</t>
-        </is>
-      </c>
-      <c r="F36" s="68" t="inlineStr">
-        <is>
-          <t>将来組織再編がある拠点で、過年度比較のためのデータ連続性が実は必要だった場合、SSBJの過年度比較要件を満たせなくなる。</t>
-        </is>
-      </c>
-      <c r="G36" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H36" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="46" customHeight="1" s="48">
-      <c r="A37" s="67" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="68" t="inlineStr">
+      <c r="C51" s="69" t="inlineStr">
+        <is>
+          <t>H4-03</t>
+        </is>
+      </c>
+      <c r="D51" s="70" t="inlineStr">
+        <is>
+          <t>按分の管理者・根拠資料</t>
+        </is>
+      </c>
+      <c r="E51" s="70" t="inlineStr">
+        <is>
+          <t>対象拠点・項目の一覧をESG企画室が提示</t>
+        </is>
+      </c>
+      <c r="G51" s="70" t="inlineStr">
+        <is>
+          <t>情報源の変更であり、ESG企画室が確実に提示すれば問題ない（運用上のToDoとして管理）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1" s="48">
+      <c r="B52" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C37" s="67" t="inlineStr">
-        <is>
-          <t>H3-09</t>
-        </is>
-      </c>
-      <c r="D37" s="68" t="inlineStr">
-        <is>
-          <t>複数報告間で数値が食い違う経験と原因</t>
-        </is>
-      </c>
-      <c r="E37" s="68" t="inlineStr">
-        <is>
-          <t>多目的出力（ワンソース・マルチユース）を要件に含める。CDP等の毎年の様式変更対応は、ESG企画室と別途すり合わせる。</t>
-        </is>
-      </c>
-      <c r="F37" s="68" t="inlineStr">
-        <is>
-          <t>各拠点での帳票間の食い違いの実態を個別に把握しないまま統一設計するため、拠点特有の食い違い要因が要件に反映されずに残る。</t>
-        </is>
-      </c>
-      <c r="G37" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H37" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="46" customHeight="1" s="48">
-      <c r="A38" s="67" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="68" t="inlineStr">
+      <c r="C52" s="69" t="inlineStr">
+        <is>
+          <t>H4-04</t>
+        </is>
+      </c>
+      <c r="D52" s="70" t="inlineStr">
+        <is>
+          <t>按分基準の見直し頻度</t>
+        </is>
+      </c>
+      <c r="E52" s="70" t="inlineStr">
+        <is>
+          <t>按分基準は年度ごとに保持する設計</t>
+        </is>
+      </c>
+      <c r="G52" s="70" t="inlineStr">
+        <is>
+          <t>保守的な設計で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="34" customHeight="1" s="48">
+      <c r="B53" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C38" s="67" t="inlineStr">
-        <is>
-          <t>H4-01</t>
-        </is>
-      </c>
-      <c r="D38" s="68" t="inlineStr">
-        <is>
-          <t>使用係数の名称・出典・年度版</t>
-        </is>
-      </c>
-      <c r="E38" s="68" t="inlineStr">
-        <is>
-          <t>係数は本社一括管理のため不要と判断。</t>
-        </is>
-      </c>
-      <c r="F38" s="68" t="inlineStr">
-        <is>
-          <t>独自係数を使う拠点が実在した場合、係数マスタにその出典・版が登録されず、監査で説明できなくなる。</t>
-        </is>
-      </c>
-      <c r="G38" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H38" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="46" customHeight="1" s="48">
-      <c r="A39" s="67" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="68" t="inlineStr">
+      <c r="C53" s="69" t="inlineStr">
+        <is>
+          <t>H4-12</t>
+        </is>
+      </c>
+      <c r="D53" s="70" t="inlineStr">
+        <is>
+          <t>製品LCA用データ</t>
+        </is>
+      </c>
+      <c r="E53" s="70" t="inlineStr">
+        <is>
+          <t>ESG企画室との事前決定待ち、決定まで対象外</t>
+        </is>
+      </c>
+      <c r="G53" s="70" t="inlineStr">
+        <is>
+          <t>意思決定プロセスを踏んだ先送りであり妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="34" customHeight="1" s="48">
+      <c r="B54" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C39" s="67" t="inlineStr">
-        <is>
-          <t>H4-02</t>
-        </is>
-      </c>
-      <c r="D39" s="68" t="inlineStr">
-        <is>
-          <t>係数更新の連絡方法・再計算の有無</t>
-        </is>
-      </c>
-      <c r="E39" s="68" t="inlineStr">
-        <is>
-          <t>検証期間中に係数更新・再計算が起こり得る点を、再計算機能の要件に反映する（保守的な対応）。</t>
-        </is>
-      </c>
-      <c r="F39" s="68" t="inlineStr">
-        <is>
-          <t>対応自体は保守的なため大きな漏れは小さいが、拠点固有の運用（更新通知を誰が受けるか等）が未確認のまま残る。</t>
-        </is>
-      </c>
-      <c r="G39" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H39" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="46" customHeight="1" s="48">
-      <c r="A40" s="67" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="68" t="inlineStr">
+      <c r="C54" s="69" t="inlineStr">
+        <is>
+          <t>H4-13</t>
+        </is>
+      </c>
+      <c r="D54" s="70" t="inlineStr">
+        <is>
+          <t>人事・安全データの拠点独自解釈</t>
+        </is>
+      </c>
+      <c r="E54" s="70" t="inlineStr">
+        <is>
+          <t>本社側の指標定義の問題として整理</t>
+        </is>
+      </c>
+      <c r="G54" s="70" t="inlineStr">
+        <is>
+          <t>対応の道筋が明確で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="34" customHeight="1" s="48">
+      <c r="B55" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C40" s="67" t="inlineStr">
-        <is>
-          <t>H4-03</t>
-        </is>
-      </c>
-      <c r="D40" s="68" t="inlineStr">
-        <is>
-          <t>割り振り（按分）の管理者・根拠資料の有無</t>
-        </is>
-      </c>
-      <c r="E40" s="68" t="inlineStr">
-        <is>
-          <t>按分の対象拠点・対象項目の一覧をESG企画室から提示してもらう前提とする。</t>
-        </is>
-      </c>
-      <c r="F40" s="68" t="inlineStr">
-        <is>
-          <t>ESG企画室が把握していない拠点独自の按分（本社未報告のローカル按分）があった場合、按分ロジックの対象から漏れる。</t>
-        </is>
-      </c>
-      <c r="G40" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H40" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="46" customHeight="1" s="48">
-      <c r="A41" s="67" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="68" t="inlineStr">
+      <c r="C55" s="69" t="inlineStr">
+        <is>
+          <t>H5-02</t>
+        </is>
+      </c>
+      <c r="D55" s="70" t="inlineStr">
+        <is>
+          <t>保存年限</t>
+        </is>
+      </c>
+      <c r="E55" s="70" t="inlineStr">
+        <is>
+          <t>ESG企画室と決定のうえシステム要件に反映</t>
+        </is>
+      </c>
+      <c r="G55" s="70" t="inlineStr">
+        <is>
+          <t>意思決定プロセスを踏んだ判断であり妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="34" customHeight="1" s="48">
+      <c r="B56" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C41" s="67" t="inlineStr">
-        <is>
-          <t>H4-04</t>
-        </is>
-      </c>
-      <c r="D41" s="68" t="inlineStr">
-        <is>
-          <t>割り振り（按分）基準の見直し頻度</t>
-        </is>
-      </c>
-      <c r="E41" s="68" t="inlineStr">
-        <is>
-          <t>床面積等の基準は変わり得るため、按分基準は年度ごとに保持する設計とする。</t>
-        </is>
-      </c>
-      <c r="F41" s="68" t="inlineStr">
-        <is>
-          <t>年度中に基準が変わる拠点があった場合、年次更新の設計では追いつかず、古い基準で計算され続ける。</t>
-        </is>
-      </c>
-      <c r="G41" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H41" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="46" customHeight="1" s="48">
-      <c r="A42" s="67" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="68" t="inlineStr">
+      <c r="C56" s="69" t="inlineStr">
+        <is>
+          <t>H5-04</t>
+        </is>
+      </c>
+      <c r="D56" s="70" t="inlineStr">
+        <is>
+          <t>第三者保有証憑の入手性</t>
+        </is>
+      </c>
+      <c r="E56" s="70" t="inlineStr">
+        <is>
+          <t>請求ありは入手可、なしは推定・除外</t>
+        </is>
+      </c>
+      <c r="G56" s="70" t="inlineStr">
+        <is>
+          <t>明確な運用ルールとして妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="34" customHeight="1" s="48">
+      <c r="B57" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C42" s="67" t="inlineStr">
-        <is>
-          <t>H4-07</t>
-        </is>
-      </c>
-      <c r="D42" s="68" t="inlineStr">
-        <is>
-          <t>小さな排出源の集計の網羅性</t>
-        </is>
-      </c>
-      <c r="E42" s="68" t="inlineStr">
-        <is>
-          <t>回答の妥当性確認が現実的に困難という前提に立ち、小規模な排出源は本社側でチェックリスト化して補う方針とする。</t>
-        </is>
-      </c>
-      <c r="F42" s="68" t="inlineStr">
-        <is>
-          <t>チェックリストに含まれない拠点固有の小口設備（本社が把握していない設備）があった場合、バウンダリの完全性が損なわれ、外部機関の確認で指摘を受ける。</t>
-        </is>
-      </c>
-      <c r="G42" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H42" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="46" customHeight="1" s="48">
-      <c r="A43" s="67" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="68" t="inlineStr">
+      <c r="C57" s="69" t="inlineStr">
+        <is>
+          <t>H5-06</t>
+        </is>
+      </c>
+      <c r="D57" s="70" t="inlineStr">
+        <is>
+          <t>過去の指摘事項の記録所在</t>
+        </is>
+      </c>
+      <c r="E57" s="70" t="inlineStr">
+        <is>
+          <t>ESG企画室の共有フォルダにあると把握</t>
+        </is>
+      </c>
+      <c r="G57" s="70" t="inlineStr">
+        <is>
+          <t>監査対応は通常ESG企画室が集約する業務であり、妥当性が高い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="34" customHeight="1" s="48">
+      <c r="B58" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C43" s="67" t="inlineStr">
-        <is>
-          <t>H4-08</t>
-        </is>
-      </c>
-      <c r="D43" s="68" t="inlineStr">
-        <is>
-          <t>冷媒（フロン類）の充填・漏えい量の把握</t>
-        </is>
-      </c>
-      <c r="E43" s="68" t="inlineStr">
-        <is>
-          <t>充填作業記録（紙をPDF化）を証憑として扱う前提で要件化する。海外は報告対象外とする。</t>
-        </is>
-      </c>
-      <c r="F43" s="68" t="inlineStr">
-        <is>
-          <t>海外拠点でも冷媒管理が将来必要になった場合（基準変更等）、証憑の仕組みがなく対応が後手になる。</t>
-        </is>
-      </c>
-      <c r="G43" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H43" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="46" customHeight="1" s="48">
-      <c r="A44" s="67" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="68" t="inlineStr">
+      <c r="C58" s="69" t="inlineStr">
+        <is>
+          <t>H6-01</t>
+        </is>
+      </c>
+      <c r="D58" s="70" t="inlineStr">
+        <is>
+          <t>チェック記録の有無</t>
+        </is>
+      </c>
+      <c r="E58" s="70" t="inlineStr">
+        <is>
+          <t>証跡はシステム内に残す前提とする</t>
+        </is>
+      </c>
+      <c r="G58" s="70" t="inlineStr">
+        <is>
+          <t>機能を厚めに実装する対応で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="34" customHeight="1" s="48">
+      <c r="B59" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C44" s="67" t="inlineStr">
-        <is>
-          <t>H4-09</t>
-        </is>
-      </c>
-      <c r="D44" s="68" t="inlineStr">
-        <is>
-          <t>水（取水源別計測・排水量把握）の実態</t>
-        </is>
-      </c>
-      <c r="E44" s="68" t="inlineStr">
-        <is>
-          <t>原則すべてメーター記録とし、地下水は計測の有無のみ確認できる形にする。</t>
-        </is>
-      </c>
-      <c r="F44" s="68" t="inlineStr">
-        <is>
-          <t>地下水の使用量が多い拠点があった場合、料金データがなく実態を過小評価したまま開示数値に反映される。</t>
-        </is>
-      </c>
-      <c r="G44" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H44" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="46" customHeight="1" s="48">
-      <c r="A45" s="67" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="68" t="inlineStr">
+      <c r="C59" s="69" t="inlineStr">
+        <is>
+          <t>H6-03</t>
+        </is>
+      </c>
+      <c r="D59" s="70" t="inlineStr">
+        <is>
+          <t>入力ミスの流出経験</t>
+        </is>
+      </c>
+      <c r="E59" s="70" t="inlineStr">
+        <is>
+          <t>現行の修正要否確認プロセスを維持</t>
+        </is>
+      </c>
+      <c r="G59" s="70" t="inlineStr">
+        <is>
+          <t>既存の安全策を維持する保守的判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1" s="48">
+      <c r="B60" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C45" s="67" t="inlineStr">
-        <is>
-          <t>H4-12</t>
-        </is>
-      </c>
-      <c r="D45" s="68" t="inlineStr">
-        <is>
-          <t>製品LCA用データの提供可否と粒度</t>
-        </is>
-      </c>
-      <c r="E45" s="68" t="inlineStr">
-        <is>
-          <t>CFP算定をシステムの対象に含めるかはESG企画室と事前に決定し、決定までは対象外として整理する。</t>
-        </is>
-      </c>
-      <c r="F45" s="68" t="inlineStr">
-        <is>
-          <t>決定が遅れた場合、製品別データの収集可否確認自体も止まり、CFP即応（攻めの柱）の実現可能性の検証が遅れる。</t>
-        </is>
-      </c>
-      <c r="G45" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H45" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="46" customHeight="1" s="48">
-      <c r="A46" s="67" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="68" t="inlineStr">
+      <c r="C60" s="69" t="inlineStr">
+        <is>
+          <t>H6-04</t>
+        </is>
+      </c>
+      <c r="D60" s="70" t="inlineStr">
+        <is>
+          <t>拠点長の関与頻度</t>
+        </is>
+      </c>
+      <c r="E60" s="70" t="inlineStr">
+        <is>
+          <t>承認者ルールは事務局で設計し拠点へ説明</t>
+        </is>
+      </c>
+      <c r="G60" s="70" t="inlineStr">
+        <is>
+          <t>トップダウンの設計方針として妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="34" customHeight="1" s="48">
+      <c r="B61" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C46" s="67" t="inlineStr">
-        <is>
-          <t>H4-13</t>
-        </is>
-      </c>
-      <c r="D46" s="68" t="inlineStr">
-        <is>
-          <t>人事・労働安全データの拠点独自解釈</t>
-        </is>
-      </c>
-      <c r="E46" s="68" t="inlineStr">
-        <is>
-          <t>本社側の指標定義の問題として整理し、定義の有無をESG企画室に確認する。</t>
-        </is>
-      </c>
-      <c r="F46" s="68" t="inlineStr">
-        <is>
-          <t>拠点独自の解釈（協力会社社員の扱い等）が実際に存在する場合、本社定義の統一だけでは解消されず、S（社会）データの集計に食い違いが残る。</t>
-        </is>
-      </c>
-      <c r="G46" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H46" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="46" customHeight="1" s="48">
-      <c r="A47" s="67" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="68" t="inlineStr">
+      <c r="C61" s="69" t="inlineStr">
+        <is>
+          <t>H6-07</t>
+        </is>
+      </c>
+      <c r="D61" s="70" t="inlineStr">
+        <is>
+          <t>内部監査・ISO審査の指摘内容</t>
+        </is>
+      </c>
+      <c r="E61" s="70" t="inlineStr">
+        <is>
+          <t>ISO監査は数値誤りを対象外として整理</t>
+        </is>
+      </c>
+      <c r="G61" s="70" t="inlineStr">
+        <is>
+          <t>一般的にISO14001は運用プロセスの適合性を見るものであり、数値精度の検証はSGS等の第三者保証が担う。理由は妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="34" customHeight="1" s="48">
+      <c r="B62" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C47" s="67" t="inlineStr">
-        <is>
-          <t>H5-01</t>
-        </is>
-      </c>
-      <c r="D47" s="68" t="inlineStr">
-        <is>
-          <t>証憑の種類・保管場所の全量</t>
-        </is>
-      </c>
-      <c r="E47" s="68" t="inlineStr">
-        <is>
-          <t>把握できた内容（紙／PDF／システム内／クラウド等の実態）で保管先の集約範囲を設計する。</t>
-        </is>
-      </c>
-      <c r="F47" s="68" t="inlineStr">
-        <is>
-          <t>把握していない証憑保管パターン（個人PC等）を持つ拠点があった場合、移行計画から漏れ、証憑が消失するリスクが残る。</t>
-        </is>
-      </c>
-      <c r="G47" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H47" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="46" customHeight="1" s="48">
-      <c r="A48" s="67" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="68" t="inlineStr">
+      <c r="C62" s="69" t="inlineStr">
+        <is>
+          <t>H7-03</t>
+        </is>
+      </c>
+      <c r="D62" s="70" t="inlineStr">
+        <is>
+          <t>子メーターの設置状況</t>
+        </is>
+      </c>
+      <c r="E62" s="70" t="inlineStr">
+        <is>
+          <t>拠点単位で足りるとし部門別粒度は対象外</t>
+        </is>
+      </c>
+      <c r="G62" s="70" t="inlineStr">
+        <is>
+          <t>意図的なスコープ決定で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="34" customHeight="1" s="48">
+      <c r="B63" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C48" s="67" t="inlineStr">
-        <is>
-          <t>H5-02</t>
-        </is>
-      </c>
-      <c r="D48" s="68" t="inlineStr">
-        <is>
-          <t>証憑の保存年限のルールと実態</t>
-        </is>
-      </c>
-      <c r="E48" s="68" t="inlineStr">
-        <is>
-          <t>保存年限をESG企画室と決定のうえ、システム要件に反映する。</t>
-        </is>
-      </c>
-      <c r="F48" s="68" t="inlineStr">
-        <is>
-          <t>拠点ごとの実際の保存実態（規定より短い等）を確認しないまま年限を決めるため、実態と異なる年限を設定すると、移行時に証憑が不足する拠点が出る。</t>
-        </is>
-      </c>
-      <c r="G48" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H48" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="46" customHeight="1" s="48">
-      <c r="A49" s="67" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="68" t="inlineStr">
+      <c r="C63" s="69" t="inlineStr">
+        <is>
+          <t>H7-04</t>
+        </is>
+      </c>
+      <c r="D63" s="70" t="inlineStr">
+        <is>
+          <t>ITサポート体制</t>
+        </is>
+      </c>
+      <c r="E63" s="70" t="inlineStr">
+        <is>
+          <t>現地IT支援は期待せず本社リモート支援を計画</t>
+        </is>
+      </c>
+      <c r="G63" s="70" t="inlineStr">
+        <is>
+          <t>最悪ケースを前提にした保守的な計画で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1" s="48">
+      <c r="B64" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C49" s="67" t="inlineStr">
-        <is>
-          <t>H5-04</t>
-        </is>
-      </c>
-      <c r="D49" s="68" t="inlineStr">
-        <is>
-          <t>第三者保有証憑の入手性</t>
-        </is>
-      </c>
-      <c r="E49" s="68" t="inlineStr">
-        <is>
-          <t>「請求がある項目は入手可能、請求がない項目は推定・除外で対応」という整理を前提とする。</t>
-        </is>
-      </c>
-      <c r="F49" s="68" t="inlineStr">
-        <is>
-          <t>請求はないが証憑としては必要な項目（契約書等）がある拠点があった場合、除外の判断が誤り、保証対応で証憑不足になる。</t>
-        </is>
-      </c>
-      <c r="G49" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H49" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="46" customHeight="1" s="48">
-      <c r="A50" s="67" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="68" t="inlineStr">
+      <c r="C64" s="69" t="inlineStr">
+        <is>
+          <t>H8-01</t>
+        </is>
+      </c>
+      <c r="D64" s="70" t="inlineStr">
+        <is>
+          <t>本社照会・差し戻し件数</t>
+        </is>
+      </c>
+      <c r="E64" s="70" t="inlineStr">
+        <is>
+          <t>把握済みの実績値を効果試算の基準値とする</t>
+        </is>
+      </c>
+      <c r="G64" s="70" t="inlineStr">
+        <is>
+          <t>実データに基づく判断で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="34" customHeight="1" s="48">
+      <c r="B65" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C50" s="67" t="inlineStr">
-        <is>
-          <t>H5-06</t>
-        </is>
-      </c>
-      <c r="D50" s="68" t="inlineStr">
-        <is>
-          <t>過去の検証での指摘事項と対応の記録所在</t>
-        </is>
-      </c>
-      <c r="E50" s="68" t="inlineStr">
-        <is>
-          <t>指摘事項の記録はESG企画室の共有フォルダにあると把握。</t>
-        </is>
-      </c>
-      <c r="F50" s="68" t="inlineStr">
-        <is>
-          <t>共有フォルダに含まれていない拠点固有の指摘（現地の第三者検証機関からの指摘等）があった場合、過去の指摘への対応が要件に反映されず、同じ指摘を繰り返す。</t>
-        </is>
-      </c>
-      <c r="G50" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H50" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="46" customHeight="1" s="48">
-      <c r="A51" s="67" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="68" t="inlineStr">
+      <c r="C65" s="69" t="inlineStr">
+        <is>
+          <t>H8-02</t>
+        </is>
+      </c>
+      <c r="D65" s="70" t="inlineStr">
+        <is>
+          <t>業務関与人数・兼務状況</t>
+        </is>
+      </c>
+      <c r="E65" s="70" t="inlineStr">
+        <is>
+          <t>Scope1・2で3名を前提にライセンス数を試算</t>
+        </is>
+      </c>
+      <c r="G65" s="70" t="inlineStr">
+        <is>
+          <t>Scope3を含める場合の見直しを自ら明記しており、リスクを認識した上での判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="34" customHeight="1" s="48">
+      <c r="B66" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C51" s="67" t="inlineStr">
-        <is>
-          <t>H6-01</t>
-        </is>
-      </c>
-      <c r="D51" s="68" t="inlineStr">
-        <is>
-          <t>チェックした事実の記録有無</t>
-        </is>
-      </c>
-      <c r="E51" s="68" t="inlineStr">
-        <is>
-          <t>チェックの証跡はシステム内に残す前提とし、拠点の自己管理には委ねない方針とする。</t>
-        </is>
-      </c>
-      <c r="F51" s="68" t="inlineStr">
-        <is>
-          <t>拠点固有の追加チェック（現地の内部統制ルール等）が把握されないまま、統制設計から漏れる。</t>
-        </is>
-      </c>
-      <c r="G51" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H51" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="46" customHeight="1" s="48">
-      <c r="A52" s="67" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="68" t="inlineStr">
+      <c r="C66" s="69" t="inlineStr">
+        <is>
+          <t>H9-03</t>
+        </is>
+      </c>
+      <c r="D66" s="70" t="inlineStr">
+        <is>
+          <t>CSRD等の追加開示要求</t>
+        </is>
+      </c>
+      <c r="E66" s="70" t="inlineStr">
+        <is>
+          <t>オーストラリア子会社分を将来要件として記録</t>
+        </is>
+      </c>
+      <c r="G66" s="70" t="inlineStr">
+        <is>
+          <t>判明した事実を無視せず要件に反映しており妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="34" customHeight="1" s="48">
+      <c r="B67" s="70" t="inlineStr">
         <is>
           <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
-      <c r="C52" s="67" t="inlineStr">
-        <is>
-          <t>H6-02</t>
-        </is>
-      </c>
-      <c r="D52" s="68" t="inlineStr">
-        <is>
-          <t>異常値の定義・閾値と対応者</t>
-        </is>
-      </c>
-      <c r="E52" s="68" t="inlineStr">
-        <is>
-          <t>閾値はESG企画室の机上設定で進める。</t>
-        </is>
-      </c>
-      <c r="F52" s="68" t="inlineStr">
-        <is>
-          <t>拠点ごとの変動特性（季節性・生産量変動等）を反映しない一律の閾値になり、異常値の誤検知・見逃しが生じる拠点が出る。</t>
-        </is>
-      </c>
-      <c r="G52" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H52" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="46" customHeight="1" s="48">
-      <c r="A53" s="67" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="68" t="inlineStr">
-        <is>
-          <t>5.選抜拠点ヒアリング</t>
-        </is>
-      </c>
-      <c r="C53" s="67" t="inlineStr">
-        <is>
-          <t>H6-03</t>
-        </is>
-      </c>
-      <c r="D53" s="68" t="inlineStr">
-        <is>
-          <t>入力ミスが本社集計まで流れた経験</t>
-        </is>
-      </c>
-      <c r="E53" s="68" t="inlineStr">
-        <is>
-          <t>一次締切後の「修正要否確認」で品質を担保している現行プロセスを、新システムでも工程として維持する前提で設計する。</t>
-        </is>
-      </c>
-      <c r="F53" s="68" t="inlineStr">
-        <is>
-          <t>現行プロセスでも防げなかった拠点固有のミスの経路（今回ヒアリングできなかった拠点の経路）が新システムでも再発する。</t>
-        </is>
-      </c>
-      <c r="G53" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H53" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="46" customHeight="1" s="48">
-      <c r="A54" s="67" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="68" t="inlineStr">
-        <is>
-          <t>5.選抜拠点ヒアリング</t>
-        </is>
-      </c>
-      <c r="C54" s="67" t="inlineStr">
-        <is>
-          <t>H6-04</t>
-        </is>
-      </c>
-      <c r="D54" s="68" t="inlineStr">
-        <is>
-          <t>拠点長・工場長がデータを見る機会</t>
-        </is>
-      </c>
-      <c r="E54" s="68" t="inlineStr">
-        <is>
-          <t>承認者のルールは事務局で設計し拠点へ説明する方針とする。承認者以外の閲覧権限も要件に含める。</t>
-        </is>
-      </c>
-      <c r="F54" s="68" t="inlineStr">
-        <is>
-          <t>拠点長の関与が薄い拠点で承認ルールへの実務的な抵抗が生じ、定着に時間がかかる可能性を事前に把握できない。</t>
-        </is>
-      </c>
-      <c r="G54" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H54" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="46" customHeight="1" s="48">
-      <c r="A55" s="67" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="68" t="inlineStr">
-        <is>
-          <t>5.選抜拠点ヒアリング</t>
-        </is>
-      </c>
-      <c r="C55" s="67" t="inlineStr">
-        <is>
-          <t>H6-07</t>
-        </is>
-      </c>
-      <c r="D55" s="68" t="inlineStr">
-        <is>
-          <t>内部監査・J-SOX・ISO審査の対象経験と指摘</t>
-        </is>
-      </c>
-      <c r="E55" s="68" t="inlineStr">
-        <is>
-          <t>ISO監査は数値の誤りを対象としないため要件への影響なしと整理。ISO14001取得拠点の一覧はESG企画室・監査室から入手する。</t>
-        </is>
-      </c>
-      <c r="F55" s="68" t="inlineStr">
-        <is>
-          <t>実際に数値関連の指摘を受けた拠点（今回ヒアリング対象外）があった場合、その指摘内容が要件に反映されない。</t>
-        </is>
-      </c>
-      <c r="G55" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H55" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="46" customHeight="1" s="48">
-      <c r="A56" s="67" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="68" t="inlineStr">
-        <is>
-          <t>5.選抜拠点ヒアリング</t>
-        </is>
-      </c>
-      <c r="C56" s="67" t="inlineStr">
-        <is>
-          <t>H7-03</t>
-        </is>
-      </c>
-      <c r="D56" s="68" t="inlineStr">
-        <is>
-          <t>子メーター（部門別・建屋別）の設置状況</t>
-        </is>
-      </c>
-      <c r="E56" s="68" t="inlineStr">
-        <is>
-          <t>拠点単位で足りるという前提で進める。部門別・建屋別の粒度は対象外とする。</t>
-        </is>
-      </c>
-      <c r="F56" s="68" t="inlineStr">
-        <is>
-          <t>部門別データが必要な拠点（複数事業が混在する拠点等）があった場合、開示要件を満たせない。</t>
-        </is>
-      </c>
-      <c r="G56" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H56" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="46" customHeight="1" s="48">
-      <c r="A57" s="67" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="68" t="inlineStr">
-        <is>
-          <t>5.選抜拠点ヒアリング</t>
-        </is>
-      </c>
-      <c r="C57" s="67" t="inlineStr">
-        <is>
-          <t>H7-04</t>
-        </is>
-      </c>
-      <c r="D57" s="68" t="inlineStr">
-        <is>
-          <t>ITサポート体制と導入時の協力可否</t>
-        </is>
-      </c>
-      <c r="E57" s="68" t="inlineStr">
-        <is>
-          <t>現地ITの支援は期待しない前提で、導入時は本社からのリモート支援を計画する。</t>
-        </is>
-      </c>
-      <c r="F57" s="68" t="inlineStr">
-        <is>
-          <t>リモート支援が届きにくい拠点（通信環境が弱い海外拠点等）があった場合、導入時の技術的トラブルの解消が遅れる。</t>
-        </is>
-      </c>
-      <c r="G57" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H57" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="46" customHeight="1" s="48">
-      <c r="A58" s="67" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="68" t="inlineStr">
-        <is>
-          <t>5.選抜拠点ヒアリング</t>
-        </is>
-      </c>
-      <c r="C58" s="67" t="inlineStr">
-        <is>
-          <t>H8-01</t>
-        </is>
-      </c>
-      <c r="D58" s="68" t="inlineStr">
-        <is>
-          <t>本社照会・差し戻し対応の件数・時間</t>
-        </is>
-      </c>
-      <c r="E58" s="68" t="inlineStr">
-        <is>
-          <t>把握済みの実績値（検証前5拠点／年、検証後は全拠点で数十〜100件）を効果試算の基準値とする。</t>
-        </is>
-      </c>
-      <c r="F58" s="68" t="inlineStr">
-        <is>
-          <t>特定拠点で差し戻しが特に多い実態があった場合、ROI試算の基準値が実態より小さく見積られ、投資判断の説明力が弱まる。</t>
-        </is>
-      </c>
-      <c r="G58" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H58" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="46" customHeight="1" s="48">
-      <c r="A59" s="67" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="68" t="inlineStr">
-        <is>
-          <t>5.選抜拠点ヒアリング</t>
-        </is>
-      </c>
-      <c r="C59" s="67" t="inlineStr">
-        <is>
-          <t>H8-02</t>
-        </is>
-      </c>
-      <c r="D59" s="68" t="inlineStr">
-        <is>
-          <t>業務に関わる人数・兼務状況</t>
-        </is>
-      </c>
-      <c r="E59" s="68" t="inlineStr">
-        <is>
-          <t>Scope1・2で3名を前提にライセンス数を試算する。Scope3を含める場合は別途見直す。</t>
-        </is>
-      </c>
-      <c r="F59" s="68" t="inlineStr">
-        <is>
-          <t>実際の関与人数が3名を超える拠点が多い場合、ライセンス数が不足し、稼働後に追加費用が発生する。</t>
-        </is>
-      </c>
-      <c r="G59" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H59" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="46" customHeight="1" s="48">
-      <c r="A60" s="67" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="68" t="inlineStr">
-        <is>
-          <t>5.選抜拠点ヒアリング</t>
-        </is>
-      </c>
-      <c r="C60" s="67" t="inlineStr">
-        <is>
-          <t>H9-02</t>
-        </is>
-      </c>
-      <c r="D60" s="68" t="inlineStr">
-        <is>
-          <t>現地排出係数の種類と入手元</t>
-        </is>
-      </c>
-      <c r="E60" s="68" t="inlineStr">
-        <is>
-          <t>既に検証を受けている係数を正とする前提で進める。</t>
-        </is>
-      </c>
-      <c r="F60" s="68" t="inlineStr">
-        <is>
-          <t>検証を受けていない独自係数を使っている海外拠点があった場合、その数値が保証で説明できなくなる。</t>
-        </is>
-      </c>
-      <c r="G60" s="69" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H60" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="46" customHeight="1" s="48">
-      <c r="A61" s="67" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="68" t="inlineStr">
-        <is>
-          <t>5.選抜拠点ヒアリング</t>
-        </is>
-      </c>
-      <c r="C61" s="67" t="inlineStr">
-        <is>
-          <t>H9-03</t>
-        </is>
-      </c>
-      <c r="D61" s="68" t="inlineStr">
-        <is>
-          <t>CSRD等の追加開示要求の有無</t>
-        </is>
-      </c>
-      <c r="E61" s="68" t="inlineStr">
-        <is>
-          <t>オーストラリア子会社分の開示義務（28年実績）のみ将来要件として記録する。</t>
-        </is>
-      </c>
-      <c r="F61" s="68" t="inlineStr">
-        <is>
-          <t>他の海外拠点でも同様の現地規制・顧客要求が今後発生した場合、拡張性要件から漏れる。</t>
-        </is>
-      </c>
-      <c r="G61" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H61" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="46" customHeight="1" s="48">
-      <c r="A62" s="67" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="68" t="inlineStr">
-        <is>
-          <t>5.選抜拠点ヒアリング</t>
-        </is>
-      </c>
-      <c r="C62" s="67" t="inlineStr">
-        <is>
-          <t>H9-05</t>
-        </is>
-      </c>
-      <c r="D62" s="68" t="inlineStr">
-        <is>
-          <t>現地事情による欠測・遅延の頻度</t>
-        </is>
-      </c>
-      <c r="E62" s="68" t="inlineStr">
-        <is>
-          <t>バングラデシュでも致命的な遅延はない想定のため、オフライン前提の機能は見送る。</t>
-        </is>
-      </c>
-      <c r="F62" s="68" t="inlineStr">
-        <is>
-          <t>他の停電・通信障害が多い拠点（他の新興国拠点等）で欠測が頻発する場合、オフライン機能なしでは運用が止まる。</t>
-        </is>
-      </c>
-      <c r="G62" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H62" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="46" customHeight="1" s="48">
-      <c r="A63" s="67" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="68" t="inlineStr">
-        <is>
-          <t>5.選抜拠点ヒアリング</t>
-        </is>
-      </c>
-      <c r="C63" s="67" t="inlineStr">
+      <c r="C67" s="69" t="inlineStr">
         <is>
           <t>H9-06</t>
         </is>
       </c>
-      <c r="D63" s="68" t="inlineStr">
-        <is>
-          <t>現地委託先からのデータ入手性</t>
-        </is>
-      </c>
-      <c r="E63" s="68" t="inlineStr">
-        <is>
-          <t>取れないデータは使わない（推定・除外）という原則で整理する。</t>
-        </is>
-      </c>
-      <c r="F63" s="68" t="inlineStr">
-        <is>
-          <t>委託先データの欠落が多い拠点では、推定・除外の範囲が大きくなり、開示数値の精度・説明力が低下する。</t>
-        </is>
-      </c>
-      <c r="G63" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H63" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="46" customHeight="1" s="48">
-      <c r="A64" s="67" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="68" t="inlineStr">
-        <is>
-          <t>5.選抜拠点ヒアリング</t>
-        </is>
-      </c>
-      <c r="C64" s="67" t="inlineStr">
-        <is>
-          <t>H9-07</t>
-        </is>
-      </c>
-      <c r="D64" s="68" t="inlineStr">
-        <is>
-          <t>現地経営層の関与度・承認追加の実現性</t>
-        </is>
-      </c>
-      <c r="E64" s="68" t="inlineStr">
-        <is>
-          <t>承認のフローとして不要という回答から判断。</t>
-        </is>
-      </c>
-      <c r="F64" s="68" t="inlineStr">
-        <is>
-          <t>現地のガバナンス上、現地経営層の承認が必須な拠点（法制度上の要求がある国等）があった場合、承認フローの要件から漏れ、現地コンプライアンス上の問題になる。</t>
-        </is>
-      </c>
-      <c r="G64" s="71" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H64" s="70" t="inlineStr">
-        <is>
-          <t>回答側（該当拠点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="72" t="inlineStr">
-        <is>
-          <t>【集計】</t>
-        </is>
-      </c>
-      <c r="B66" s="73" t="n"/>
-      <c r="C66" s="73" t="n"/>
-      <c r="D66" s="73" t="n"/>
-      <c r="E66" s="73" t="n"/>
-      <c r="F66" s="73" t="n"/>
-      <c r="G66" s="73" t="n"/>
-      <c r="H66" s="73" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="74" t="inlineStr">
-        <is>
-          <t>削減設問 合計: 60件</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2.データ項目インベントリ: 1件</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　3.コア設問: 16件</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　4.難所チェック: 9件</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　5.選抜拠点ヒアリング: 34件</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="76" t="inlineStr">
-        <is>
-          <t>影響度「高」: 26件／「中」: 34件</t>
-        </is>
-      </c>
-      <c r="B72" s="77" t="n"/>
-      <c r="C72" s="77" t="n"/>
-      <c r="D72" s="77" t="n"/>
-      <c r="E72" s="77" t="n"/>
-      <c r="F72" s="77" t="n"/>
-      <c r="G72" s="77" t="n"/>
-      <c r="H72" s="77" t="n"/>
+      <c r="D67" s="70" t="inlineStr">
+        <is>
+          <t>現地委託先データの入手性</t>
+        </is>
+      </c>
+      <c r="E67" s="70" t="inlineStr">
+        <is>
+          <t>取れないデータは推定・除外する原則</t>
+        </is>
+      </c>
+      <c r="G67" s="70" t="inlineStr">
+        <is>
+          <t>明確な運用ルールとして妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1" s="48">
+      <c r="A69" s="77" t="inlineStr">
+        <is>
+          <t>【集計】60件レビュー ／ 削除に同意 37件 ／ 要注意 23件（うち理由不十分・誤り＝7件、理由は妥当だがリスク残存＝16件）</t>
+        </is>
+      </c>
+      <c r="B69" s="78" t="n"/>
+      <c r="C69" s="78" t="n"/>
+      <c r="D69" s="78" t="n"/>
+      <c r="E69" s="78" t="n"/>
+      <c r="F69" s="78" t="n"/>
+      <c r="G69" s="78" t="n"/>
+      <c r="H69" s="78" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A66:H66"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/As-Is調査_V1.1_削減設問リスク一覧_0917.xlsx
+++ b/docs/As-Is調査_V1.1_削減設問リスク一覧_0917.xlsx
@@ -12066,7 +12066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="48" min="1" max="1"/>
@@ -12082,21 +12082,21 @@
     <row r="1" ht="22" customHeight="1" s="48">
       <c r="A1" s="64" t="inlineStr">
         <is>
-          <t>6. 削減設問リスク一覧 ― 専門家レビュー版（60件を検証し、37件は削除に同意／23件は要注意）</t>
+          <t>6. 削減設問リスク一覧 ― 専門家レビュー版（81件を検証し、51件は削除に同意／30件は要注意）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="66" customHeight="1" s="48">
       <c r="A2" s="65" t="inlineStr">
         <is>
-          <t>南（デジ戦）がv1.1パイロット回答を受けて「拠点への設問として不要」と判断した60件（単純な重複統合を除く）について、プロの戦略コンサルタント・システムコンサルタントの視点であらためて検証しました。削除理由が妥当でリスクが軽微、または別の仕組みで担保されている37件は【削除に同意】とし、リスク一覧からは外しています（下部に一覧を残しています）。一方、削除理由に論理的な誤り・対応不足がある、または理由自体は妥当でもシステム導入・コンプライアンス上のリスクが残る23件を【要注意】として、本シート上部に詳細を記載します。要注意の設問については、拠点配布前にESG企画室・海外BUへの再確認、または設問を残す判断を推奨します。</t>
+          <t>南（デジ戦）がv1.1パイロット回答を受けて「拠点への設問として不要」と判断した81件（単純な重複統合を除く。当初検出した60件に加え、「【回答】」形式で記載されていた21件を追加検証）について、プロの戦略コンサルタント・システムコンサルタントの視点であらためて検証しました。削除理由が妥当でリスクが軽微、または別の仕組みで担保されている51件は【削除に同意】とし、リスク一覧からは外しています（下部に一覧を残しています）。一方、削除理由に論理的な誤り・対応不足がある、または理由自体は妥当でもシステム導入・コンプライアンス上のリスクが残る30件を【要注意】として、本シート上部に詳細を記載します。要注意の設問については、拠点配布前にESG企画室・海外BUへの再確認、または設問を残す判断を推奨します。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="48">
       <c r="A3" s="66" t="inlineStr">
         <is>
-          <t>【要注意 23件】理由が不十分、または理由は妥当でもリスクが残る設問</t>
+          <t>【要注意 30件】理由が不十分、または理由は妥当でもリスクが残る設問</t>
         </is>
       </c>
       <c r="B3" s="67" t="n"/>
@@ -13069,233 +13069,324 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1" s="48">
-      <c r="A29" s="75" t="inlineStr">
-        <is>
-          <t>【削除に同意 37件】理由が妥当と判断し、リスク一覧からは除外した設問（参考記録）</t>
-        </is>
-      </c>
-      <c r="B29" s="76" t="n"/>
-      <c r="C29" s="76" t="n"/>
-      <c r="D29" s="76" t="n"/>
-      <c r="E29" s="76" t="n"/>
-      <c r="F29" s="76" t="n"/>
-      <c r="G29" s="76" t="n"/>
-      <c r="H29" s="76" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1" s="48">
-      <c r="B30" s="68" t="inlineStr">
+    <row r="28" ht="68" customHeight="1" s="48">
+      <c r="A28" s="69" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C28" s="69" t="inlineStr">
+        <is>
+          <t>C-06</t>
+        </is>
+      </c>
+      <c r="D28" s="70" t="inlineStr">
+        <is>
+          <t>CO2換算排出量等の計算をどこまで拠点側で行っているか</t>
+        </is>
+      </c>
+      <c r="E28" s="70" t="inlineStr">
+        <is>
+          <t>海外法人向けは削除。国内拠点向けは実態をESGに確認したうえて調整。</t>
+        </is>
+      </c>
+      <c r="F28" s="71" t="inlineStr">
+        <is>
+          <t>リスク残存・理由不十分</t>
+        </is>
+      </c>
+      <c r="G28" s="70" t="inlineStr">
+        <is>
+          <t>海外BU自身が「生産拠点では自前で算定をしている」と明言しているにもかかわらず、海外法人向けの設問を削除するのは、まさに当初のリスク（拠点独自計算による数値連続性の断絶）を放置することになる。国内拠点分もステータスが『保留』のまま未決着であり、要求定義確定前に必ず解消が必要。</t>
+        </is>
+      </c>
+      <c r="H28" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="68" customHeight="1" s="48">
+      <c r="A29" s="69" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C29" s="69" t="inlineStr">
+        <is>
+          <t>C-11</t>
+        </is>
+      </c>
+      <c r="D29" s="70" t="inlineStr">
+        <is>
+          <t>証憑添付が必須になった場合、今のやり方のまま対応できるか</t>
+        </is>
+      </c>
+      <c r="E29" s="70" t="inlineStr">
+        <is>
+          <t>ご指摘を踏まえ設問は削除。海外は事務局からの提出方法の指示自体がないため、「今のやり方」を聞く前提が成立していなかった。</t>
+        </is>
+      </c>
+      <c r="F29" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G29" s="70" t="inlineStr">
+        <is>
+          <t>設問の前提（今のやり方と比較する）が成立しないという指摘は妥当だが、『証憑添付を必須化した場合に運用が回るか』という論点自体は解消されていない。代替の確認方法（言い換えた設問等）を検討すべき。</t>
+        </is>
+      </c>
+      <c r="H29" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="68" customHeight="1" s="48">
+      <c r="A30" s="69" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C30" s="69" t="inlineStr">
+        <is>
+          <t>C-17</t>
+        </is>
+      </c>
+      <c r="D30" s="70" t="inlineStr">
+        <is>
+          <t>非財務データ業務の月間工数（詳細含む）</t>
+        </is>
+      </c>
+      <c r="E30" s="70" t="inlineStr">
+        <is>
+          <t>本社推定で進める。拠点への工数設問（詳細①〜⑤含む）は削除。</t>
+        </is>
+      </c>
+      <c r="F30" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存（データなし）</t>
+        </is>
+      </c>
+      <c r="G30" s="70" t="inlineStr">
+        <is>
+          <t>回答者コメントは「LCT以外でまともに実施したことがない」「推測で進めてください」「質問が分からなかった」であり、実質的に未回答。本社推定は仮説にすぎず、投資判断の根拠となるROI試算の分母が検証されないまま確定するリスクが最も大きい項目。少なくとも1〜2拠点で実測に近い値を確認するサンプル調査を推奨する。</t>
+        </is>
+      </c>
+      <c r="H30" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="68" customHeight="1" s="48">
+      <c r="A31" s="69" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C31" s="69" t="inlineStr">
+        <is>
+          <t>C-32</t>
+        </is>
+      </c>
+      <c r="D31" s="70" t="inlineStr">
+        <is>
+          <t>入力ファイル・システムのアクセス権はどうなっているか</t>
+        </is>
+      </c>
+      <c r="E31" s="70" t="inlineStr">
+        <is>
+          <t>拠点で使っている計算用Excelのアクセス権を想定した設問だったため、設問としては削除。</t>
+        </is>
+      </c>
+      <c r="F31" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G31" s="70" t="inlineStr">
+        <is>
+          <t>設問の対象を明確化したのみで、『誰でも編集できる状態か』という統制上の論点自体は解消されていない。当初、改ざんリスクとして外部機関に指摘されるおそれから影響度「高」に設定されていた点を踏まえ、代替の確認方法を残すべき。</t>
+        </is>
+      </c>
+      <c r="H31" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="68" customHeight="1" s="48">
+      <c r="A32" s="69" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C32" s="69" t="inlineStr">
+        <is>
+          <t>H3-07</t>
+        </is>
+      </c>
+      <c r="D32" s="70" t="inlineStr">
+        <is>
+          <t>メーター交換・契約変更時のデータ処理手順</t>
+        </is>
+      </c>
+      <c r="E32" s="70" t="inlineStr">
+        <is>
+          <t>すべて校正済みとして扱い、交換による影響を無視する前提で設問は削除。</t>
+        </is>
+      </c>
+      <c r="F32" s="71" t="inlineStr">
+        <is>
+          <t>根拠不明確</t>
+        </is>
+      </c>
+      <c r="G32" s="70" t="inlineStr">
+        <is>
+          <t>『交換による影響を無視する』根拠が示されていない。頻度は低いと考えられるが、精度への影響が皆無であるかは未確認。</t>
+        </is>
+      </c>
+      <c r="H32" s="74" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="68" customHeight="1" s="48">
+      <c r="A33" s="69" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C33" s="69" t="inlineStr">
+        <is>
+          <t>H7-05</t>
+        </is>
+      </c>
+      <c r="D33" s="70" t="inlineStr">
+        <is>
+          <t>過去に定着しなかったシステム・ツールとその理由</t>
+        </is>
+      </c>
+      <c r="E33" s="70" t="inlineStr">
+        <is>
+          <t>Scope3算定システムの導入検討の経緯を、ESG室の末武さんに確認する。設問は不要。</t>
+        </is>
+      </c>
+      <c r="F33" s="73" t="inlineStr">
+        <is>
+          <t>対応未完了</t>
+        </is>
+      </c>
+      <c r="G33" s="70" t="inlineStr">
+        <is>
+          <t>『確認する』は未完了のToDoとして記載されており、実際にヒアリングが完了したかは本シートから確認できない。定着リスクの最重要インプットとして影響度「高」に設定されていた項目であり、実施状況の確認を要する。</t>
+        </is>
+      </c>
+      <c r="H33" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="68" customHeight="1" s="48">
+      <c r="A34" s="69" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C34" s="69" t="inlineStr">
+        <is>
+          <t>H9-08</t>
+        </is>
+      </c>
+      <c r="D34" s="70" t="inlineStr">
+        <is>
+          <t>本社未報告の現地環境・安全データの有無</t>
+        </is>
+      </c>
+      <c r="E34" s="70" t="inlineStr">
+        <is>
+          <t>網羅性を証明してもらうのではなく、本社側のチェックリストで補う方針に切り替え、設問は削除。</t>
+        </is>
+      </c>
+      <c r="F34" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存</t>
+        </is>
+      </c>
+      <c r="G34" s="70" t="inlineStr">
+        <is>
+          <t>H4-07と同根の問題。本社チェックリストが全海外拠点の未報告データを実際に洗い出せる網羅性を持つかは不透明。バウンダリ完全性に関わる影響度「高」の項目であり、リスクが残る。</t>
+        </is>
+      </c>
+      <c r="H34" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" s="48">
+      <c r="A36" s="75" t="inlineStr">
+        <is>
+          <t>【削除に同意 51件】理由が妥当と判断し、リスク一覧からは除外した設問（参考記録）</t>
+        </is>
+      </c>
+      <c r="B36" s="76" t="n"/>
+      <c r="C36" s="76" t="n"/>
+      <c r="D36" s="76" t="n"/>
+      <c r="E36" s="76" t="n"/>
+      <c r="F36" s="76" t="n"/>
+      <c r="G36" s="76" t="n"/>
+      <c r="H36" s="76" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1" s="48">
+      <c r="B37" s="68" t="inlineStr">
         <is>
           <t>シート</t>
         </is>
       </c>
-      <c r="C30" s="68" t="inlineStr">
+      <c r="C37" s="68" t="inlineStr">
         <is>
           <t>元ID</t>
         </is>
       </c>
-      <c r="D30" s="68" t="inlineStr">
+      <c r="D37" s="68" t="inlineStr">
         <is>
           <t>元の設問（要旨）</t>
         </is>
       </c>
-      <c r="E30" s="68" t="inlineStr">
+      <c r="E37" s="68" t="inlineStr">
         <is>
           <t>削除理由の要旨</t>
         </is>
       </c>
-      <c r="G30" s="68" t="inlineStr">
+      <c r="G37" s="68" t="inlineStr">
         <is>
           <t>同意コメント</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="34" customHeight="1" s="48">
-      <c r="B31" s="70" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C31" s="69" t="inlineStr">
-        <is>
-          <t>C-01</t>
-        </is>
-      </c>
-      <c r="D31" s="70" t="inlineStr">
-        <is>
-          <t>手順書の有無</t>
-        </is>
-      </c>
-      <c r="E31" s="70" t="inlineStr">
-        <is>
-          <t>両拠点とも手順書なしで一致</t>
-        </is>
-      </c>
-      <c r="G31" s="70" t="inlineStr">
-        <is>
-          <t>仮に手順書がある拠点があっても、被る不利益は個別ヒアリングの手間程度で小さい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="34" customHeight="1" s="48">
-      <c r="B32" s="70" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C32" s="69" t="inlineStr">
-        <is>
-          <t>C-09</t>
-        </is>
-      </c>
-      <c r="D32" s="70" t="inlineStr">
-        <is>
-          <t>証憑の保管形式</t>
-        </is>
-      </c>
-      <c r="E32" s="70" t="inlineStr">
-        <is>
-          <t>PDF・Excelが中心と把握</t>
-        </is>
-      </c>
-      <c r="G32" s="70" t="inlineStr">
-        <is>
-          <t>低リスク。仮に紙中心の拠点があっても保管容量を多めに見ておけば対応可能。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="34" customHeight="1" s="48">
-      <c r="B33" s="70" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C33" s="69" t="inlineStr">
-        <is>
-          <t>C-13</t>
-        </is>
-      </c>
-      <c r="D33" s="70" t="inlineStr">
-        <is>
-          <t>変更履歴の有無</t>
-        </is>
-      </c>
-      <c r="E33" s="70" t="inlineStr">
-        <is>
-          <t>変更履歴を必須要件として確定</t>
-        </is>
-      </c>
-      <c r="G33" s="70" t="inlineStr">
-        <is>
-          <t>履歴機能を全拠点前提で実装するため、実態が違っても上位互換で吸収できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="34" customHeight="1" s="48">
-      <c r="B34" s="70" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C34" s="69" t="inlineStr">
-        <is>
-          <t>C-23</t>
-        </is>
-      </c>
-      <c r="D34" s="70" t="inlineStr">
-        <is>
-          <t>抜け漏れ・遅延の主な原因</t>
-        </is>
-      </c>
-      <c r="E34" s="70" t="inlineStr">
-        <is>
-          <t>5つの原因を要件に反映</t>
-        </is>
-      </c>
-      <c r="G34" s="70" t="inlineStr">
-        <is>
-          <t>汎用的な原因（アラート視認性、単位換算、年始重なり等）で妥当性が高い。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="34" customHeight="1" s="48">
-      <c r="B35" s="70" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C35" s="69" t="inlineStr">
-        <is>
-          <t>C-27</t>
-        </is>
-      </c>
-      <c r="D35" s="70" t="inlineStr">
-        <is>
-          <t>妥当性チェック方法</t>
-        </is>
-      </c>
-      <c r="E35" s="70" t="inlineStr">
-        <is>
-          <t>標準閾値はESG企画室が設定</t>
-        </is>
-      </c>
-      <c r="G35" s="70" t="inlineStr">
-        <is>
-          <t>現状の拠点実態に関わらず、今後の方針として妥当な決定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="34" customHeight="1" s="48">
-      <c r="B36" s="70" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C36" s="69" t="inlineStr">
-        <is>
-          <t>C-29</t>
-        </is>
-      </c>
-      <c r="D36" s="70" t="inlineStr">
-        <is>
-          <t>証憑を探す時間</t>
-        </is>
-      </c>
-      <c r="E36" s="70" t="inlineStr">
-        <is>
-          <t>BOX運用を前提に保存・検索機能を必須化</t>
-        </is>
-      </c>
-      <c r="G36" s="70" t="inlineStr">
-        <is>
-          <t>機能を厚めに実装する対応であり、実態が違っても問題は生じにくい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1" s="48">
-      <c r="B37" s="70" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C37" s="69" t="inlineStr">
-        <is>
-          <t>C-31</t>
-        </is>
-      </c>
-      <c r="D37" s="70" t="inlineStr">
-        <is>
-          <t>確定・ロックの概念</t>
-        </is>
-      </c>
-      <c r="E37" s="70" t="inlineStr">
-        <is>
-          <t>本社が確定・ロックを行っている</t>
-        </is>
-      </c>
-      <c r="G37" s="70" t="inlineStr">
-        <is>
-          <t>本社主導の統制であり、拠点側の実態に依存しない。</t>
         </is>
       </c>
     </row>
@@ -13307,22 +13398,22 @@
       </c>
       <c r="C38" s="69" t="inlineStr">
         <is>
-          <t>C-34</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D38" s="70" t="inlineStr">
         <is>
-          <t>スマートメーター等の有無</t>
+          <t>手順書の有無</t>
         </is>
       </c>
       <c r="E38" s="70" t="inlineStr">
         <is>
-          <t>自動計測は対象外、OCR検討に振替</t>
+          <t>両拠点とも手順書なしで一致</t>
         </is>
       </c>
       <c r="G38" s="70" t="inlineStr">
         <is>
-          <t>意図的なスコープ決定であり、機会損失は自覚的に受容されている。</t>
+          <t>仮に手順書がある拠点があっても、被る不利益は個別ヒアリングの手間程度で小さい。</t>
         </is>
       </c>
     </row>
@@ -13334,373 +13425,373 @@
       </c>
       <c r="C39" s="69" t="inlineStr">
         <is>
-          <t>C-37</t>
+          <t>C-09</t>
         </is>
       </c>
       <c r="D39" s="70" t="inlineStr">
         <is>
-          <t>属人化の有無</t>
+          <t>証憑の保管形式</t>
         </is>
       </c>
       <c r="E39" s="70" t="inlineStr">
         <is>
-          <t>一部属人化前提でマニュアル整備を要件化</t>
+          <t>PDF・Excelが中心と把握</t>
         </is>
       </c>
       <c r="G39" s="70" t="inlineStr">
         <is>
-          <t>保守的な前提で対応するため、実態が多少違っても支障は小さい。</t>
+          <t>低リスク。仮に紙中心の拠点があっても保管容量を多めに見ておけば対応可能。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="34" customHeight="1" s="48">
       <c r="B40" s="70" t="inlineStr">
         <is>
-          <t>4.難所チェック</t>
+          <t>3.コア設問</t>
         </is>
       </c>
       <c r="C40" s="69" t="inlineStr">
         <is>
-          <t>10-06</t>
+          <t>C-13</t>
         </is>
       </c>
       <c r="D40" s="70" t="inlineStr">
         <is>
-          <t>抜け漏れの構造的発生</t>
+          <t>変更履歴の有無</t>
         </is>
       </c>
       <c r="E40" s="70" t="inlineStr">
         <is>
-          <t>未然防止でなく事後の早期修正で担保</t>
+          <t>変更履歴を必須要件として確定</t>
         </is>
       </c>
       <c r="G40" s="70" t="inlineStr">
         <is>
-          <t>リスクを無視せず、別の仕組み（早期修正）で正面から対応している。</t>
+          <t>履歴機能を全拠点前提で実装するため、実態が違っても上位互換で吸収できる。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="34" customHeight="1" s="48">
       <c r="B41" s="70" t="inlineStr">
         <is>
-          <t>4.難所チェック</t>
+          <t>3.コア設問</t>
         </is>
       </c>
       <c r="C41" s="69" t="inlineStr">
         <is>
-          <t>10-07</t>
+          <t>C-23</t>
         </is>
       </c>
       <c r="D41" s="70" t="inlineStr">
         <is>
-          <t>単位換算・按分の計算ミス</t>
+          <t>抜け漏れ・遅延の主な原因</t>
         </is>
       </c>
       <c r="E41" s="70" t="inlineStr">
         <is>
-          <t>実績（毎年1〜2拠点で発生）を閾値設計に反映</t>
+          <t>5つの原因を要件に反映</t>
         </is>
       </c>
       <c r="G41" s="70" t="inlineStr">
         <is>
-          <t>エビデンスに基づく設計判断。</t>
+          <t>汎用的な原因（アラート視認性、単位換算、年始重なり等）で妥当性が高い。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="34" customHeight="1" s="48">
       <c r="B42" s="70" t="inlineStr">
         <is>
-          <t>4.難所チェック</t>
+          <t>3.コア設問</t>
         </is>
       </c>
       <c r="C42" s="69" t="inlineStr">
         <is>
-          <t>10-08</t>
+          <t>C-27</t>
         </is>
       </c>
       <c r="D42" s="70" t="inlineStr">
         <is>
-          <t>異常値照会の往復</t>
+          <t>妥当性チェック方法</t>
         </is>
       </c>
       <c r="E42" s="70" t="inlineStr">
         <is>
-          <t>異常値照会機能を優先度高い要件とする</t>
+          <t>標準閾値はESG企画室が設定</t>
         </is>
       </c>
       <c r="G42" s="70" t="inlineStr">
         <is>
-          <t>リスクを認識した上で機能として正面から対応している。</t>
+          <t>現状の拠点実態に関わらず、今後の方針として妥当な決定。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1" s="48">
       <c r="B43" s="70" t="inlineStr">
         <is>
-          <t>4.難所チェック</t>
+          <t>3.コア設問</t>
         </is>
       </c>
       <c r="C43" s="69" t="inlineStr">
         <is>
-          <t>10-09</t>
+          <t>C-29</t>
         </is>
       </c>
       <c r="D43" s="70" t="inlineStr">
         <is>
-          <t>再計算への不安</t>
+          <t>証憑を探す時間</t>
         </is>
       </c>
       <c r="E43" s="70" t="inlineStr">
         <is>
-          <t>拠点は計算していないため本社機能として設計</t>
+          <t>BOX運用を前提に保存・検索機能を必須化</t>
         </is>
       </c>
       <c r="G43" s="70" t="inlineStr">
         <is>
-          <t>C-06が引き続き生きた設問として残り、実態と異なる拠点があれば別途捕捉される安全網がある。</t>
+          <t>機能を厚めに実装する対応であり、実態が違っても問題は生じにくい。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="34" customHeight="1" s="48">
       <c r="B44" s="70" t="inlineStr">
         <is>
-          <t>4.難所チェック</t>
+          <t>3.コア設問</t>
         </is>
       </c>
       <c r="C44" s="69" t="inlineStr">
         <is>
-          <t>10-11</t>
+          <t>C-31</t>
         </is>
       </c>
       <c r="D44" s="70" t="inlineStr">
         <is>
-          <t>証拠探しの負荷</t>
+          <t>確定・ロックの概念</t>
         </is>
       </c>
       <c r="E44" s="70" t="inlineStr">
         <is>
-          <t>国内浸透・海外未浸透を移行計画の前提</t>
+          <t>本社が確定・ロックを行っている</t>
         </is>
       </c>
       <c r="G44" s="70" t="inlineStr">
         <is>
-          <t>結果に誤りがあっても移行期間の見積り誤差程度で、影響は軽微。</t>
+          <t>本社主導の統制であり、拠点側の実態に依存しない。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1" s="48">
       <c r="B45" s="70" t="inlineStr">
         <is>
-          <t>4.難所チェック</t>
+          <t>3.コア設問</t>
         </is>
       </c>
       <c r="C45" s="69" t="inlineStr">
         <is>
-          <t>10-12</t>
+          <t>C-34</t>
         </is>
       </c>
       <c r="D45" s="70" t="inlineStr">
         <is>
-          <t>フィードバック機能の要否</t>
+          <t>スマートメーター等の有無</t>
         </is>
       </c>
       <c r="E45" s="70" t="inlineStr">
         <is>
-          <t>費用対効果で判断する保留項目として整理</t>
+          <t>自動計測は対象外、OCR検討に振替</t>
         </is>
       </c>
       <c r="G45" s="70" t="inlineStr">
         <is>
-          <t>無視ではなく先送りの判断であり妥当。</t>
+          <t>意図的なスコープ決定であり、機会損失は自覚的に受容されている。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="34" customHeight="1" s="48">
       <c r="B46" s="70" t="inlineStr">
         <is>
-          <t>5.選抜拠点ヒアリング</t>
+          <t>3.コア設問</t>
         </is>
       </c>
       <c r="C46" s="69" t="inlineStr">
         <is>
-          <t>H3-01</t>
+          <t>C-37</t>
         </is>
       </c>
       <c r="D46" s="70" t="inlineStr">
         <is>
-          <t>手順書の形式等</t>
+          <t>属人化の有無</t>
         </is>
       </c>
       <c r="E46" s="70" t="inlineStr">
         <is>
-          <t>システム入力マニュアル以外の手順書はない</t>
+          <t>一部属人化前提でマニュアル整備を要件化</t>
         </is>
       </c>
       <c r="G46" s="70" t="inlineStr">
         <is>
-          <t>C-01と同様、低リスク。</t>
+          <t>保守的な前提で対応するため、実態が多少違っても支障は小さい。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1" s="48">
       <c r="B47" s="70" t="inlineStr">
         <is>
-          <t>5.選抜拠点ヒアリング</t>
+          <t>4.難所チェック</t>
         </is>
       </c>
       <c r="C47" s="69" t="inlineStr">
         <is>
-          <t>H3-02</t>
+          <t>10-06</t>
         </is>
       </c>
       <c r="D47" s="70" t="inlineStr">
         <is>
-          <t>手順書と実態の乖離</t>
+          <t>抜け漏れの構造的発生</t>
         </is>
       </c>
       <c r="E47" s="70" t="inlineStr">
         <is>
-          <t>手順書がないため明文化を導入時タスクに含める</t>
+          <t>未然防止でなく事後の早期修正で担保</t>
         </is>
       </c>
       <c r="G47" s="70" t="inlineStr">
         <is>
-          <t>対応がリスクを正面から解消している。</t>
+          <t>リスクを無視せず、別の仕組み（早期修正）で正面から対応している。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="34" customHeight="1" s="48">
       <c r="B48" s="70" t="inlineStr">
         <is>
-          <t>5.選抜拠点ヒアリング</t>
+          <t>4.難所チェック</t>
         </is>
       </c>
       <c r="C48" s="69" t="inlineStr">
         <is>
-          <t>H3-06</t>
+          <t>10-07</t>
         </is>
       </c>
       <c r="D48" s="70" t="inlineStr">
         <is>
-          <t>データ欠測の穴埋め方法</t>
+          <t>単位換算・按分の計算ミス</t>
         </is>
       </c>
       <c r="E48" s="70" t="inlineStr">
         <is>
-          <t>欠測は例外的としシステム外の補完を許容</t>
+          <t>実績（毎年1〜2拠点で発生）を閾値設計に反映</t>
         </is>
       </c>
       <c r="G48" s="70" t="inlineStr">
         <is>
-          <t>例外処理を許容する設計判断で妥当。</t>
+          <t>エビデンスに基づく設計判断。</t>
         </is>
       </c>
     </row>
     <row r="49" ht="34" customHeight="1" s="48">
       <c r="B49" s="70" t="inlineStr">
         <is>
-          <t>5.選抜拠点ヒアリング</t>
+          <t>4.難所チェック</t>
         </is>
       </c>
       <c r="C49" s="69" t="inlineStr">
         <is>
-          <t>H3-09</t>
+          <t>10-08</t>
         </is>
       </c>
       <c r="D49" s="70" t="inlineStr">
         <is>
-          <t>複数報告間の食い違い</t>
+          <t>異常値照会の往復</t>
         </is>
       </c>
       <c r="E49" s="70" t="inlineStr">
         <is>
-          <t>多目的出力を要件化、様式変更対応は別途調整</t>
+          <t>異常値照会機能を優先度高い要件とする</t>
         </is>
       </c>
       <c r="G49" s="70" t="inlineStr">
         <is>
-          <t>主要リスク（数値不整合）は要件化で解消。CDP対応のみ先送り。</t>
+          <t>リスクを認識した上で機能として正面から対応している。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="34" customHeight="1" s="48">
       <c r="B50" s="70" t="inlineStr">
         <is>
-          <t>5.選抜拠点ヒアリング</t>
+          <t>4.難所チェック</t>
         </is>
       </c>
       <c r="C50" s="69" t="inlineStr">
         <is>
-          <t>H4-02</t>
+          <t>10-09</t>
         </is>
       </c>
       <c r="D50" s="70" t="inlineStr">
         <is>
-          <t>係数更新時の再計算</t>
+          <t>再計算への不安</t>
         </is>
       </c>
       <c r="E50" s="70" t="inlineStr">
         <is>
-          <t>更新・再計算可能性を要件に反映（保守的）</t>
+          <t>拠点は計算していないため本社機能として設計</t>
         </is>
       </c>
       <c r="G50" s="70" t="inlineStr">
         <is>
-          <t>機能を厚めに実装する対応で妥当。</t>
+          <t>C-06が引き続き生きた設問として残り、実態と異なる拠点があれば別途捕捉される安全網がある。</t>
         </is>
       </c>
     </row>
     <row r="51" ht="34" customHeight="1" s="48">
       <c r="B51" s="70" t="inlineStr">
         <is>
-          <t>5.選抜拠点ヒアリング</t>
+          <t>4.難所チェック</t>
         </is>
       </c>
       <c r="C51" s="69" t="inlineStr">
         <is>
-          <t>H4-03</t>
+          <t>10-11</t>
         </is>
       </c>
       <c r="D51" s="70" t="inlineStr">
         <is>
-          <t>按分の管理者・根拠資料</t>
+          <t>証拠探しの負荷</t>
         </is>
       </c>
       <c r="E51" s="70" t="inlineStr">
         <is>
-          <t>対象拠点・項目の一覧をESG企画室が提示</t>
+          <t>国内浸透・海外未浸透を移行計画の前提</t>
         </is>
       </c>
       <c r="G51" s="70" t="inlineStr">
         <is>
-          <t>情報源の変更であり、ESG企画室が確実に提示すれば問題ない（運用上のToDoとして管理）。</t>
+          <t>結果に誤りがあっても移行期間の見積り誤差程度で、影響は軽微。</t>
         </is>
       </c>
     </row>
     <row r="52" ht="34" customHeight="1" s="48">
       <c r="B52" s="70" t="inlineStr">
         <is>
-          <t>5.選抜拠点ヒアリング</t>
+          <t>4.難所チェック</t>
         </is>
       </c>
       <c r="C52" s="69" t="inlineStr">
         <is>
-          <t>H4-04</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="D52" s="70" t="inlineStr">
         <is>
-          <t>按分基準の見直し頻度</t>
+          <t>フィードバック機能の要否</t>
         </is>
       </c>
       <c r="E52" s="70" t="inlineStr">
         <is>
-          <t>按分基準は年度ごとに保持する設計</t>
+          <t>費用対効果で判断する保留項目として整理</t>
         </is>
       </c>
       <c r="G52" s="70" t="inlineStr">
         <is>
-          <t>保守的な設計で妥当。</t>
+          <t>無視ではなく先送りの判断であり妥当。</t>
         </is>
       </c>
     </row>
@@ -13712,22 +13803,22 @@
       </c>
       <c r="C53" s="69" t="inlineStr">
         <is>
-          <t>H4-12</t>
+          <t>H3-01</t>
         </is>
       </c>
       <c r="D53" s="70" t="inlineStr">
         <is>
-          <t>製品LCA用データ</t>
+          <t>手順書の形式等</t>
         </is>
       </c>
       <c r="E53" s="70" t="inlineStr">
         <is>
-          <t>ESG企画室との事前決定待ち、決定まで対象外</t>
+          <t>システム入力マニュアル以外の手順書はない</t>
         </is>
       </c>
       <c r="G53" s="70" t="inlineStr">
         <is>
-          <t>意思決定プロセスを踏んだ先送りであり妥当。</t>
+          <t>C-01と同様、低リスク。</t>
         </is>
       </c>
     </row>
@@ -13739,22 +13830,22 @@
       </c>
       <c r="C54" s="69" t="inlineStr">
         <is>
-          <t>H4-13</t>
+          <t>H3-02</t>
         </is>
       </c>
       <c r="D54" s="70" t="inlineStr">
         <is>
-          <t>人事・安全データの拠点独自解釈</t>
+          <t>手順書と実態の乖離</t>
         </is>
       </c>
       <c r="E54" s="70" t="inlineStr">
         <is>
-          <t>本社側の指標定義の問題として整理</t>
+          <t>手順書がないため明文化を導入時タスクに含める</t>
         </is>
       </c>
       <c r="G54" s="70" t="inlineStr">
         <is>
-          <t>対応の道筋が明確で妥当。</t>
+          <t>対応がリスクを正面から解消している。</t>
         </is>
       </c>
     </row>
@@ -13766,22 +13857,22 @@
       </c>
       <c r="C55" s="69" t="inlineStr">
         <is>
-          <t>H5-02</t>
+          <t>H3-06</t>
         </is>
       </c>
       <c r="D55" s="70" t="inlineStr">
         <is>
-          <t>保存年限</t>
+          <t>データ欠測の穴埋め方法</t>
         </is>
       </c>
       <c r="E55" s="70" t="inlineStr">
         <is>
-          <t>ESG企画室と決定のうえシステム要件に反映</t>
+          <t>欠測は例外的としシステム外の補完を許容</t>
         </is>
       </c>
       <c r="G55" s="70" t="inlineStr">
         <is>
-          <t>意思決定プロセスを踏んだ判断であり妥当。</t>
+          <t>例外処理を許容する設計判断で妥当。</t>
         </is>
       </c>
     </row>
@@ -13793,22 +13884,22 @@
       </c>
       <c r="C56" s="69" t="inlineStr">
         <is>
-          <t>H5-04</t>
+          <t>H3-09</t>
         </is>
       </c>
       <c r="D56" s="70" t="inlineStr">
         <is>
-          <t>第三者保有証憑の入手性</t>
+          <t>複数報告間の食い違い</t>
         </is>
       </c>
       <c r="E56" s="70" t="inlineStr">
         <is>
-          <t>請求ありは入手可、なしは推定・除外</t>
+          <t>多目的出力を要件化、様式変更対応は別途調整</t>
         </is>
       </c>
       <c r="G56" s="70" t="inlineStr">
         <is>
-          <t>明確な運用ルールとして妥当。</t>
+          <t>主要リスク（数値不整合）は要件化で解消。CDP対応のみ先送り。</t>
         </is>
       </c>
     </row>
@@ -13820,22 +13911,22 @@
       </c>
       <c r="C57" s="69" t="inlineStr">
         <is>
-          <t>H5-06</t>
+          <t>H4-02</t>
         </is>
       </c>
       <c r="D57" s="70" t="inlineStr">
         <is>
-          <t>過去の指摘事項の記録所在</t>
+          <t>係数更新時の再計算</t>
         </is>
       </c>
       <c r="E57" s="70" t="inlineStr">
         <is>
-          <t>ESG企画室の共有フォルダにあると把握</t>
+          <t>更新・再計算可能性を要件に反映（保守的）</t>
         </is>
       </c>
       <c r="G57" s="70" t="inlineStr">
         <is>
-          <t>監査対応は通常ESG企画室が集約する業務であり、妥当性が高い。</t>
+          <t>機能を厚めに実装する対応で妥当。</t>
         </is>
       </c>
     </row>
@@ -13847,22 +13938,22 @@
       </c>
       <c r="C58" s="69" t="inlineStr">
         <is>
-          <t>H6-01</t>
+          <t>H4-03</t>
         </is>
       </c>
       <c r="D58" s="70" t="inlineStr">
         <is>
-          <t>チェック記録の有無</t>
+          <t>按分の管理者・根拠資料</t>
         </is>
       </c>
       <c r="E58" s="70" t="inlineStr">
         <is>
-          <t>証跡はシステム内に残す前提とする</t>
+          <t>対象拠点・項目の一覧をESG企画室が提示</t>
         </is>
       </c>
       <c r="G58" s="70" t="inlineStr">
         <is>
-          <t>機能を厚めに実装する対応で妥当。</t>
+          <t>情報源の変更であり、ESG企画室が確実に提示すれば問題ない（運用上のToDoとして管理）。</t>
         </is>
       </c>
     </row>
@@ -13874,22 +13965,22 @@
       </c>
       <c r="C59" s="69" t="inlineStr">
         <is>
-          <t>H6-03</t>
+          <t>H4-04</t>
         </is>
       </c>
       <c r="D59" s="70" t="inlineStr">
         <is>
-          <t>入力ミスの流出経験</t>
+          <t>按分基準の見直し頻度</t>
         </is>
       </c>
       <c r="E59" s="70" t="inlineStr">
         <is>
-          <t>現行の修正要否確認プロセスを維持</t>
+          <t>按分基準は年度ごとに保持する設計</t>
         </is>
       </c>
       <c r="G59" s="70" t="inlineStr">
         <is>
-          <t>既存の安全策を維持する保守的判断。</t>
+          <t>保守的な設計で妥当。</t>
         </is>
       </c>
     </row>
@@ -13901,22 +13992,22 @@
       </c>
       <c r="C60" s="69" t="inlineStr">
         <is>
-          <t>H6-04</t>
+          <t>H4-12</t>
         </is>
       </c>
       <c r="D60" s="70" t="inlineStr">
         <is>
-          <t>拠点長の関与頻度</t>
+          <t>製品LCA用データ</t>
         </is>
       </c>
       <c r="E60" s="70" t="inlineStr">
         <is>
-          <t>承認者ルールは事務局で設計し拠点へ説明</t>
+          <t>ESG企画室との事前決定待ち、決定まで対象外</t>
         </is>
       </c>
       <c r="G60" s="70" t="inlineStr">
         <is>
-          <t>トップダウンの設計方針として妥当。</t>
+          <t>意思決定プロセスを踏んだ先送りであり妥当。</t>
         </is>
       </c>
     </row>
@@ -13928,22 +14019,22 @@
       </c>
       <c r="C61" s="69" t="inlineStr">
         <is>
-          <t>H6-07</t>
+          <t>H4-13</t>
         </is>
       </c>
       <c r="D61" s="70" t="inlineStr">
         <is>
-          <t>内部監査・ISO審査の指摘内容</t>
+          <t>人事・安全データの拠点独自解釈</t>
         </is>
       </c>
       <c r="E61" s="70" t="inlineStr">
         <is>
-          <t>ISO監査は数値誤りを対象外として整理</t>
+          <t>本社側の指標定義の問題として整理</t>
         </is>
       </c>
       <c r="G61" s="70" t="inlineStr">
         <is>
-          <t>一般的にISO14001は運用プロセスの適合性を見るものであり、数値精度の検証はSGS等の第三者保証が担う。理由は妥当。</t>
+          <t>対応の道筋が明確で妥当。</t>
         </is>
       </c>
     </row>
@@ -13955,22 +14046,22 @@
       </c>
       <c r="C62" s="69" t="inlineStr">
         <is>
-          <t>H7-03</t>
+          <t>H5-02</t>
         </is>
       </c>
       <c r="D62" s="70" t="inlineStr">
         <is>
-          <t>子メーターの設置状況</t>
+          <t>保存年限</t>
         </is>
       </c>
       <c r="E62" s="70" t="inlineStr">
         <is>
-          <t>拠点単位で足りるとし部門別粒度は対象外</t>
+          <t>ESG企画室と決定のうえシステム要件に反映</t>
         </is>
       </c>
       <c r="G62" s="70" t="inlineStr">
         <is>
-          <t>意図的なスコープ決定で妥当。</t>
+          <t>意思決定プロセスを踏んだ判断であり妥当。</t>
         </is>
       </c>
     </row>
@@ -13982,22 +14073,22 @@
       </c>
       <c r="C63" s="69" t="inlineStr">
         <is>
-          <t>H7-04</t>
+          <t>H5-04</t>
         </is>
       </c>
       <c r="D63" s="70" t="inlineStr">
         <is>
-          <t>ITサポート体制</t>
+          <t>第三者保有証憑の入手性</t>
         </is>
       </c>
       <c r="E63" s="70" t="inlineStr">
         <is>
-          <t>現地IT支援は期待せず本社リモート支援を計画</t>
+          <t>請求ありは入手可、なしは推定・除外</t>
         </is>
       </c>
       <c r="G63" s="70" t="inlineStr">
         <is>
-          <t>最悪ケースを前提にした保守的な計画で妥当。</t>
+          <t>明確な運用ルールとして妥当。</t>
         </is>
       </c>
     </row>
@@ -14009,22 +14100,22 @@
       </c>
       <c r="C64" s="69" t="inlineStr">
         <is>
-          <t>H8-01</t>
+          <t>H5-06</t>
         </is>
       </c>
       <c r="D64" s="70" t="inlineStr">
         <is>
-          <t>本社照会・差し戻し件数</t>
+          <t>過去の指摘事項の記録所在</t>
         </is>
       </c>
       <c r="E64" s="70" t="inlineStr">
         <is>
-          <t>把握済みの実績値を効果試算の基準値とする</t>
+          <t>ESG企画室の共有フォルダにあると把握</t>
         </is>
       </c>
       <c r="G64" s="70" t="inlineStr">
         <is>
-          <t>実データに基づく判断で妥当。</t>
+          <t>監査対応は通常ESG企画室が集約する業務であり、妥当性が高い。</t>
         </is>
       </c>
     </row>
@@ -14036,22 +14127,22 @@
       </c>
       <c r="C65" s="69" t="inlineStr">
         <is>
-          <t>H8-02</t>
+          <t>H6-01</t>
         </is>
       </c>
       <c r="D65" s="70" t="inlineStr">
         <is>
-          <t>業務関与人数・兼務状況</t>
+          <t>チェック記録の有無</t>
         </is>
       </c>
       <c r="E65" s="70" t="inlineStr">
         <is>
-          <t>Scope1・2で3名を前提にライセンス数を試算</t>
+          <t>証跡はシステム内に残す前提とする</t>
         </is>
       </c>
       <c r="G65" s="70" t="inlineStr">
         <is>
-          <t>Scope3を含める場合の見直しを自ら明記しており、リスクを認識した上での判断。</t>
+          <t>機能を厚めに実装する対応で妥当。</t>
         </is>
       </c>
     </row>
@@ -14063,22 +14154,22 @@
       </c>
       <c r="C66" s="69" t="inlineStr">
         <is>
-          <t>H9-03</t>
+          <t>H6-03</t>
         </is>
       </c>
       <c r="D66" s="70" t="inlineStr">
         <is>
-          <t>CSRD等の追加開示要求</t>
+          <t>入力ミスの流出経験</t>
         </is>
       </c>
       <c r="E66" s="70" t="inlineStr">
         <is>
-          <t>オーストラリア子会社分を将来要件として記録</t>
+          <t>現行の修正要否確認プロセスを維持</t>
         </is>
       </c>
       <c r="G66" s="70" t="inlineStr">
         <is>
-          <t>判明した事実を無視せず要件に反映しており妥当。</t>
+          <t>既存の安全策を維持する保守的判断。</t>
         </is>
       </c>
     </row>
@@ -14090,45 +14181,612 @@
       </c>
       <c r="C67" s="69" t="inlineStr">
         <is>
+          <t>H6-04</t>
+        </is>
+      </c>
+      <c r="D67" s="70" t="inlineStr">
+        <is>
+          <t>拠点長の関与頻度</t>
+        </is>
+      </c>
+      <c r="E67" s="70" t="inlineStr">
+        <is>
+          <t>承認者ルールは事務局で設計し拠点へ説明</t>
+        </is>
+      </c>
+      <c r="G67" s="70" t="inlineStr">
+        <is>
+          <t>トップダウンの設計方針として妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="34" customHeight="1" s="48">
+      <c r="B68" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C68" s="69" t="inlineStr">
+        <is>
+          <t>H6-07</t>
+        </is>
+      </c>
+      <c r="D68" s="70" t="inlineStr">
+        <is>
+          <t>内部監査・ISO審査の指摘内容</t>
+        </is>
+      </c>
+      <c r="E68" s="70" t="inlineStr">
+        <is>
+          <t>ISO監査は数値誤りを対象外として整理</t>
+        </is>
+      </c>
+      <c r="G68" s="70" t="inlineStr">
+        <is>
+          <t>一般的にISO14001は運用プロセスの適合性を見るものであり、数値精度の検証はSGS等の第三者保証が担う。理由は妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="34" customHeight="1" s="48">
+      <c r="B69" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C69" s="69" t="inlineStr">
+        <is>
+          <t>H7-03</t>
+        </is>
+      </c>
+      <c r="D69" s="70" t="inlineStr">
+        <is>
+          <t>子メーターの設置状況</t>
+        </is>
+      </c>
+      <c r="E69" s="70" t="inlineStr">
+        <is>
+          <t>拠点単位で足りるとし部門別粒度は対象外</t>
+        </is>
+      </c>
+      <c r="G69" s="70" t="inlineStr">
+        <is>
+          <t>意図的なスコープ決定で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="34" customHeight="1" s="48">
+      <c r="B70" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C70" s="69" t="inlineStr">
+        <is>
+          <t>H7-04</t>
+        </is>
+      </c>
+      <c r="D70" s="70" t="inlineStr">
+        <is>
+          <t>ITサポート体制</t>
+        </is>
+      </c>
+      <c r="E70" s="70" t="inlineStr">
+        <is>
+          <t>現地IT支援は期待せず本社リモート支援を計画</t>
+        </is>
+      </c>
+      <c r="G70" s="70" t="inlineStr">
+        <is>
+          <t>最悪ケースを前提にした保守的な計画で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="34" customHeight="1" s="48">
+      <c r="B71" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C71" s="69" t="inlineStr">
+        <is>
+          <t>H8-01</t>
+        </is>
+      </c>
+      <c r="D71" s="70" t="inlineStr">
+        <is>
+          <t>本社照会・差し戻し件数</t>
+        </is>
+      </c>
+      <c r="E71" s="70" t="inlineStr">
+        <is>
+          <t>把握済みの実績値を効果試算の基準値とする</t>
+        </is>
+      </c>
+      <c r="G71" s="70" t="inlineStr">
+        <is>
+          <t>実データに基づく判断で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="34" customHeight="1" s="48">
+      <c r="B72" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C72" s="69" t="inlineStr">
+        <is>
+          <t>H8-02</t>
+        </is>
+      </c>
+      <c r="D72" s="70" t="inlineStr">
+        <is>
+          <t>業務関与人数・兼務状況</t>
+        </is>
+      </c>
+      <c r="E72" s="70" t="inlineStr">
+        <is>
+          <t>Scope1・2で3名を前提にライセンス数を試算</t>
+        </is>
+      </c>
+      <c r="G72" s="70" t="inlineStr">
+        <is>
+          <t>Scope3を含める場合の見直しを自ら明記しており、リスクを認識した上での判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="34" customHeight="1" s="48">
+      <c r="B73" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C73" s="69" t="inlineStr">
+        <is>
+          <t>H9-03</t>
+        </is>
+      </c>
+      <c r="D73" s="70" t="inlineStr">
+        <is>
+          <t>CSRD等の追加開示要求</t>
+        </is>
+      </c>
+      <c r="E73" s="70" t="inlineStr">
+        <is>
+          <t>オーストラリア子会社分を将来要件として記録</t>
+        </is>
+      </c>
+      <c r="G73" s="70" t="inlineStr">
+        <is>
+          <t>判明した事実を無視せず要件に反映しており妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="34" customHeight="1" s="48">
+      <c r="B74" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C74" s="69" t="inlineStr">
+        <is>
           <t>H9-06</t>
         </is>
       </c>
-      <c r="D67" s="70" t="inlineStr">
+      <c r="D74" s="70" t="inlineStr">
         <is>
           <t>現地委託先データの入手性</t>
         </is>
       </c>
-      <c r="E67" s="70" t="inlineStr">
+      <c r="E74" s="70" t="inlineStr">
         <is>
           <t>取れないデータは推定・除外する原則</t>
         </is>
       </c>
-      <c r="G67" s="70" t="inlineStr">
+      <c r="G74" s="70" t="inlineStr">
         <is>
           <t>明確な運用ルールとして妥当。</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="22" customHeight="1" s="48">
-      <c r="A69" s="77" t="inlineStr">
-        <is>
-          <t>【集計】60件レビュー ／ 削除に同意 37件 ／ 要注意 23件（うち理由不十分・誤り＝7件、理由は妥当だがリスク残存＝16件）</t>
-        </is>
-      </c>
-      <c r="B69" s="78" t="n"/>
-      <c r="C69" s="78" t="n"/>
-      <c r="D69" s="78" t="n"/>
-      <c r="E69" s="78" t="n"/>
-      <c r="F69" s="78" t="n"/>
-      <c r="G69" s="78" t="n"/>
-      <c r="H69" s="78" t="n"/>
+    <row r="75" ht="34" customHeight="1" s="48">
+      <c r="B75" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C75" s="69" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="D75" s="70" t="inlineStr">
+        <is>
+          <t>報告後のデータ修正頻度</t>
+        </is>
+      </c>
+      <c r="E75" s="70" t="inlineStr">
+        <is>
+          <t>算定前の桁間違い修正が毎年発生する実態を踏まえ修正機能を実装前提化</t>
+        </is>
+      </c>
+      <c r="G75" s="70" t="inlineStr">
+        <is>
+          <t>機能を厚めに実装する対応であり妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="34" customHeight="1" s="48">
+      <c r="B76" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C76" s="69" t="inlineStr">
+        <is>
+          <t>C-05</t>
+        </is>
+      </c>
+      <c r="D76" s="70" t="inlineStr">
+        <is>
+          <t>主担当不在時の報告継続性</t>
+        </is>
+      </c>
+      <c r="E76" s="70" t="inlineStr">
+        <is>
+          <t>1拠点でも止まると全体が遅れるため代理承認を実装前提化</t>
+        </is>
+      </c>
+      <c r="G76" s="70" t="inlineStr">
+        <is>
+          <t>保守的な機能実装で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="34" customHeight="1" s="48">
+      <c r="B77" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C77" s="69" t="inlineStr">
+        <is>
+          <t>C-10</t>
+        </is>
+      </c>
+      <c r="D77" s="70" t="inlineStr">
+        <is>
+          <t>証憑への遡及可能性</t>
+        </is>
+      </c>
+      <c r="E77" s="70" t="inlineStr">
+        <is>
+          <t>保存年限決定後に判断し、必要な場合は事前相談する段階的対応</t>
+        </is>
+      </c>
+      <c r="G77" s="70" t="inlineStr">
+        <is>
+          <t>意思決定プロセスを踏んだ判断で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="34" customHeight="1" s="48">
+      <c r="B78" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C78" s="69" t="inlineStr">
+        <is>
+          <t>C-19</t>
+        </is>
+      </c>
+      <c r="D78" s="70" t="inlineStr">
+        <is>
+          <t>多言語UI・現地サポートなしでの運用可否</t>
+        </is>
+      </c>
+      <c r="E78" s="70" t="inlineStr">
+        <is>
+          <t>多言語対応をRFPに含める前提で設計</t>
+        </is>
+      </c>
+      <c r="G78" s="70" t="inlineStr">
+        <is>
+          <t>機能を厚めに実装する対応で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="34" customHeight="1" s="48">
+      <c r="B79" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C79" s="69" t="inlineStr">
+        <is>
+          <t>C-20</t>
+        </is>
+      </c>
+      <c r="D79" s="70" t="inlineStr">
+        <is>
+          <t>月次で最も時間がかかるステップ</t>
+        </is>
+      </c>
+      <c r="E79" s="70" t="inlineStr">
+        <is>
+          <t>ステップ案をESG室へ確認する対応に切替</t>
+        </is>
+      </c>
+      <c r="G79" s="70" t="inlineStr">
+        <is>
+          <t>全拠点調査の代替として合理的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="34" customHeight="1" s="48">
+      <c r="B80" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C80" s="69" t="inlineStr">
+        <is>
+          <t>C-24</t>
+        </is>
+      </c>
+      <c r="D80" s="70" t="inlineStr">
+        <is>
+          <t>過年度データの遡及修正経験</t>
+        </is>
+      </c>
+      <c r="E80" s="70" t="inlineStr">
+        <is>
+          <t>過年度修正機能を要件に含める方向</t>
+        </is>
+      </c>
+      <c r="G80" s="70" t="inlineStr">
+        <is>
+          <t>機能を厚めに実装する対応で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="34" customHeight="1" s="48">
+      <c r="B81" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C81" s="69" t="inlineStr">
+        <is>
+          <t>C-25</t>
+        </is>
+      </c>
+      <c r="D81" s="70" t="inlineStr">
+        <is>
+          <t>単位換算・按分の実施有無</t>
+        </is>
+      </c>
+      <c r="E81" s="70" t="inlineStr">
+        <is>
+          <t>換算・按分をシステム側で行う基本方針</t>
+        </is>
+      </c>
+      <c r="G81" s="70" t="inlineStr">
+        <is>
+          <t>機能を厚めに実装する対応で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="34" customHeight="1" s="48">
+      <c r="B82" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C82" s="69" t="inlineStr">
+        <is>
+          <t>C-36</t>
+        </is>
+      </c>
+      <c r="D82" s="70" t="inlineStr">
+        <is>
+          <t>電子承認の導入有無</t>
+        </is>
+      </c>
+      <c r="E82" s="70" t="inlineStr">
+        <is>
+          <t>入力担当者向けでなくシステム担当者向けの技術確認事項として切り出し</t>
+        </is>
+      </c>
+      <c r="G82" s="70" t="inlineStr">
+        <is>
+          <t>質問対象の適正化として妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="34" customHeight="1" s="48">
+      <c r="B83" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C83" s="69" t="inlineStr">
+        <is>
+          <t>H5-05</t>
+        </is>
+      </c>
+      <c r="D83" s="70" t="inlineStr">
+        <is>
+          <t>記録引継ぎの実態</t>
+        </is>
+      </c>
+      <c r="E83" s="70" t="inlineStr">
+        <is>
+          <t>本社からデータ・証憑を明示する方式に切替</t>
+        </is>
+      </c>
+      <c r="G83" s="70" t="inlineStr">
+        <is>
+          <t>別の仕組みで正面から対応しており妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="34" customHeight="1" s="48">
+      <c r="B84" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C84" s="69" t="inlineStr">
+        <is>
+          <t>H5-07</t>
+        </is>
+      </c>
+      <c r="D84" s="70" t="inlineStr">
+        <is>
+          <t>改ざん防止の仕組み</t>
+        </is>
+      </c>
+      <c r="E84" s="70" t="inlineStr">
+        <is>
+          <t>権限分離・確定ロック・変更履歴としてシステム側で担保</t>
+        </is>
+      </c>
+      <c r="G84" s="70" t="inlineStr">
+        <is>
+          <t>機能を厚めに実装する対応で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="34" customHeight="1" s="48">
+      <c r="B85" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C85" s="69" t="inlineStr">
+        <is>
+          <t>H6-08</t>
+        </is>
+      </c>
+      <c r="D85" s="70" t="inlineStr">
+        <is>
+          <t>データ信頼性のヒヤリ経験</t>
+        </is>
+      </c>
+      <c r="E85" s="70" t="inlineStr">
+        <is>
+          <t>自己申告でなく本社側の指摘・修正記録から傾向を把握</t>
+        </is>
+      </c>
+      <c r="G85" s="70" t="inlineStr">
+        <is>
+          <t>客観的データへの切替で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="34" customHeight="1" s="48">
+      <c r="B86" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C86" s="69" t="inlineStr">
+        <is>
+          <t>H8-03</t>
+        </is>
+      </c>
+      <c r="D86" s="70" t="inlineStr">
+        <is>
+          <t>担当者のスキル自己評価</t>
+        </is>
+      </c>
+      <c r="E86" s="70" t="inlineStr">
+        <is>
+          <t>スキルを前提にせず入力作業をマニュアル化する方針</t>
+        </is>
+      </c>
+      <c r="G86" s="70" t="inlineStr">
+        <is>
+          <t>設計思想の転換として妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="34" customHeight="1" s="48">
+      <c r="B87" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C87" s="69" t="inlineStr">
+        <is>
+          <t>H8-04</t>
+        </is>
+      </c>
+      <c r="D87" s="70" t="inlineStr">
+        <is>
+          <t>業務の拠点内での位置づけ</t>
+        </is>
+      </c>
+      <c r="E87" s="70" t="inlineStr">
+        <is>
+          <t>自己申告でなく実際の対応状況で督促強度を判断</t>
+        </is>
+      </c>
+      <c r="G87" s="70" t="inlineStr">
+        <is>
+          <t>客観的データへの切替で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="34" customHeight="1" s="48">
+      <c r="B88" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C88" s="69" t="inlineStr">
+        <is>
+          <t>H9-01</t>
+        </is>
+      </c>
+      <c r="D88" s="70" t="inlineStr">
+        <is>
+          <t>言語・翻訳体制</t>
+        </is>
+      </c>
+      <c r="E88" s="70" t="inlineStr">
+        <is>
+          <t>多言語対応をRFPに含める前提で設計</t>
+        </is>
+      </c>
+      <c r="G88" s="70" t="inlineStr">
+        <is>
+          <t>機能を厚めに実装する対応で妥当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1" s="48">
+      <c r="A90" s="77" t="inlineStr">
+        <is>
+          <t>【集計】81件レビュー ／ 削除に同意 51件 ／ 要注意 30件（うち理由不十分・誤り＝10件、理由は妥当だがリスク残存＝20件）</t>
+        </is>
+      </c>
+      <c r="B90" s="78" t="n"/>
+      <c r="C90" s="78" t="n"/>
+      <c r="D90" s="78" t="n"/>
+      <c r="E90" s="78" t="n"/>
+      <c r="F90" s="78" t="n"/>
+      <c r="G90" s="78" t="n"/>
+      <c r="H90" s="78" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/As-Is調査_V1.1_削減設問リスク一覧_0917.xlsx
+++ b/docs/As-Is調査_V1.1_削減設問リスク一覧_0917.xlsx
@@ -12082,21 +12082,21 @@
     <row r="1" ht="22" customHeight="1" s="48">
       <c r="A1" s="64" t="inlineStr">
         <is>
-          <t>6. 削減設問リスク一覧 ― 専門家レビュー版（81件を検証し、51件は削除に同意／30件は要注意）</t>
+          <t>6. 削減設問リスク一覧 ― 専門家レビュー版（81件を検証し、48件は削除に同意／33件は要注意）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="66" customHeight="1" s="48">
       <c r="A2" s="65" t="inlineStr">
         <is>
-          <t>南（デジ戦）がv1.1パイロット回答を受けて「拠点への設問として不要」と判断した81件（単純な重複統合を除く。当初検出した60件に加え、「【回答】」形式で記載されていた21件を追加検証）について、プロの戦略コンサルタント・システムコンサルタントの視点であらためて検証しました。削除理由が妥当でリスクが軽微、または別の仕組みで担保されている51件は【削除に同意】とし、リスク一覧からは外しています（下部に一覧を残しています）。一方、削除理由に論理的な誤り・対応不足がある、または理由自体は妥当でもシステム導入・コンプライアンス上のリスクが残る30件を【要注意】として、本シート上部に詳細を記載します。要注意の設問については、拠点配布前にESG企画室・海外BUへの再確認、または設問を残す判断を推奨します。</t>
+          <t>南（デジ戦）がv1.1パイロット回答を受けて「拠点への設問として不要」と判断した81件（単純な重複統合を除く。当初検出した60件に加え、「【回答】」形式で記載されていた21件を追加検証）について、プロの戦略コンサルタント・システムコンサルタントの視点であらためて検証しました。削除理由が妥当でリスクが軽微、または別の仕組みで担保されている48件は【削除に同意】とし、リスク一覧からは外しています（下部に一覧を残しています）。一方、削除理由に論理的な誤り・対応不足がある、または理由自体は妥当でもシステム導入・コンプライアンス上のリスクが残る33件を【要注意】として、本シート上部に詳細を記載します。要注意の設問については、拠点配布前にESG企画室・海外BUへの再確認、または設問を残す判断を推奨します。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="48">
       <c r="A3" s="66" t="inlineStr">
         <is>
-          <t>【要注意 30件】理由が不十分、または理由は妥当でもリスクが残る設問</t>
+          <t>【要注意 33件】理由が不十分、または理由は妥当でもリスクが残る設問（うち3件はユーザー指摘により再分類）</t>
         </is>
       </c>
       <c r="B3" s="67" t="n"/>
@@ -13349,125 +13349,164 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1" s="48">
-      <c r="A36" s="75" t="inlineStr">
-        <is>
-          <t>【削除に同意 51件】理由が妥当と判断し、リスク一覧からは除外した設問（参考記録）</t>
-        </is>
-      </c>
-      <c r="B36" s="76" t="n"/>
-      <c r="C36" s="76" t="n"/>
-      <c r="D36" s="76" t="n"/>
-      <c r="E36" s="76" t="n"/>
-      <c r="F36" s="76" t="n"/>
-      <c r="G36" s="76" t="n"/>
-      <c r="H36" s="76" t="n"/>
-    </row>
-    <row r="37" ht="20" customHeight="1" s="48">
-      <c r="B37" s="68" t="inlineStr">
+    <row r="35" ht="68" customHeight="1" s="48">
+      <c r="A35" s="69" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="70" t="inlineStr">
+        <is>
+          <t>3.コア設問</t>
+        </is>
+      </c>
+      <c r="C35" s="69" t="inlineStr">
+        <is>
+          <t>C-19</t>
+        </is>
+      </c>
+      <c r="D35" s="70" t="inlineStr">
+        <is>
+          <t>多言語UI・現地サポートなしでの運用可否（海外関係会社のみ）</t>
+        </is>
+      </c>
+      <c r="E35" s="70" t="inlineStr">
+        <is>
+          <t>多言語対応をRFPに含める前提で設計。設問としては削除。</t>
+        </is>
+      </c>
+      <c r="F35" s="71" t="inlineStr">
+        <is>
+          <t>理由不十分（判断基準の誤り）</t>
+        </is>
+      </c>
+      <c r="G35" s="70" t="inlineStr">
+        <is>
+          <t>「機能を厚めに実装すれば安全」という理由づけは、この設問自体が当初指摘していたトレードオフ（翻訳・現地サポートのコスト、対応できるベンダーの減少、価格上昇）を無視している。多言語対応は追加すればするだけ良い機能ではなく、過剰な要求は価格上昇とベンダー選定の失敗に直結する。少なくとも『どこまでの言語・拠点に対応するか』の程度感を確認する設問は残すべき（後日ユーザーの指摘により再分類）。</t>
+        </is>
+      </c>
+      <c r="H35" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="68" customHeight="1" s="48">
+      <c r="A36" s="69" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="70" t="inlineStr">
+        <is>
+          <t>5.選抜拠点ヒアリング</t>
+        </is>
+      </c>
+      <c r="C36" s="69" t="inlineStr">
+        <is>
+          <t>H9-01</t>
+        </is>
+      </c>
+      <c r="D36" s="70" t="inlineStr">
+        <is>
+          <t>業務・帳票・システムの言語と翻訳体制</t>
+        </is>
+      </c>
+      <c r="E36" s="70" t="inlineStr">
+        <is>
+          <t>多言語対応をRFPに含める前提で設計。設問としては削除。</t>
+        </is>
+      </c>
+      <c r="F36" s="71" t="inlineStr">
+        <is>
+          <t>理由不十分（判断基準の誤り）</t>
+        </is>
+      </c>
+      <c r="G36" s="70" t="inlineStr">
+        <is>
+          <t>C-19と同じ問題。『機能を厚めに実装すれば安全』という判断は、コスト増・対応可能ベンダーの減少という当初のリスクを無視している（後日ユーザーの指摘により再分類）。</t>
+        </is>
+      </c>
+      <c r="H36" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="68" customHeight="1" s="48">
+      <c r="A37" s="69" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="70" t="inlineStr">
+        <is>
+          <t>4.難所チェック</t>
+        </is>
+      </c>
+      <c r="C37" s="69" t="inlineStr">
+        <is>
+          <t>10-09</t>
+        </is>
+      </c>
+      <c r="D37" s="70" t="inlineStr">
+        <is>
+          <t>計算に使う数値やルールが変わったときの再計算への不安</t>
+        </is>
+      </c>
+      <c r="E37" s="70" t="inlineStr">
+        <is>
+          <t>拠点で計算は行っていないため、再計算は本社側の機能として設計。</t>
+        </is>
+      </c>
+      <c r="F37" s="73" t="inlineStr">
+        <is>
+          <t>リスク残存（前提の再検証が必要）</t>
+        </is>
+      </c>
+      <c r="G37" s="70" t="inlineStr">
+        <is>
+          <t>当初はC-06（拠点側での計算実施範囲）が安全網になるとして削除に同意していたが、C-06自体の削除判断に問題があると判明した（海外BU自身が『生産拠点は自前で算定している』と証言）。安全網が機能していない可能性があり、要注意に位置づけを変更する（後日の再検証により再分類）。</t>
+        </is>
+      </c>
+      <c r="H37" s="72" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" s="48">
+      <c r="A39" s="75" t="inlineStr">
+        <is>
+          <t>【削除に同意 48件】理由が妥当と判断し、リスク一覧からは除外した設問（参考記録）</t>
+        </is>
+      </c>
+      <c r="B39" s="76" t="n"/>
+      <c r="C39" s="76" t="n"/>
+      <c r="D39" s="76" t="n"/>
+      <c r="E39" s="76" t="n"/>
+      <c r="F39" s="76" t="n"/>
+      <c r="G39" s="76" t="n"/>
+      <c r="H39" s="76" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" s="48">
+      <c r="B40" s="68" t="inlineStr">
         <is>
           <t>シート</t>
         </is>
       </c>
-      <c r="C37" s="68" t="inlineStr">
+      <c r="C40" s="68" t="inlineStr">
         <is>
           <t>元ID</t>
         </is>
       </c>
-      <c r="D37" s="68" t="inlineStr">
+      <c r="D40" s="68" t="inlineStr">
         <is>
           <t>元の設問（要旨）</t>
         </is>
       </c>
-      <c r="E37" s="68" t="inlineStr">
+      <c r="E40" s="68" t="inlineStr">
         <is>
           <t>削除理由の要旨</t>
         </is>
       </c>
-      <c r="G37" s="68" t="inlineStr">
+      <c r="G40" s="68" t="inlineStr">
         <is>
           <t>同意コメント</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="34" customHeight="1" s="48">
-      <c r="B38" s="70" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C38" s="69" t="inlineStr">
-        <is>
-          <t>C-01</t>
-        </is>
-      </c>
-      <c r="D38" s="70" t="inlineStr">
-        <is>
-          <t>手順書の有無</t>
-        </is>
-      </c>
-      <c r="E38" s="70" t="inlineStr">
-        <is>
-          <t>両拠点とも手順書なしで一致</t>
-        </is>
-      </c>
-      <c r="G38" s="70" t="inlineStr">
-        <is>
-          <t>仮に手順書がある拠点があっても、被る不利益は個別ヒアリングの手間程度で小さい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="34" customHeight="1" s="48">
-      <c r="B39" s="70" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C39" s="69" t="inlineStr">
-        <is>
-          <t>C-09</t>
-        </is>
-      </c>
-      <c r="D39" s="70" t="inlineStr">
-        <is>
-          <t>証憑の保管形式</t>
-        </is>
-      </c>
-      <c r="E39" s="70" t="inlineStr">
-        <is>
-          <t>PDF・Excelが中心と把握</t>
-        </is>
-      </c>
-      <c r="G39" s="70" t="inlineStr">
-        <is>
-          <t>低リスク。仮に紙中心の拠点があっても保管容量を多めに見ておけば対応可能。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="34" customHeight="1" s="48">
-      <c r="B40" s="70" t="inlineStr">
-        <is>
-          <t>3.コア設問</t>
-        </is>
-      </c>
-      <c r="C40" s="69" t="inlineStr">
-        <is>
-          <t>C-13</t>
-        </is>
-      </c>
-      <c r="D40" s="70" t="inlineStr">
-        <is>
-          <t>変更履歴の有無</t>
-        </is>
-      </c>
-      <c r="E40" s="70" t="inlineStr">
-        <is>
-          <t>変更履歴を必須要件として確定</t>
-        </is>
-      </c>
-      <c r="G40" s="70" t="inlineStr">
-        <is>
-          <t>履歴機能を全拠点前提で実装するため、実態が違っても上位互換で吸収できる。</t>
         </is>
       </c>
     </row>
@@ -13479,22 +13518,22 @@
       </c>
       <c r="C41" s="69" t="inlineStr">
         <is>
-          <t>C-23</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="D41" s="70" t="inlineStr">
         <is>
-          <t>抜け漏れ・遅延の主な原因</t>
+          <t>手順書の有無</t>
         </is>
       </c>
       <c r="E41" s="70" t="inlineStr">
         <is>
-          <t>5つの原因を要件に反映</t>
+          <t>両拠点とも手順書なしで一致</t>
         </is>
       </c>
       <c r="G41" s="70" t="inlineStr">
         <is>
-          <t>汎用的な原因（アラート視認性、単位換算、年始重なり等）で妥当性が高い。</t>
+          <t>仮に手順書がある拠点があっても、被る不利益は個別ヒアリングの手間程度で小さい。</t>
         </is>
       </c>
     </row>
@@ -13506,22 +13545,22 @@
       </c>
       <c r="C42" s="69" t="inlineStr">
         <is>
-          <t>C-27</t>
+          <t>C-09</t>
         </is>
       </c>
       <c r="D42" s="70" t="inlineStr">
         <is>
-          <t>妥当性チェック方法</t>
+          <t>証憑の保管形式</t>
         </is>
       </c>
       <c r="E42" s="70" t="inlineStr">
         <is>
-          <t>標準閾値はESG企画室が設定</t>
+          <t>PDF・Excelが中心と把握</t>
         </is>
       </c>
       <c r="G42" s="70" t="inlineStr">
         <is>
-          <t>現状の拠点実態に関わらず、今後の方針として妥当な決定。</t>
+          <t>低リスク。仮に紙中心の拠点があっても保管容量を多めに見ておけば対応可能。</t>
         </is>
       </c>
     </row>
@@ -13533,22 +13572,22 @@
       </c>
       <c r="C43" s="69" t="inlineStr">
         <is>
-          <t>C-29</t>
+          <t>C-13</t>
         </is>
       </c>
       <c r="D43" s="70" t="inlineStr">
         <is>
-          <t>証憑を探す時間</t>
+          <t>変更履歴の有無</t>
         </is>
       </c>
       <c r="E43" s="70" t="inlineStr">
         <is>
-          <t>BOX運用を前提に保存・検索機能を必須化</t>
+          <t>変更履歴を必須要件として確定</t>
         </is>
       </c>
       <c r="G43" s="70" t="inlineStr">
         <is>
-          <t>機能を厚めに実装する対応であり、実態が違っても問題は生じにくい。</t>
+          <t>履歴機能を全拠点前提で実装するため、実態が違っても上位互換で吸収できる。</t>
         </is>
       </c>
     </row>
@@ -13560,22 +13599,22 @@
       </c>
       <c r="C44" s="69" t="inlineStr">
         <is>
-          <t>C-31</t>
+          <t>C-23</t>
         </is>
       </c>
       <c r="D44" s="70" t="inlineStr">
         <is>
-          <t>確定・ロックの概念</t>
+          <t>抜け漏れ・遅延の主な原因</t>
         </is>
       </c>
       <c r="E44" s="70" t="inlineStr">
         <is>
-          <t>本社が確定・ロックを行っている</t>
+          <t>5つの原因を要件に反映</t>
         </is>
       </c>
       <c r="G44" s="70" t="inlineStr">
         <is>
-          <t>本社主導の統制であり、拠点側の実態に依存しない。</t>
+          <t>汎用的な原因（アラート視認性、単位換算、年始重なり等）で妥当性が高い。</t>
         </is>
       </c>
     </row>
@@ -13587,22 +13626,22 @@
       </c>
       <c r="C45" s="69" t="inlineStr">
         <is>
-          <t>C-34</t>
+          <t>C-27</t>
         </is>
       </c>
       <c r="D45" s="70" t="inlineStr">
         <is>
-          <t>スマートメーター等の有無</t>
+          <t>妥当性チェック方法</t>
         </is>
       </c>
       <c r="E45" s="70" t="inlineStr">
         <is>
-          <t>自動計測は対象外、OCR検討に振替</t>
+          <t>標準閾値はESG企画室が設定</t>
         </is>
       </c>
       <c r="G45" s="70" t="inlineStr">
         <is>
-          <t>意図的なスコープ決定であり、機会損失は自覚的に受容されている。</t>
+          <t>現状の拠点実態に関わらず、今後の方針として妥当な決定。</t>
         </is>
       </c>
     </row>
@@ -13614,103 +13653,103 @@
       </c>
       <c r="C46" s="69" t="inlineStr">
         <is>
-          <t>C-37</t>
+          <t>C-29</t>
         </is>
       </c>
       <c r="D46" s="70" t="inlineStr">
         <is>
-          <t>属人化の有無</t>
+          <t>証憑を探す時間</t>
         </is>
       </c>
       <c r="E46" s="70" t="inlineStr">
         <is>
-          <t>一部属人化前提でマニュアル整備を要件化</t>
+          <t>BOX運用を前提に保存・検索機能を必須化</t>
         </is>
       </c>
       <c r="G46" s="70" t="inlineStr">
         <is>
-          <t>保守的な前提で対応するため、実態が多少違っても支障は小さい。</t>
+          <t>機能を厚めに実装する対応であり、実態が違っても問題は生じにくい。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1" s="48">
       <c r="B47" s="70" t="inlineStr">
         <is>
-          <t>4.難所チェック</t>
+          <t>3.コア設問</t>
         </is>
       </c>
       <c r="C47" s="69" t="inlineStr">
         <is>
-          <t>10-06</t>
+          <t>C-31</t>
         </is>
       </c>
       <c r="D47" s="70" t="inlineStr">
         <is>
-          <t>抜け漏れの構造的発生</t>
+          <t>確定・ロックの概念</t>
         </is>
       </c>
       <c r="E47" s="70" t="inlineStr">
         <is>
-          <t>未然防止でなく事後の早期修正で担保</t>
+          <t>本社が確定・ロックを行っている</t>
         </is>
       </c>
       <c r="G47" s="70" t="inlineStr">
         <is>
-          <t>リスクを無視せず、別の仕組み（早期修正）で正面から対応している。</t>
+          <t>本社主導の統制であり、拠点側の実態に依存しない。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="34" customHeight="1" s="48">
       <c r="B48" s="70" t="inlineStr">
         <is>
-          <t>4.難所チェック</t>
+          <t>3.コア設問</t>
         </is>
       </c>
       <c r="C48" s="69" t="inlineStr">
         <is>
-          <t>10-07</t>
+          <t>C-34</t>
         </is>
       </c>
       <c r="D48" s="70" t="inlineStr">
         <is>
-          <t>単位換算・按分の計算ミス</t>
+          <t>スマートメーター等の有無</t>
         </is>
       </c>
       <c r="E48" s="70" t="inlineStr">
         <is>
-          <t>実績（毎年1〜2拠点で発生）を閾値設計に反映</t>
+          <t>自動計測は対象外、OCR検討に振替</t>
         </is>
       </c>
       <c r="G48" s="70" t="inlineStr">
         <is>
-          <t>エビデンスに基づく設計判断。</t>
+          <t>意図的なスコープ決定であり、機会損失は自覚的に受容されている。</t>
         </is>
       </c>
     </row>
     <row r="49" ht="34" customHeight="1" s="48">
       <c r="B49" s="70" t="inlineStr">
         <is>
-          <t>4.難所チェック</t>
+          <t>3.コア設問</t>
         </is>
       </c>
       <c r="C49" s="69" t="inlineStr">
         <is>
-          <t>10-08</t>
+          <t>C-37</t>
         </is>
       </c>
       <c r="D49" s="70" t="inlineStr">
         <is>
-          <t>異常値照会の往復</t>
+          <t>属人化の有無</t>
         </is>
       </c>
       <c r="E49" s="70" t="inlineStr">
         <is>
-          <t>異常値照会機能を優先度高い要件とする</t>
+          <t>一部属人化前提でマニュアル整備を要件化</t>
         </is>
       </c>
       <c r="G49" s="70" t="inlineStr">
         <is>
-          <t>リスクを認識した上で機能として正面から対応している。</t>
+          <t>保守的な前提で対応するため、実態が多少違っても支障は小さい。</t>
         </is>
       </c>
     </row>
@@ -13722,22 +13761,22 @@
       </c>
       <c r="C50" s="69" t="inlineStr">
         <is>
-          <t>10-09</t>
+          <t>10-06</t>
         </is>
       </c>
       <c r="D50" s="70" t="inlineStr">
         <is>
-          <t>再計算への不安</t>
+          <t>抜け漏れの構造的発生</t>
         </is>
       </c>
       <c r="E50" s="70" t="inlineStr">
         <is>
-          <t>拠点は計算していないため本社機能として設計</t>
+          <t>未然防止でなく事後の早期修正で担保</t>
         </is>
       </c>
       <c r="G50" s="70" t="inlineStr">
         <is>
-          <t>C-06が引き続き生きた設問として残り、実態と異なる拠点があれば別途捕捉される安全網がある。</t>
+          <t>リスクを無視せず、別の仕組み（早期修正）で正面から対応している。</t>
         </is>
       </c>
     </row>
@@ -13749,22 +13788,22 @@
       </c>
       <c r="C51" s="69" t="inlineStr">
         <is>
-          <t>10-11</t>
+          <t>10-07</t>
         </is>
       </c>
       <c r="D51" s="70" t="inlineStr">
         <is>
-          <t>証拠探しの負荷</t>
+          <t>単位換算・按分の計算ミス</t>
         </is>
       </c>
       <c r="E51" s="70" t="inlineStr">
         <is>
-          <t>国内浸透・海外未浸透を移行計画の前提</t>
+          <t>実績（毎年1〜2拠点で発生）を閾値設計に反映</t>
         </is>
       </c>
       <c r="G51" s="70" t="inlineStr">
         <is>
-          <t>結果に誤りがあっても移行期間の見積り誤差程度で、影響は軽微。</t>
+          <t>エビデンスに基づく設計判断。</t>
         </is>
       </c>
     </row>
@@ -13776,76 +13815,76 @@
       </c>
       <c r="C52" s="69" t="inlineStr">
         <is>
-          <t>10-12</t>
+          <t>10-08</t>
         </is>
       </c>
       <c r="D52" s="70" t="inlineStr">
         <is>
-          <t>フィードバック機能の要否</t>
+          <t>異常値照会の往復</t>
         </is>
       </c>
       <c r="E52" s="70" t="inlineStr">
         <is>
-          <t>費用対効果で判断する保留項目として整理</t>
+          <t>異常値照会機能を優先度高い要件とする</t>
         </is>
       </c>
       <c r="G52" s="70" t="inlineStr">
         <is>
-          <t>無視ではなく先送りの判断であり妥当。</t>
+          <t>リスクを認識した上で機能として正面から対応している。</t>
         </is>
       </c>
     </row>
     <row r="53" ht="34" customHeight="1" s="48">
       <c r="B53" s="70" t="inlineStr">
         <is>
-          <t>5.選抜拠点ヒアリング</t>
+          <t>4.難所チェック</t>
         </is>
       </c>
       <c r="C53" s="69" t="inlineStr">
         <is>
-          <t>H3-01</t>
+          <t>10-11</t>
         </is>
       </c>
       <c r="D53" s="70" t="inlineStr">
         <is>
-          <t>手順書の形式等</t>
+          <t>証拠探しの負荷</t>
         </is>
       </c>
       <c r="E53" s="70" t="inlineStr">
         <is>
-          <t>システム入力マニュアル以外の手順書はない</t>
+          <t>国内浸透・海外未浸透を移行計画の前提</t>
         </is>
       </c>
       <c r="G53" s="70" t="inlineStr">
         <is>
-          <t>C-01と同様、低リスク。</t>
+          <t>結果に誤りがあっても移行期間の見積り誤差程度で、影響は軽微。</t>
         </is>
       </c>
     </row>
     <row r="54" ht="34" customHeight="1" s="48">
       <c r="B54" s="70" t="inlineStr">
         <is>
-          <t>5.選抜拠点ヒアリング</t>
+          <t>4.難所チェック</t>
         </is>
       </c>
       <c r="C54" s="69" t="inlineStr">
         <is>
-          <t>H3-02</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="D54" s="70" t="inlineStr">
         <is>
-          <t>手順書と実態の乖離</t>
+          <t>フィードバック機能の要否</t>
         </is>
       </c>
       <c r="E54" s="70" t="inlineStr">
         <is>
-          <t>手順書がないため明文化を導入時タスクに含める</t>
+          <t>費用対効果で判断する保留項目として整理</t>
         </is>
       </c>
       <c r="G54" s="70" t="inlineStr">
         <is>
-          <t>対応がリスクを正面から解消している。</t>
+          <t>無視ではなく先送りの判断であり妥当。</t>
         </is>
       </c>
     </row>
@@ -13857,22 +13896,22 @@
       </c>
       <c r="C55" s="69" t="inlineStr">
         <is>
-          <t>H3-06</t>
+          <t>H3-01</t>
         </is>
       </c>
       <c r="D55" s="70" t="inlineStr">
         <is>
-          <t>データ欠測の穴埋め方法</t>
+          <t>手順書の形式等</t>
         </is>
       </c>
       <c r="E55" s="70" t="inlineStr">
         <is>
-          <t>欠測は例外的としシステム外の補完を許容</t>
+          <t>システム入力マニュアル以外の手順書はない</t>
         </is>
       </c>
       <c r="G55" s="70" t="inlineStr">
         <is>
-          <t>例外処理を許容する設計判断で妥当。</t>
+          <t>C-01と同様、低リスク。</t>
         </is>
       </c>
     </row>
@@ -13884,22 +13923,22 @@
       </c>
       <c r="C56" s="69" t="inlineStr">
         <is>
-          <t>H3-09</t>
+          <t>H3-02</t>
         </is>
       </c>
       <c r="D56" s="70" t="inlineStr">
         <is>
-          <t>複数報告間の食い違い</t>
+          <t>手順書と実態の乖離</t>
         </is>
       </c>
       <c r="E56" s="70" t="inlineStr">
         <is>
-          <t>多目的出力を要件化、様式変更対応は別途調整</t>
+          <t>手順書がないため明文化を導入時タスクに含める</t>
         </is>
       </c>
       <c r="G56" s="70" t="inlineStr">
         <is>
-          <t>主要リスク（数値不整合）は要件化で解消。CDP対応のみ先送り。</t>
+          <t>対応がリスクを正面から解消している。</t>
         </is>
       </c>
     </row>
@@ -13911,22 +13950,22 @@
       </c>
       <c r="C57" s="69" t="inlineStr">
         <is>
-          <t>H4-02</t>
+          <t>H3-06</t>
         </is>
       </c>
       <c r="D57" s="70" t="inlineStr">
         <is>
-          <t>係数更新時の再計算</t>
+          <t>データ欠測の穴埋め方法</t>
         </is>
       </c>
       <c r="E57" s="70" t="inlineStr">
         <is>
-          <t>更新・再計算可能性を要件に反映（保守的）</t>
+          <t>欠測は例外的としシステム外の補完を許容</t>
         </is>
       </c>
       <c r="G57" s="70" t="inlineStr">
         <is>
-          <t>機能を厚めに実装する対応で妥当。</t>
+          <t>例外処理を許容する設計判断で妥当。</t>
         </is>
       </c>
     </row>
@@ -13938,22 +13977,22 @@
       </c>
       <c r="C58" s="69" t="inlineStr">
         <is>
-          <t>H4-03</t>
+          <t>H3-09</t>
         </is>
       </c>
       <c r="D58" s="70" t="inlineStr">
         <is>
-          <t>按分の管理者・根拠資料</t>
+          <t>複数報告間の食い違い</t>
         </is>
       </c>
       <c r="E58" s="70" t="inlineStr">
         <is>
-          <t>対象拠点・項目の一覧をESG企画室が提示</t>
+          <t>多目的出力を要件化、様式変更対応は別途調整</t>
         </is>
       </c>
       <c r="G58" s="70" t="inlineStr">
         <is>
-          <t>情報源の変更であり、ESG企画室が確実に提示すれば問題ない（運用上のToDoとして管理）。</t>
+          <t>主要リスク（数値不整合）は要件化で解消。CDP対応のみ先送り。</t>
         </is>
       </c>
     </row>
@@ -13965,22 +14004,22 @@
       </c>
       <c r="C59" s="69" t="inlineStr">
         <is>
-          <t>H4-04</t>
+          <t>H4-02</t>
         </is>
       </c>
       <c r="D59" s="70" t="inlineStr">
         <is>
-          <t>按分基準の見直し頻度</t>
+          <t>係数更新時の再計算</t>
         </is>
       </c>
       <c r="E59" s="70" t="inlineStr">
         <is>
-          <t>按分基準は年度ごとに保持する設計</t>
+          <t>更新・再計算可能性を要件に反映（保守的）</t>
         </is>
       </c>
       <c r="G59" s="70" t="inlineStr">
         <is>
-          <t>保守的な設計で妥当。</t>
+          <t>機能を厚めに実装する対応で妥当。</t>
         </is>
       </c>
     </row>
@@ -13992,22 +14031,22 @@
       </c>
       <c r="C60" s="69" t="inlineStr">
         <is>
-          <t>H4-12</t>
+          <t>H4-03</t>
         </is>
       </c>
       <c r="D60" s="70" t="inlineStr">
         <is>
-          <t>製品LCA用データ</t>
+          <t>按分の管理者・根拠資料</t>
         </is>
       </c>
       <c r="E60" s="70" t="inlineStr">
         <is>
-          <t>ESG企画室との事前決定待ち、決定まで対象外</t>
+          <t>対象拠点・項目の一覧をESG企画室が提示</t>
         </is>
       </c>
       <c r="G60" s="70" t="inlineStr">
         <is>
-          <t>意思決定プロセスを踏んだ先送りであり妥当。</t>
+          <t>情報源の変更であり、ESG企画室が確実に提示すれば問題ない（運用上のToDoとして管理）。</t>
         </is>
       </c>
     </row>
@@ -14019,22 +14058,22 @@
       </c>
       <c r="C61" s="69" t="inlineStr">
         <is>
-          <t>H4-13</t>
+          <t>H4-04</t>
         </is>
       </c>
       <c r="D61" s="70" t="inlineStr">
         <is>
-          <t>人事・安全データの拠点独自解釈</t>
+          <t>按分基準の見直し頻度</t>
         </is>
       </c>
       <c r="E61" s="70" t="inlineStr">
         <is>
-          <t>本社側の指標定義の問題として整理</t>
+          <t>按分基準は年度ごとに保持する設計</t>
         </is>
       </c>
       <c r="G61" s="70" t="inlineStr">
         <is>
-          <t>対応の道筋が明確で妥当。</t>
+          <t>保守的な設計で妥当。</t>
         </is>
       </c>
     </row>
@@ -14046,22 +14085,22 @@
       </c>
       <c r="C62" s="69" t="inlineStr">
         <is>
-          <t>H5-02</t>
+          <t>H4-12</t>
         </is>
       </c>
       <c r="D62" s="70" t="inlineStr">
         <is>
-          <t>保存年限</t>
+          <t>製品LCA用データ</t>
         </is>
       </c>
       <c r="E62" s="70" t="inlineStr">
         <is>
-          <t>ESG企画室と決定のうえシステム要件に反映</t>
+          <t>ESG企画室との事前決定待ち、決定まで対象外</t>
         </is>
       </c>
       <c r="G62" s="70" t="inlineStr">
         <is>
-          <t>意思決定プロセスを踏んだ判断であり妥当。</t>
+          <t>意思決定プロセスを踏んだ先送りであり妥当。</t>
         </is>
       </c>
     </row>
@@ -14073,22 +14112,22 @@
       </c>
       <c r="C63" s="69" t="inlineStr">
         <is>
-          <t>H5-04</t>
+          <t>H4-13</t>
         </is>
       </c>
       <c r="D63" s="70" t="inlineStr">
         <is>
-          <t>第三者保有証憑の入手性</t>
+          <t>人事・安全データの拠点独自解釈</t>
         </is>
       </c>
       <c r="E63" s="70" t="inlineStr">
         <is>
-          <t>請求ありは入手可、なしは推定・除外</t>
+          <t>本社側の指標定義の問題として整理</t>
         </is>
       </c>
       <c r="G63" s="70" t="inlineStr">
         <is>
-          <t>明確な運用ルールとして妥当。</t>
+          <t>対応の道筋が明確で妥当。</t>
         </is>
       </c>
     </row>
@@ -14100,22 +14139,22 @@
       </c>
       <c r="C64" s="69" t="inlineStr">
         <is>
-          <t>H5-06</t>
+          <t>H5-02</t>
         </is>
       </c>
       <c r="D64" s="70" t="inlineStr">
         <is>
-          <t>過去の指摘事項の記録所在</t>
+          <t>保存年限</t>
         </is>
       </c>
       <c r="E64" s="70" t="inlineStr">
         <is>
-          <t>ESG企画室の共有フォルダにあると把握</t>
+          <t>ESG企画室と決定のうえシステム要件に反映</t>
         </is>
       </c>
       <c r="G64" s="70" t="inlineStr">
         <is>
-          <t>監査対応は通常ESG企画室が集約する業務であり、妥当性が高い。</t>
+          <t>意思決定プロセスを踏んだ判断であり妥当。</t>
         </is>
       </c>
     </row>
@@ -14127,22 +14166,22 @@
       </c>
       <c r="C65" s="69" t="inlineStr">
         <is>
-          <t>H6-01</t>
+          <t>H5-04</t>
         </is>
       </c>
       <c r="D65" s="70" t="inlineStr">
         <is>
-          <t>チェック記録の有無</t>
+          <t>第三者保有証憑の入手性</t>
         </is>
       </c>
       <c r="E65" s="70" t="inlineStr">
         <is>
-          <t>証跡はシステム内に残す前提とする</t>
+          <t>請求ありは入手可、なしは推定・除外</t>
         </is>
       </c>
       <c r="G65" s="70" t="inlineStr">
         <is>
-          <t>機能を厚めに実装する対応で妥当。</t>
+          <t>明確な運用ルールとして妥当。</t>
         </is>
       </c>
     </row>
@@ -14154,22 +14193,22 @@
       </c>
       <c r="C66" s="69" t="inlineStr">
         <is>
-          <t>H6-03</t>
+          <t>H5-06</t>
         </is>
       </c>
       <c r="D66" s="70" t="inlineStr">
         <is>
-          <t>入力ミスの流出経験</t>
+          <t>過去の指摘事項の記録所在</t>
         </is>
       </c>
       <c r="E66" s="70" t="inlineStr">
         <is>
-          <t>現行の修正要否確認プロセスを維持</t>
+          <t>ESG企画室の共有フォルダにあると把握</t>
         </is>
       </c>
       <c r="G66" s="70" t="inlineStr">
         <is>
-          <t>既存の安全策を維持する保守的判断。</t>
+          <t>監査対応は通常ESG企画室が集約する業務であり、妥当性が高い。</t>
         </is>
       </c>
     </row>
@@ -14181,22 +14220,22 @@
       </c>
       <c r="C67" s="69" t="inlineStr">
         <is>
-          <t>H6-04</t>
+          <t>H6-01</t>
         </is>
       </c>
       <c r="D67" s="70" t="inlineStr">
         <is>
-          <t>拠点長の関与頻度</t>
+          <t>チェック記録の有無</t>
         </is>
       </c>
       <c r="E67" s="70" t="inlineStr">
         <is>
-          <t>承認者ルールは事務局で設計し拠点へ説明</t>
+          <t>証跡はシステム内に残す前提とする</t>
         </is>
       </c>
       <c r="G67" s="70" t="inlineStr">
         <is>
-          <t>トップダウンの設計方針として妥当。</t>
+          <t>機能を厚めに実装する対応で妥当。</t>
         </is>
       </c>
     </row>
@@ -14208,22 +14247,22 @@
       </c>
       <c r="C68" s="69" t="inlineStr">
         <is>
-          <t>H6-07</t>
+          <t>H6-03</t>
         </is>
       </c>
       <c r="D68" s="70" t="inlineStr">
         <is>
-          <t>内部監査・ISO審査の指摘内容</t>
+          <t>入力ミスの流出経験</t>
         </is>
       </c>
       <c r="E68" s="70" t="inlineStr">
         <is>
-          <t>ISO監査は数値誤りを対象外として整理</t>
+          <t>現行の修正要否確認プロセスを維持</t>
         </is>
       </c>
       <c r="G68" s="70" t="inlineStr">
         <is>
-          <t>一般的にISO14001は運用プロセスの適合性を見るものであり、数値精度の検証はSGS等の第三者保証が担う。理由は妥当。</t>
+          <t>既存の安全策を維持する保守的判断。</t>
         </is>
       </c>
     </row>
@@ -14235,22 +14274,22 @@
       </c>
       <c r="C69" s="69" t="inlineStr">
         <is>
-          <t>H7-03</t>
+          <t>H6-04</t>
         </is>
       </c>
       <c r="D69" s="70" t="inlineStr">
         <is>
-          <t>子メーターの設置状況</t>
+          <t>拠点長の関与頻度</t>
         </is>
       </c>
       <c r="E69" s="70" t="inlineStr">
         <is>
-          <t>拠点単位で足りるとし部門別粒度は対象外</t>
+          <t>承認者ルールは事務局で設計し拠点へ説明</t>
         </is>
       </c>
       <c r="G69" s="70" t="inlineStr">
         <is>
-          <t>意図的なスコープ決定で妥当。</t>
+          <t>トップダウンの設計方針として妥当。</t>
         </is>
       </c>
     </row>
@@ -14262,22 +14301,22 @@
       </c>
       <c r="C70" s="69" t="inlineStr">
         <is>
-          <t>H7-04</t>
+          <t>H6-07</t>
         </is>
       </c>
       <c r="D70" s="70" t="inlineStr">
         <is>
-          <t>ITサポート体制</t>
+          <t>内部監査・ISO審査の指摘内容</t>
         </is>
       </c>
       <c r="E70" s="70" t="inlineStr">
         <is>
-          <t>現地IT支援は期待せず本社リモート支援を計画</t>
+          <t>ISO監査は数値誤りを対象外として整理</t>
         </is>
       </c>
       <c r="G70" s="70" t="inlineStr">
         <is>
-          <t>最悪ケースを前提にした保守的な計画で妥当。</t>
+          <t>一般的にISO14001は運用プロセスの適合性を見るものであり、数値精度の検証はSGS等の第三者保証が担う。理由は妥当。</t>
         </is>
       </c>
     </row>
@@ -14289,22 +14328,22 @@
       </c>
       <c r="C71" s="69" t="inlineStr">
         <is>
-          <t>H8-01</t>
+          <t>H7-03</t>
         </is>
       </c>
       <c r="D71" s="70" t="inlineStr">
         <is>
-          <t>本社照会・差し戻し件数</t>
+          <t>子メーターの設置状況</t>
         </is>
       </c>
       <c r="E71" s="70" t="inlineStr">
         <is>
-          <t>把握済みの実績値を効果試算の基準値とする</t>
+          <t>拠点単位で足りるとし部門別粒度は対象外</t>
         </is>
       </c>
       <c r="G71" s="70" t="inlineStr">
         <is>
-          <t>実データに基づく判断で妥当。</t>
+          <t>意図的なスコープ決定で妥当。</t>
         </is>
       </c>
     </row>
@@ -14316,22 +14355,22 @@
       </c>
       <c r="C72" s="69" t="inlineStr">
         <is>
-          <t>H8-02</t>
+          <t>H7-04</t>
         </is>
       </c>
       <c r="D72" s="70" t="inlineStr">
         <is>
-          <t>業務関与人数・兼務状況</t>
+          <t>ITサポート体制</t>
         </is>
       </c>
       <c r="E72" s="70" t="inlineStr">
         <is>
-          <t>Scope1・2で3名を前提にライセンス数を試算</t>
+          <t>現地IT支援は期待せず本社リモート支援を計画</t>
         </is>
       </c>
       <c r="G72" s="70" t="inlineStr">
         <is>
-          <t>Scope3を含める場合の見直しを自ら明記しており、リスクを認識した上での判断。</t>
+          <t>最悪ケースを前提にした保守的な計画で妥当。</t>
         </is>
       </c>
     </row>
@@ -14343,22 +14382,22 @@
       </c>
       <c r="C73" s="69" t="inlineStr">
         <is>
-          <t>H9-03</t>
+          <t>H8-01</t>
         </is>
       </c>
       <c r="D73" s="70" t="inlineStr">
         <is>
-          <t>CSRD等の追加開示要求</t>
+          <t>本社照会・差し戻し件数</t>
         </is>
       </c>
       <c r="E73" s="70" t="inlineStr">
         <is>
-          <t>オーストラリア子会社分を将来要件として記録</t>
+          <t>把握済みの実績値を効果試算の基準値とする</t>
         </is>
       </c>
       <c r="G73" s="70" t="inlineStr">
         <is>
-          <t>判明した事実を無視せず要件に反映しており妥当。</t>
+          <t>実データに基づく判断で妥当。</t>
         </is>
       </c>
     </row>
@@ -14370,76 +14409,76 @@
       </c>
       <c r="C74" s="69" t="inlineStr">
         <is>
-          <t>H9-06</t>
+          <t>H8-02</t>
         </is>
       </c>
       <c r="D74" s="70" t="inlineStr">
         <is>
-          <t>現地委託先データの入手性</t>
+          <t>業務関与人数・兼務状況</t>
         </is>
       </c>
       <c r="E74" s="70" t="inlineStr">
         <is>
-          <t>取れないデータは推定・除外する原則</t>
+          <t>Scope1・2で3名を前提にライセンス数を試算</t>
         </is>
       </c>
       <c r="G74" s="70" t="inlineStr">
         <is>
-          <t>明確な運用ルールとして妥当。</t>
+          <t>Scope3を含める場合の見直しを自ら明記しており、リスクを認識した上での判断。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="34" customHeight="1" s="48">
       <c r="B75" s="70" t="inlineStr">
         <is>
-          <t>3.コア設問</t>
+          <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
       <c r="C75" s="69" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>H9-03</t>
         </is>
       </c>
       <c r="D75" s="70" t="inlineStr">
         <is>
-          <t>報告後のデータ修正頻度</t>
+          <t>CSRD等の追加開示要求</t>
         </is>
       </c>
       <c r="E75" s="70" t="inlineStr">
         <is>
-          <t>算定前の桁間違い修正が毎年発生する実態を踏まえ修正機能を実装前提化</t>
+          <t>オーストラリア子会社分を将来要件として記録</t>
         </is>
       </c>
       <c r="G75" s="70" t="inlineStr">
         <is>
-          <t>機能を厚めに実装する対応であり妥当。</t>
+          <t>判明した事実を無視せず要件に反映しており妥当。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="34" customHeight="1" s="48">
       <c r="B76" s="70" t="inlineStr">
         <is>
-          <t>3.コア設問</t>
+          <t>5.選抜拠点ヒアリング</t>
         </is>
       </c>
       <c r="C76" s="69" t="inlineStr">
         <is>
-          <t>C-05</t>
+          <t>H9-06</t>
         </is>
       </c>
       <c r="D76" s="70" t="inlineStr">
         <is>
-          <t>主担当不在時の報告継続性</t>
+          <t>現地委託先データの入手性</t>
         </is>
       </c>
       <c r="E76" s="70" t="inlineStr">
         <is>
-          <t>1拠点でも止まると全体が遅れるため代理承認を実装前提化</t>
+          <t>取れないデータは推定・除外する原則</t>
         </is>
       </c>
       <c r="G76" s="70" t="inlineStr">
         <is>
-          <t>保守的な機能実装で妥当。</t>
+          <t>明確な運用ルールとして妥当。</t>
         </is>
       </c>
     </row>
@@ -14451,22 +14490,22 @@
       </c>
       <c r="C77" s="69" t="inlineStr">
         <is>
-          <t>C-10</t>
+          <t>C-04</t>
         </is>
       </c>
       <c r="D77" s="70" t="inlineStr">
         <is>
-          <t>証憑への遡及可能性</t>
+          <t>報告後のデータ修正頻度</t>
         </is>
       </c>
       <c r="E77" s="70" t="inlineStr">
         <is>
-          <t>保存年限決定後に判断し、必要な場合は事前相談する段階的対応</t>
+          <t>算定前の桁間違い修正が毎年発生する実態を踏まえ修正機能を実装前提化</t>
         </is>
       </c>
       <c r="G77" s="70" t="inlineStr">
         <is>
-          <t>意思決定プロセスを踏んだ判断で妥当。</t>
+          <t>機能を厚めに実装する対応であり妥当。</t>
         </is>
       </c>
     </row>
@@ -14478,22 +14517,22 @@
       </c>
       <c r="C78" s="69" t="inlineStr">
         <is>
-          <t>C-19</t>
+          <t>C-05</t>
         </is>
       </c>
       <c r="D78" s="70" t="inlineStr">
         <is>
-          <t>多言語UI・現地サポートなしでの運用可否</t>
+          <t>主担当不在時の報告継続性</t>
         </is>
       </c>
       <c r="E78" s="70" t="inlineStr">
         <is>
-          <t>多言語対応をRFPに含める前提で設計</t>
+          <t>1拠点でも止まると全体が遅れるため代理承認を実装前提化</t>
         </is>
       </c>
       <c r="G78" s="70" t="inlineStr">
         <is>
-          <t>機能を厚めに実装する対応で妥当。</t>
+          <t>保守的な機能実装で妥当。</t>
         </is>
       </c>
     </row>
@@ -14505,22 +14544,22 @@
       </c>
       <c r="C79" s="69" t="inlineStr">
         <is>
-          <t>C-20</t>
+          <t>C-10</t>
         </is>
       </c>
       <c r="D79" s="70" t="inlineStr">
         <is>
-          <t>月次で最も時間がかかるステップ</t>
+          <t>証憑への遡及可能性</t>
         </is>
       </c>
       <c r="E79" s="70" t="inlineStr">
         <is>
-          <t>ステップ案をESG室へ確認する対応に切替</t>
+          <t>保存年限決定後に判断し、必要な場合は事前相談する段階的対応</t>
         </is>
       </c>
       <c r="G79" s="70" t="inlineStr">
         <is>
-          <t>全拠点調査の代替として合理的。</t>
+          <t>意思決定プロセスを踏んだ判断で妥当。</t>
         </is>
       </c>
     </row>
@@ -14532,22 +14571,22 @@
       </c>
       <c r="C80" s="69" t="inlineStr">
         <is>
-          <t>C-24</t>
+          <t>C-20</t>
         </is>
       </c>
       <c r="D80" s="70" t="inlineStr">
         <is>
-          <t>過年度データの遡及修正経験</t>
+          <t>月次で最も時間がかかるステップ</t>
         </is>
       </c>
       <c r="E80" s="70" t="inlineStr">
         <is>
-          <t>過年度修正機能を要件に含める方向</t>
+          <t>ステップ案をESG室へ確認する対応に切替</t>
         </is>
       </c>
       <c r="G80" s="70" t="inlineStr">
         <is>
-          <t>機能を厚めに実装する対応で妥当。</t>
+          <t>全拠点調査の代替として合理的。</t>
         </is>
       </c>
     </row>
@@ -14559,17 +14598,17 @@
       </c>
       <c r="C81" s="69" t="inlineStr">
         <is>
-          <t>C-25</t>
+          <t>C-24</t>
         </is>
       </c>
       <c r="D81" s="70" t="inlineStr">
         <is>
-          <t>単位換算・按分の実施有無</t>
+          <t>過年度データの遡及修正経験</t>
         </is>
       </c>
       <c r="E81" s="70" t="inlineStr">
         <is>
-          <t>換算・按分をシステム側で行う基本方針</t>
+          <t>過年度修正機能を要件に含める方向</t>
         </is>
       </c>
       <c r="G81" s="70" t="inlineStr">
@@ -14586,49 +14625,49 @@
       </c>
       <c r="C82" s="69" t="inlineStr">
         <is>
-          <t>C-36</t>
+          <t>C-25</t>
         </is>
       </c>
       <c r="D82" s="70" t="inlineStr">
         <is>
-          <t>電子承認の導入有無</t>
+          <t>単位換算・按分の実施有無</t>
         </is>
       </c>
       <c r="E82" s="70" t="inlineStr">
         <is>
-          <t>入力担当者向けでなくシステム担当者向けの技術確認事項として切り出し</t>
+          <t>換算・按分をシステム側で行う基本方針</t>
         </is>
       </c>
       <c r="G82" s="70" t="inlineStr">
         <is>
-          <t>質問対象の適正化として妥当。</t>
+          <t>機能を厚めに実装する対応で妥当。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="34" customHeight="1" s="48">
       <c r="B83" s="70" t="inlineStr">
         <is>
-          <t>5.選抜拠点ヒアリング</t>
+          <t>3.コア設問</t>
         </is>
       </c>
       <c r="C83" s="69" t="inlineStr">
         <is>
-          <t>H5-05</t>
+          <t>C-36</t>
         </is>
       </c>
       <c r="D83" s="70" t="inlineStr">
         <is>
-          <t>記録引継ぎの実態</t>
+          <t>電子承認の導入有無</t>
         </is>
       </c>
       <c r="E83" s="70" t="inlineStr">
         <is>
-          <t>本社からデータ・証憑を明示する方式に切替</t>
+          <t>入力担当者向けでなくシステム担当者向けの技術確認事項として切り出し</t>
         </is>
       </c>
       <c r="G83" s="70" t="inlineStr">
         <is>
-          <t>別の仕組みで正面から対応しており妥当。</t>
+          <t>質問対象の適正化として妥当。</t>
         </is>
       </c>
     </row>
@@ -14640,22 +14679,22 @@
       </c>
       <c r="C84" s="69" t="inlineStr">
         <is>
-          <t>H5-07</t>
+          <t>H5-05</t>
         </is>
       </c>
       <c r="D84" s="70" t="inlineStr">
         <is>
-          <t>改ざん防止の仕組み</t>
+          <t>記録引継ぎの実態</t>
         </is>
       </c>
       <c r="E84" s="70" t="inlineStr">
         <is>
-          <t>権限分離・確定ロック・変更履歴としてシステム側で担保</t>
+          <t>本社からデータ・証憑を明示する方式に切替</t>
         </is>
       </c>
       <c r="G84" s="70" t="inlineStr">
         <is>
-          <t>機能を厚めに実装する対応で妥当。</t>
+          <t>別の仕組みで正面から対応しており妥当。</t>
         </is>
       </c>
     </row>
@@ -14667,22 +14706,22 @@
       </c>
       <c r="C85" s="69" t="inlineStr">
         <is>
-          <t>H6-08</t>
+          <t>H5-07</t>
         </is>
       </c>
       <c r="D85" s="70" t="inlineStr">
         <is>
-          <t>データ信頼性のヒヤリ経験</t>
+          <t>改ざん防止の仕組み</t>
         </is>
       </c>
       <c r="E85" s="70" t="inlineStr">
         <is>
-          <t>自己申告でなく本社側の指摘・修正記録から傾向を把握</t>
+          <t>権限分離・確定ロック・変更履歴としてシステム側で担保</t>
         </is>
       </c>
       <c r="G85" s="70" t="inlineStr">
         <is>
-          <t>客観的データへの切替で妥当。</t>
+          <t>機能を厚めに実装する対応で妥当。</t>
         </is>
       </c>
     </row>
@@ -14694,22 +14733,22 @@
       </c>
       <c r="C86" s="69" t="inlineStr">
         <is>
-          <t>H8-03</t>
+          <t>H6-08</t>
         </is>
       </c>
       <c r="D86" s="70" t="inlineStr">
         <is>
-          <t>担当者のスキル自己評価</t>
+          <t>データ信頼性のヒヤリ経験</t>
         </is>
       </c>
       <c r="E86" s="70" t="inlineStr">
         <is>
-          <t>スキルを前提にせず入力作業をマニュアル化する方針</t>
+          <t>自己申告でなく本社側の指摘・修正記録から傾向を把握</t>
         </is>
       </c>
       <c r="G86" s="70" t="inlineStr">
         <is>
-          <t>設計思想の転換として妥当。</t>
+          <t>客観的データへの切替で妥当。</t>
         </is>
       </c>
     </row>
@@ -14721,22 +14760,22 @@
       </c>
       <c r="C87" s="69" t="inlineStr">
         <is>
-          <t>H8-04</t>
+          <t>H8-03</t>
         </is>
       </c>
       <c r="D87" s="70" t="inlineStr">
         <is>
-          <t>業務の拠点内での位置づけ</t>
+          <t>担当者のスキル自己評価</t>
         </is>
       </c>
       <c r="E87" s="70" t="inlineStr">
         <is>
-          <t>自己申告でなく実際の対応状況で督促強度を判断</t>
+          <t>スキルを前提にせず入力作業をマニュアル化する方針</t>
         </is>
       </c>
       <c r="G87" s="70" t="inlineStr">
         <is>
-          <t>客観的データへの切替で妥当。</t>
+          <t>設計思想の転換として妥当。</t>
         </is>
       </c>
     </row>
@@ -14748,29 +14787,29 @@
       </c>
       <c r="C88" s="69" t="inlineStr">
         <is>
-          <t>H9-01</t>
+          <t>H8-04</t>
         </is>
       </c>
       <c r="D88" s="70" t="inlineStr">
         <is>
-          <t>言語・翻訳体制</t>
+          <t>業務の拠点内での位置づけ</t>
         </is>
       </c>
       <c r="E88" s="70" t="inlineStr">
         <is>
-          <t>多言語対応をRFPに含める前提で設計</t>
+          <t>自己申告でなく実際の対応状況で督促強度を判断</t>
         </is>
       </c>
       <c r="G88" s="70" t="inlineStr">
         <is>
-          <t>機能を厚めに実装する対応で妥当。</t>
+          <t>客観的データへの切替で妥当。</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" s="48">
       <c r="A90" s="77" t="inlineStr">
         <is>
-          <t>【集計】81件レビュー ／ 削除に同意 51件 ／ 要注意 30件（うち理由不十分・誤り＝10件、理由は妥当だがリスク残存＝20件）</t>
+          <t>【集計】81件レビュー ／ 削除に同意 48件 ／ 要注意 33件（うち理由不十分・誤り＝12件、理由は妥当だがリスク残存＝21件）</t>
         </is>
       </c>
       <c r="B90" s="78" t="n"/>
@@ -14784,9 +14823,9 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
